--- a/履歴書・職務経歴書/履歴書.xlsx
+++ b/履歴書・職務経歴書/履歴書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Documents/GitHub/private/履歴書・職務経歴書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB0D170-1B7E-884C-98FF-04C5205AF1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853E8EC-999A-5542-BD70-0BC294ABB911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="26140" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37140" yWindow="-21100" windowWidth="29000" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書フォーマット" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>履 歴 書</t>
   </si>
@@ -67,13 +67,6 @@
 貴社規定に準じます</t>
   </si>
   <si>
-    <t>記入上の注意</t>
-  </si>
-  <si>
-    <t>1 .  鉛筆以外の黒又は青の筆記具で記入。　　2 .  数字はアラビア数字で、文字はくずさず正確に書く。
-3 .  ※印のところは、該当するものを○で囲む。</t>
-  </si>
-  <si>
     <t>桾 知香子</t>
     <rPh sb="0" eb="1">
       <t>クヌギ</t>
@@ -81,42 +74,23 @@
     <rPh sb="2" eb="5">
       <t>チカコ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>くぬぎ ちかこ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>　　　令和５　年　8　　月　　4　日現在</t>
-    <rPh sb="3" eb="5">
-      <t>レイワ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1984年　　　　9　月　　　　1　日生　（満　　38　歳）　</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>※　女</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>〒650-0004</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>兵庫県神戸市中央区中山手通4-10-26-1</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>chikakokunugi@icloud.com</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>090-5046-6489</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸女学院高等学部 卒業</t>
@@ -129,7 +103,7 @@
     <rPh sb="10" eb="12">
       <t>ソツギョウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸女学院大学音楽学部ピアノ専攻 卒業</t>
@@ -142,7 +116,7 @@
     <rPh sb="17" eb="19">
       <t>ソツギョウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸女学院大学大学院音楽研究科 終了</t>
@@ -152,7 +126,27 @@
     <rPh sb="16" eb="18">
       <t>シュウリョウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>神戸市立有野北中学校常勤講師 任用</t>
+    <rPh sb="0" eb="4">
+      <t>コウベ</t>
+    </rPh>
+    <rPh sb="4" eb="10">
+      <t>アリノキタ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニn</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>神戸市立有野北中学校常勤講師 任用満了</t>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>久元きぞう講演会連合会 勤務</t>
@@ -165,7 +159,7 @@
     <rPh sb="12" eb="14">
       <t>キンム</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>久元きぞう講演会連合会 退職</t>
@@ -181,7 +175,7 @@
     <rPh sb="12" eb="14">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸女学院大学 入試広報室 / 大学図書館 勤務</t>
@@ -197,14 +191,14 @@
     <rPh sb="22" eb="24">
       <t>キンム</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸女学院大学 入試広報室 / 大学図書館 退職</t>
     <rPh sb="22" eb="24">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸山手女子高等学校音楽科 常勤講師 任用</t>
@@ -223,14 +217,14 @@
     <rPh sb="19" eb="21">
       <t>ニンヨウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>神戸山手女子高等学校音楽科 常勤講師 任用満了</t>
     <rPh sb="21" eb="23">
       <t>マンリョウタイショク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>株式会社CBSデザイン 入社</t>
@@ -240,7 +234,7 @@
     <rPh sb="12" eb="14">
       <t>ニュウシャ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>株式会社ワサビ 入社 (9月より正社員、2019年4月よりアルバイト)</t>
@@ -262,7 +256,7 @@
     <rPh sb="26" eb="27">
       <t>ガツヨリ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>株式会社ワサビ / 株式会社CBSデザイン 退職</t>
@@ -275,36 +269,14 @@
     <rPh sb="22" eb="24">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>株式会社浜学園入社 (2020年3月退職)</t>
-    <rPh sb="0" eb="4">
-      <t>カブシキ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ハマガク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ネn</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ガテゥ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>タイショ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>普通自動車第一種運転免許 取得</t>
     <rPh sb="13" eb="15">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>高等学校教諭専修免許状  取得</t>
@@ -317,7 +289,7 @@
     <rPh sb="8" eb="11">
       <t>m</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>中学校教諭専修免許状  取得</t>
@@ -330,7 +302,7 @@
     <rPh sb="7" eb="10">
       <t>m</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>高等学校教諭一種免許状  取得</t>
@@ -346,7 +318,7 @@
     <rPh sb="8" eb="11">
       <t>メn</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>中学校教諭一種免許状  取得</t>
@@ -362,204 +334,94 @@
     <rPh sb="7" eb="10">
       <t>メn</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t xml:space="preserve">株式会社かもめ 入社 </t>
+    <t>1984年　　　　9　月　　　　1　日生　（満　　39　歳）　</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>〒652-0008</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>兵庫県神戸市兵庫区上祇園町 11-1 サニーハイツ上祇園303</t>
+    <rPh sb="6" eb="9">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>株式会社浜学園退職</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハマガク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タイショク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>株式会社浜学園入社</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ハマガク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウシャ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>　　　令和6　年　9　　月　　10　日現在</t>
+    <rPh sb="3" eb="5">
+      <t>レイワ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>株式会社かもめ 入社 2022年4月よりリ取締役員</t>
     <rPh sb="0" eb="4">
       <t>カブシキ</t>
     </rPh>
     <rPh sb="8" eb="10">
       <t>ニュウシャ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <rPh sb="15" eb="16">
+      <t>ネn</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ガツヨリ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>トリシマリ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>株式会社かもめ 取締役員 リユース事業部 部長</t>
+    <t>株式会社かもめ 退職</t>
     <rPh sb="0" eb="4">
       <t>カブシキ</t>
     </rPh>
-    <rPh sb="8" eb="11">
-      <t>トリシマリヤク</t>
+    <rPh sb="8" eb="10">
+      <t>タイショク</t>
     </rPh>
-    <rPh sb="11" eb="12">
-      <t>イn</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ブチョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>転職。○○にj従事しながら、他社でWEBサイト管理、制作、EC運営業務代行などWEB関係の業務を経験し</t>
-    <rPh sb="0" eb="2">
-      <t>テンショク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t xml:space="preserve">１０ジ </t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>タシャ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t xml:space="preserve">シャ </t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="31" eb="37">
-      <t>ウンエイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カンケイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ギョウム</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>現在の職場に。SEO施策、リユース事業部全体のオペレーション統括、売上管理、サイト管理、</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ショクバ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シサク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ゼn</t>
-    </rPh>
-    <rPh sb="33" eb="37">
-      <t>ウリ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>、RPAを活用した自動化、タスク管理、VBAによる一括出品システムの開発など</t>
-    <rPh sb="5" eb="7">
-      <t>カツヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>イッカテゥ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>カイハテゥ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>私は教職を計6年経験後、オンラインのプログラミングスクールに通いながら、システム提供会社のサポート部に</t>
-    <rPh sb="0" eb="1">
-      <t>ワタセィ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キョウショク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ケイサn</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ネn</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ケイケn</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>カヨイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ガイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>「自分がいなくても事業が運営できる」組織づくりに成功したと思っている。</t>
-    <rPh sb="1" eb="3">
-      <t>ジブn</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジギョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ウンエイデク</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ソシキ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>オモッテ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>私が貴社を志望する理由はBpassに魅力を感じたからです。</t>
-    <rPh sb="0" eb="1">
-      <t>ワタセィ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キシャ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シボウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>リユウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ミリョク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カンゼィ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>貴社規定に準じます。</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">キシャ </t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キテイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>神戸市立有野北中学校常勤講師 教員</t>
-    <rPh sb="0" eb="4">
-      <t>コウベ</t>
-    </rPh>
-    <rPh sb="4" eb="10">
-      <t>アリノキタ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>キョウイn</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -614,6 +476,13 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="MS PMincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -621,15 +490,14 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="MS PMincho"/>
-      <family val="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="MS PGothic"/>
-      <family val="3"/>
+      <name val="MS PMincho"/>
+      <family val="1"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -641,7 +509,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -993,6 +861,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="hair">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="double">
@@ -1073,6 +965,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1092,168 +995,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1274,71 +1020,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1362,12 +1088,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1377,142 +1097,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1524,14 +1127,95 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1542,7 +1226,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1553,6 +1237,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2206,7 +1896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD1003"/>
+  <dimension ref="A1:AD1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -2242,9 +1932,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="9" customHeight="1">
-      <c r="A1" s="75"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
+      <c r="A1" s="57"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2256,93 +1946,93 @@
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="1:30" ht="9" customHeight="1">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
     </row>
     <row r="3" spans="1:30" ht="9" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
     </row>
     <row r="4" spans="1:30" ht="9" customHeight="1">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2"/>
       <c r="F4" s="5"/>
@@ -2354,94 +2044,94 @@
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="66" t="s">
+      <c r="P4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="55" t="s">
+      <c r="Q4" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="57"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="41"/>
     </row>
     <row r="5" spans="1:30" ht="9" customHeight="1">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="77" t="s">
-        <v>17</v>
+      <c r="F5" s="59" t="s">
+        <v>42</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="44"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="21"/>
     </row>
     <row r="6" spans="1:30" ht="9" customHeight="1">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="59"/>
-      <c r="W6" s="59"/>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="60"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64"/>
+      <c r="AC6" s="64"/>
+      <c r="AD6" s="65"/>
     </row>
     <row r="7" spans="1:30" ht="9" customHeight="1">
       <c r="A7" s="2"/>
@@ -2458,690 +2148,690 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="68">
+      <c r="O7" s="46">
         <v>2008</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="47">
         <v>3</v>
       </c>
-      <c r="Q7" s="61" t="s">
-        <v>41</v>
+      <c r="Q7" s="48" t="s">
+        <v>36</v>
       </c>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="44"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="21"/>
     </row>
     <row r="8" spans="1:30" ht="9" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="72" t="s">
-        <v>16</v>
+      <c r="B8" s="61" t="s">
+        <v>14</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="44"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="21"/>
     </row>
     <row r="9" spans="1:30" ht="9" customHeight="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="42"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="34"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="45"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="33"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="33"/>
+      <c r="AD9" s="34"/>
     </row>
     <row r="10" spans="1:30" ht="9" customHeight="1">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="93" t="s">
-        <v>15</v>
+      <c r="B10" s="74" t="s">
+        <v>13</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="68">
+      <c r="O10" s="46">
         <v>2008</v>
       </c>
-      <c r="P10" s="70">
+      <c r="P10" s="47">
         <v>3</v>
       </c>
-      <c r="Q10" s="61" t="s">
-        <v>40</v>
+      <c r="Q10" s="48" t="s">
+        <v>35</v>
       </c>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="38"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="38"/>
-      <c r="AD10" s="44"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="21"/>
     </row>
     <row r="11" spans="1:30" ht="9" customHeight="1">
-      <c r="A11" s="29"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
       <c r="J11" s="6"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="38"/>
-      <c r="AD11" s="44"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="21"/>
     </row>
     <row r="12" spans="1:30" ht="9" customHeight="1">
-      <c r="A12" s="29"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="21"/>
       <c r="J12" s="6"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="45"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="34"/>
     </row>
     <row r="13" spans="1:30" ht="9" customHeight="1">
-      <c r="A13" s="29"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="21"/>
       <c r="J13" s="6"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="86">
+      <c r="O13" s="35">
         <v>2010</v>
       </c>
-      <c r="P13" s="31">
+      <c r="P13" s="25">
         <v>3</v>
       </c>
-      <c r="Q13" s="34" t="s">
-        <v>39</v>
+      <c r="Q13" s="28" t="s">
+        <v>34</v>
       </c>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="35"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="43"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="30"/>
     </row>
     <row r="14" spans="1:30" ht="9" customHeight="1">
-      <c r="A14" s="29"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="21"/>
       <c r="J14" s="6"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="38"/>
-      <c r="AB14" s="38"/>
-      <c r="AC14" s="38"/>
-      <c r="AD14" s="44"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="21"/>
     </row>
     <row r="15" spans="1:30" ht="9" customHeight="1">
-      <c r="A15" s="74"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="82"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="6"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="45"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="34"/>
     </row>
     <row r="16" spans="1:30" ht="9" customHeight="1">
-      <c r="A16" s="95" t="s">
-        <v>18</v>
+      <c r="A16" s="75" t="s">
+        <v>37</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="62" t="s">
-        <v>19</v>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="39" t="s">
+        <v>15</v>
       </c>
-      <c r="I16" s="51"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="86">
+      <c r="O16" s="35">
         <v>2010</v>
       </c>
-      <c r="P16" s="31">
+      <c r="P16" s="25">
         <v>3</v>
       </c>
-      <c r="Q16" s="34" t="s">
-        <v>38</v>
+      <c r="Q16" s="28" t="s">
+        <v>33</v>
       </c>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="43"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="30"/>
     </row>
     <row r="17" spans="1:30" ht="9" customHeight="1">
-      <c r="A17" s="52"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="39"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="21"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="64"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="38"/>
-      <c r="AC17" s="38"/>
-      <c r="AD17" s="44"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="21"/>
     </row>
     <row r="18" spans="1:30" ht="9" customHeight="1">
-      <c r="A18" s="81"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="82"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="41"/>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="41"/>
-      <c r="AB18" s="41"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="45"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="34"/>
     </row>
     <row r="19" spans="1:30" ht="9" customHeight="1">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="96" t="s">
+      <c r="B19" s="61"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="51"/>
+      <c r="L19" s="41"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="86">
+      <c r="O19" s="35">
         <v>2010</v>
       </c>
-      <c r="P19" s="31">
+      <c r="P19" s="25">
         <v>3</v>
       </c>
-      <c r="Q19" s="34" t="s">
-        <v>37</v>
+      <c r="Q19" s="28" t="s">
+        <v>32</v>
       </c>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="43"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="30"/>
     </row>
     <row r="20" spans="1:30" ht="9" customHeight="1">
-      <c r="A20" s="30"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="39"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="7"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="38"/>
-      <c r="Z20" s="38"/>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="38"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="44"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="21"/>
     </row>
     <row r="21" spans="1:30" ht="9" customHeight="1">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="92" t="s">
-        <v>20</v>
+      <c r="B21" s="73" t="s">
+        <v>38</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="80" t="s">
-        <v>23</v>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="68" t="s">
+        <v>17</v>
       </c>
-      <c r="L21" s="36"/>
+      <c r="L21" s="30"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="87"/>
-      <c r="P21" s="88"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
-      <c r="AA21" s="47"/>
-      <c r="AB21" s="47"/>
-      <c r="AC21" s="47"/>
-      <c r="AD21" s="48"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="34"/>
     </row>
     <row r="22" spans="1:30" ht="9" customHeight="1">
-      <c r="A22" s="29"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="82"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="24"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="29"/>
+      <c r="AD22" s="30"/>
     </row>
     <row r="23" spans="1:30" ht="9" customHeight="1">
-      <c r="A23" s="29"/>
-      <c r="B23" s="97" t="s">
-        <v>21</v>
+      <c r="A23" s="36"/>
+      <c r="B23" s="77" t="s">
+        <v>39</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="83" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="39"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="49" t="s">
+      <c r="O23" s="36"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="21"/>
+    </row>
+    <row r="24" spans="1:30" ht="9" customHeight="1">
+      <c r="A24" s="36"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="49"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="23"/>
+      <c r="X24" s="23"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="23"/>
+      <c r="AA24" s="23"/>
+      <c r="AB24" s="23"/>
+      <c r="AC24" s="23"/>
+      <c r="AD24" s="24"/>
+    </row>
+    <row r="25" spans="1:30" ht="9" customHeight="1">
+      <c r="A25" s="36"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="79"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+    </row>
+    <row r="26" spans="1:30" ht="9" customHeight="1">
+      <c r="A26" s="71"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
-      <c r="Y23" s="50"/>
-      <c r="Z23" s="50"/>
-      <c r="AA23" s="50"/>
-      <c r="AB23" s="50"/>
-      <c r="AC23" s="50"/>
-      <c r="AD23" s="51"/>
-    </row>
-    <row r="24" spans="1:30" ht="9" customHeight="1">
-      <c r="A24" s="29"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="38"/>
-      <c r="Y24" s="38"/>
-      <c r="Z24" s="38"/>
-      <c r="AA24" s="38"/>
-      <c r="AB24" s="38"/>
-      <c r="AC24" s="38"/>
-      <c r="AD24" s="39"/>
-    </row>
-    <row r="25" spans="1:30" ht="9" customHeight="1">
-      <c r="A25" s="29"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="99"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="52"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="53"/>
-      <c r="T25" s="53"/>
-      <c r="U25" s="53"/>
-      <c r="V25" s="53"/>
-      <c r="W25" s="53"/>
-      <c r="X25" s="53"/>
-      <c r="Y25" s="53"/>
-      <c r="Z25" s="53"/>
-      <c r="AA25" s="53"/>
-      <c r="AB25" s="53"/>
-      <c r="AC25" s="53"/>
-      <c r="AD25" s="39"/>
-    </row>
-    <row r="26" spans="1:30" ht="9" customHeight="1">
-      <c r="A26" s="74"/>
-      <c r="B26" s="94"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="94"/>
-      <c r="E26" s="94"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="82"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="19"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="51"/>
+      <c r="W26" s="51"/>
+      <c r="X26" s="51"/>
+      <c r="Y26" s="51"/>
+      <c r="Z26" s="51"/>
+      <c r="AA26" s="51"/>
+      <c r="AB26" s="51"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="52"/>
     </row>
     <row r="27" spans="1:30" ht="9" customHeight="1">
       <c r="A27" s="3"/>
@@ -3158,1964 +2848,1772 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="25"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="9" customHeight="1">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="91" t="s">
+      <c r="B28" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="51"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="41"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="25"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="55"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="55"/>
+      <c r="X28" s="55"/>
+      <c r="Y28" s="55"/>
+      <c r="Z28" s="55"/>
+      <c r="AA28" s="55"/>
+      <c r="AB28" s="55"/>
+      <c r="AC28" s="55"/>
+      <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="9" customHeight="1">
-      <c r="A29" s="29"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="39"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="21"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="24"/>
-      <c r="AC29" s="24"/>
-      <c r="AD29" s="25"/>
-    </row>
-    <row r="30" spans="1:30" ht="9" customHeight="1">
-      <c r="A30" s="90"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="85"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="55"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="55"/>
+      <c r="Z29" s="55"/>
+      <c r="AA29" s="55"/>
+      <c r="AB29" s="55"/>
+      <c r="AC29" s="55"/>
+      <c r="AD29" s="54"/>
+    </row>
+    <row r="30" spans="1:30" ht="9" customHeight="1" thickBot="1">
+      <c r="A30" s="43"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="65"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="24"/>
-      <c r="T30" s="24"/>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="24"/>
-      <c r="AC30" s="24"/>
-      <c r="AD30" s="25"/>
-    </row>
-    <row r="31" spans="1:30" ht="9" customHeight="1">
-      <c r="A31" s="28">
+      <c r="O30" s="53"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="20"/>
+      <c r="AD30" s="54"/>
+    </row>
+    <row r="31" spans="1:30" ht="9" customHeight="1" thickTop="1">
+      <c r="A31" s="35">
         <v>2003</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="25">
         <v>3</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="54"/>
+    </row>
+    <row r="32" spans="1:30" ht="9" customHeight="1">
+      <c r="A32" s="36"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="54"/>
+    </row>
+    <row r="33" spans="1:30" ht="9" customHeight="1">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="54"/>
+    </row>
+    <row r="34" spans="1:30" ht="9" customHeight="1">
+      <c r="A34" s="35">
+        <v>2008</v>
+      </c>
+      <c r="B34" s="25">
+        <v>3</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="54"/>
+    </row>
+    <row r="35" spans="1:30" ht="9" customHeight="1">
+      <c r="A35" s="36"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="54"/>
+    </row>
+    <row r="36" spans="1:30" ht="9" customHeight="1">
+      <c r="A36" s="37"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="54"/>
+    </row>
+    <row r="37" spans="1:30" ht="9" customHeight="1">
+      <c r="A37" s="35">
+        <v>2010</v>
+      </c>
+      <c r="B37" s="25">
+        <v>3</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="54"/>
+    </row>
+    <row r="38" spans="1:30" ht="9" customHeight="1">
+      <c r="A38" s="36"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="54"/>
+    </row>
+    <row r="39" spans="1:30" ht="9" customHeight="1">
+      <c r="A39" s="37"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="54"/>
+    </row>
+    <row r="40" spans="1:30" ht="9" customHeight="1">
+      <c r="A40" s="35">
+        <v>2010</v>
+      </c>
+      <c r="B40" s="25">
+        <v>4</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="54"/>
+    </row>
+    <row r="41" spans="1:30" ht="9" customHeight="1">
+      <c r="A41" s="36"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="54"/>
+    </row>
+    <row r="42" spans="1:30" ht="9" customHeight="1">
+      <c r="A42" s="37"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="53"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="54"/>
+    </row>
+    <row r="43" spans="1:30" ht="9" customHeight="1">
+      <c r="A43" s="35">
+        <v>2013</v>
+      </c>
+      <c r="B43" s="25">
+        <v>3</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="53"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20"/>
+      <c r="AD43" s="54"/>
+    </row>
+    <row r="44" spans="1:30" ht="9" customHeight="1">
+      <c r="A44" s="36"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="53"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="20"/>
+      <c r="AC44" s="20"/>
+      <c r="AD44" s="54"/>
+    </row>
+    <row r="45" spans="1:30" ht="9" customHeight="1">
+      <c r="A45" s="37"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="20"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="20"/>
+      <c r="AC45" s="20"/>
+      <c r="AD45" s="54"/>
+    </row>
+    <row r="46" spans="1:30" ht="9" customHeight="1">
+      <c r="A46" s="35">
+        <v>2013</v>
+      </c>
+      <c r="B46" s="25">
+        <v>4</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="53"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="20"/>
+      <c r="AC46" s="20"/>
+      <c r="AD46" s="54"/>
+    </row>
+    <row r="47" spans="1:30" ht="9" customHeight="1">
+      <c r="A47" s="36"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="10"/>
+    </row>
+    <row r="48" spans="1:30" ht="9" customHeight="1">
+      <c r="A48" s="37"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="11"/>
+      <c r="AD48" s="12"/>
+    </row>
+    <row r="49" spans="1:30" ht="9" customHeight="1">
+      <c r="A49" s="35">
+        <v>2013</v>
+      </c>
+      <c r="B49" s="25">
+        <v>10</v>
+      </c>
+      <c r="C49" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="24"/>
-      <c r="T31" s="24"/>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="24"/>
-      <c r="AC31" s="24"/>
-      <c r="AD31" s="25"/>
-    </row>
-    <row r="32" spans="1:30" ht="9" customHeight="1">
-      <c r="A32" s="29"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="24"/>
-      <c r="AC32" s="24"/>
-      <c r="AD32" s="25"/>
-    </row>
-    <row r="33" spans="1:30" ht="9" customHeight="1">
-      <c r="A33" s="30"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="24"/>
-      <c r="R33" s="24"/>
-      <c r="S33" s="24"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="24"/>
-      <c r="V33" s="24"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
-      <c r="AA33" s="24"/>
-      <c r="AB33" s="24"/>
-      <c r="AC33" s="24"/>
-      <c r="AD33" s="25"/>
-    </row>
-    <row r="34" spans="1:30" ht="9" customHeight="1">
-      <c r="A34" s="28">
-        <v>2008</v>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="11"/>
+      <c r="AD49" s="12"/>
+    </row>
+    <row r="50" spans="1:30" ht="9" customHeight="1">
+      <c r="A50" s="36"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="11"/>
+      <c r="AD50" s="12"/>
+    </row>
+    <row r="51" spans="1:30" ht="9" customHeight="1">
+      <c r="A51" s="37"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="11"/>
+      <c r="AD51" s="12"/>
+    </row>
+    <row r="52" spans="1:30" ht="9" customHeight="1">
+      <c r="A52" s="35">
+        <v>2013</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B52" s="25">
+        <v>11</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="11"/>
+      <c r="AD52" s="12"/>
+    </row>
+    <row r="53" spans="1:30" ht="9" customHeight="1">
+      <c r="A53" s="36"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="11"/>
+      <c r="AD53" s="12"/>
+    </row>
+    <row r="54" spans="1:30" ht="9" customHeight="1">
+      <c r="A54" s="37"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="11"/>
+      <c r="AD54" s="12"/>
+    </row>
+    <row r="55" spans="1:30" ht="9" customHeight="1">
+      <c r="A55" s="35">
+        <v>2014</v>
+      </c>
+      <c r="B55" s="25">
         <v>3</v>
       </c>
-      <c r="C34" s="34" t="s">
-        <v>25</v>
+      <c r="C55" s="38" t="s">
+        <v>26</v>
       </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="24"/>
-      <c r="T34" s="24"/>
-      <c r="U34" s="24"/>
-      <c r="V34" s="24"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
-      <c r="AA34" s="24"/>
-      <c r="AB34" s="24"/>
-      <c r="AC34" s="24"/>
-      <c r="AD34" s="25"/>
-    </row>
-    <row r="35" spans="1:30" ht="9" customHeight="1">
-      <c r="A35" s="29"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="38"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
-      <c r="V35" s="24"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="24"/>
-      <c r="Z35" s="24"/>
-      <c r="AA35" s="24"/>
-      <c r="AB35" s="24"/>
-      <c r="AC35" s="24"/>
-      <c r="AD35" s="25"/>
-    </row>
-    <row r="36" spans="1:30" ht="9" customHeight="1">
-      <c r="A36" s="30"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="25"/>
-    </row>
-    <row r="37" spans="1:30" ht="9" customHeight="1">
-      <c r="A37" s="28">
-        <v>2010</v>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="11"/>
+      <c r="AD55" s="12"/>
+    </row>
+    <row r="56" spans="1:30" ht="9" customHeight="1">
+      <c r="A56" s="36"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="21"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="11"/>
+      <c r="AD56" s="12"/>
+    </row>
+    <row r="57" spans="1:30" ht="9" customHeight="1">
+      <c r="A57" s="37"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="34"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="11"/>
+      <c r="AD57" s="12"/>
+    </row>
+    <row r="58" spans="1:30" ht="9" customHeight="1">
+      <c r="A58" s="35">
+        <v>2014</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B58" s="25">
+        <v>4</v>
+      </c>
+      <c r="C58" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="11"/>
+      <c r="AD58" s="12"/>
+    </row>
+    <row r="59" spans="1:30" ht="9" customHeight="1">
+      <c r="A59" s="36"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="11"/>
+      <c r="AD59" s="12"/>
+    </row>
+    <row r="60" spans="1:30" ht="9" customHeight="1">
+      <c r="A60" s="37"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="11"/>
+      <c r="AD60" s="12"/>
+    </row>
+    <row r="61" spans="1:30" ht="9" customHeight="1">
+      <c r="A61" s="35">
+        <v>2017</v>
+      </c>
+      <c r="B61" s="25">
         <v>3</v>
       </c>
-      <c r="C37" s="34" t="s">
-        <v>26</v>
+      <c r="C61" s="38" t="s">
+        <v>28</v>
       </c>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="24"/>
-      <c r="AC37" s="24"/>
-      <c r="AD37" s="25"/>
-    </row>
-    <row r="38" spans="1:30" ht="9" customHeight="1">
-      <c r="A38" s="29"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
-      <c r="AC38" s="24"/>
-      <c r="AD38" s="25"/>
-    </row>
-    <row r="39" spans="1:30" ht="9" customHeight="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="24"/>
-      <c r="Y39" s="24"/>
-      <c r="Z39" s="24"/>
-      <c r="AA39" s="24"/>
-      <c r="AB39" s="24"/>
-      <c r="AC39" s="24"/>
-      <c r="AD39" s="25"/>
-    </row>
-    <row r="40" spans="1:30" ht="9" customHeight="1">
-      <c r="A40" s="28">
-        <v>2010</v>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="11"/>
+      <c r="AD61" s="12"/>
+    </row>
+    <row r="62" spans="1:30" ht="9" customHeight="1">
+      <c r="A62" s="36"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="21"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="11"/>
+      <c r="AD62" s="12"/>
+    </row>
+    <row r="63" spans="1:30" ht="9" customHeight="1">
+      <c r="A63" s="37"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="34"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="11"/>
+      <c r="AD63" s="12"/>
+    </row>
+    <row r="64" spans="1:30" ht="9" customHeight="1">
+      <c r="A64" s="35">
+        <v>2017</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B64" s="25">
+        <v>6</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="11"/>
+      <c r="AD64" s="12"/>
+    </row>
+    <row r="65" spans="1:30" ht="9" customHeight="1">
+      <c r="A65" s="36"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="21"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="14"/>
+      <c r="Q65" s="14"/>
+      <c r="R65" s="14"/>
+      <c r="S65" s="14"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="14"/>
+      <c r="V65" s="14"/>
+      <c r="W65" s="14"/>
+      <c r="X65" s="14"/>
+      <c r="Y65" s="14"/>
+      <c r="Z65" s="14"/>
+      <c r="AA65" s="14"/>
+      <c r="AB65" s="14"/>
+      <c r="AC65" s="14"/>
+      <c r="AD65" s="15"/>
+    </row>
+    <row r="66" spans="1:30" ht="9" customHeight="1">
+      <c r="A66" s="37"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="34"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+    </row>
+    <row r="67" spans="1:30" ht="9" customHeight="1">
+      <c r="A67" s="35">
+        <v>2019</v>
+      </c>
+      <c r="B67" s="25">
         <v>4</v>
       </c>
-      <c r="C40" s="34" t="s">
-        <v>51</v>
+      <c r="C67" s="28" t="s">
+        <v>29</v>
       </c>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
-      <c r="AB40" s="24"/>
-      <c r="AC40" s="24"/>
-      <c r="AD40" s="25"/>
-    </row>
-    <row r="41" spans="1:30" ht="9" customHeight="1">
-      <c r="A41" s="29"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
-      <c r="AB41" s="24"/>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="25"/>
-    </row>
-    <row r="42" spans="1:30" ht="9" customHeight="1">
-      <c r="A42" s="30"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="24"/>
-      <c r="T42" s="24"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
-      <c r="AA42" s="24"/>
-      <c r="AB42" s="24"/>
-      <c r="AC42" s="24"/>
-      <c r="AD42" s="25"/>
-    </row>
-    <row r="43" spans="1:30" ht="9" customHeight="1">
-      <c r="A43" s="28">
-        <v>2013</v>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="1:30" ht="9" customHeight="1">
+      <c r="A68" s="36"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="39" t="s">
+        <v>11</v>
       </c>
-      <c r="B43" s="31">
+      <c r="P68" s="40"/>
+      <c r="Q68" s="40"/>
+      <c r="R68" s="40"/>
+      <c r="S68" s="40"/>
+      <c r="T68" s="40"/>
+      <c r="U68" s="40"/>
+      <c r="V68" s="40"/>
+      <c r="W68" s="40"/>
+      <c r="X68" s="40"/>
+      <c r="Y68" s="40"/>
+      <c r="Z68" s="40"/>
+      <c r="AA68" s="40"/>
+      <c r="AB68" s="40"/>
+      <c r="AC68" s="40"/>
+      <c r="AD68" s="41"/>
+    </row>
+    <row r="69" spans="1:30" ht="9" customHeight="1">
+      <c r="A69" s="37"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="34"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="19"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="20"/>
+      <c r="R69" s="20"/>
+      <c r="S69" s="20"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="20"/>
+      <c r="V69" s="20"/>
+      <c r="W69" s="20"/>
+      <c r="X69" s="20"/>
+      <c r="Y69" s="20"/>
+      <c r="Z69" s="20"/>
+      <c r="AA69" s="20"/>
+      <c r="AB69" s="20"/>
+      <c r="AC69" s="20"/>
+      <c r="AD69" s="21"/>
+    </row>
+    <row r="70" spans="1:30" ht="9" customHeight="1" thickBot="1">
+      <c r="A70" s="35">
+        <v>2019</v>
+      </c>
+      <c r="B70" s="25">
+        <v>10</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="19"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="20"/>
+      <c r="R70" s="20"/>
+      <c r="S70" s="20"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="20"/>
+      <c r="V70" s="20"/>
+      <c r="W70" s="20"/>
+      <c r="X70" s="20"/>
+      <c r="Y70" s="20"/>
+      <c r="Z70" s="20"/>
+      <c r="AA70" s="20"/>
+      <c r="AB70" s="20"/>
+      <c r="AC70" s="20"/>
+      <c r="AD70" s="21"/>
+    </row>
+    <row r="71" spans="1:30" ht="9" customHeight="1" thickTop="1">
+      <c r="A71" s="36"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="P71" s="17"/>
+      <c r="Q71" s="17"/>
+      <c r="R71" s="17"/>
+      <c r="S71" s="17"/>
+      <c r="T71" s="17"/>
+      <c r="U71" s="17"/>
+      <c r="V71" s="17"/>
+      <c r="W71" s="17"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="17"/>
+      <c r="Z71" s="17"/>
+      <c r="AA71" s="17"/>
+      <c r="AB71" s="17"/>
+      <c r="AC71" s="17"/>
+      <c r="AD71" s="18"/>
+    </row>
+    <row r="72" spans="1:30" ht="9" customHeight="1">
+      <c r="A72" s="37"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="33"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="33"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="33"/>
+      <c r="L72" s="34"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+      <c r="R72" s="20"/>
+      <c r="S72" s="20"/>
+      <c r="T72" s="20"/>
+      <c r="U72" s="20"/>
+      <c r="V72" s="20"/>
+      <c r="W72" s="20"/>
+      <c r="X72" s="20"/>
+      <c r="Y72" s="20"/>
+      <c r="Z72" s="20"/>
+      <c r="AA72" s="20"/>
+      <c r="AB72" s="20"/>
+      <c r="AC72" s="20"/>
+      <c r="AD72" s="21"/>
+    </row>
+    <row r="73" spans="1:30" ht="9" customHeight="1">
+      <c r="A73" s="35">
+        <v>2020</v>
+      </c>
+      <c r="B73" s="25">
         <v>3</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="24"/>
-      <c r="AC43" s="24"/>
-      <c r="AD43" s="25"/>
-    </row>
-    <row r="44" spans="1:30" ht="9" customHeight="1">
-      <c r="A44" s="29"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="38"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
-      <c r="R44" s="24"/>
-      <c r="S44" s="24"/>
-      <c r="T44" s="24"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="25"/>
-    </row>
-    <row r="45" spans="1:30" ht="9" customHeight="1">
-      <c r="A45" s="30"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="24"/>
-      <c r="R45" s="24"/>
-      <c r="S45" s="24"/>
-      <c r="T45" s="24"/>
-      <c r="U45" s="24"/>
-      <c r="V45" s="24"/>
-      <c r="W45" s="24"/>
-      <c r="X45" s="24"/>
-      <c r="Y45" s="24"/>
-      <c r="Z45" s="24"/>
-      <c r="AA45" s="24"/>
-      <c r="AB45" s="24"/>
-      <c r="AC45" s="24"/>
-      <c r="AD45" s="25"/>
-    </row>
-    <row r="46" spans="1:30" ht="9" customHeight="1">
-      <c r="A46" s="28">
-        <v>2013</v>
+      <c r="C73" s="28" t="s">
+        <v>40</v>
       </c>
-      <c r="B46" s="31">
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="29"/>
+      <c r="J73" s="29"/>
+      <c r="K73" s="29"/>
+      <c r="L73" s="30"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="19"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+      <c r="T73" s="20"/>
+      <c r="U73" s="20"/>
+      <c r="V73" s="20"/>
+      <c r="W73" s="20"/>
+      <c r="X73" s="20"/>
+      <c r="Y73" s="20"/>
+      <c r="Z73" s="20"/>
+      <c r="AA73" s="20"/>
+      <c r="AB73" s="20"/>
+      <c r="AC73" s="20"/>
+      <c r="AD73" s="21"/>
+    </row>
+    <row r="74" spans="1:30" ht="9" customHeight="1">
+      <c r="A74" s="36"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="19"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
+      <c r="R74" s="20"/>
+      <c r="S74" s="20"/>
+      <c r="T74" s="20"/>
+      <c r="U74" s="20"/>
+      <c r="V74" s="20"/>
+      <c r="W74" s="20"/>
+      <c r="X74" s="20"/>
+      <c r="Y74" s="20"/>
+      <c r="Z74" s="20"/>
+      <c r="AA74" s="20"/>
+      <c r="AB74" s="20"/>
+      <c r="AC74" s="20"/>
+      <c r="AD74" s="21"/>
+    </row>
+    <row r="75" spans="1:30" ht="9" customHeight="1">
+      <c r="A75" s="37"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="33"/>
+      <c r="I75" s="33"/>
+      <c r="J75" s="33"/>
+      <c r="K75" s="33"/>
+      <c r="L75" s="34"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="19"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="20"/>
+      <c r="V75" s="20"/>
+      <c r="W75" s="20"/>
+      <c r="X75" s="20"/>
+      <c r="Y75" s="20"/>
+      <c r="Z75" s="20"/>
+      <c r="AA75" s="20"/>
+      <c r="AB75" s="20"/>
+      <c r="AC75" s="20"/>
+      <c r="AD75" s="21"/>
+    </row>
+    <row r="76" spans="1:30" ht="9" customHeight="1">
+      <c r="A76" s="35">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="25">
+        <v>3</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="19"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="20"/>
+      <c r="U76" s="20"/>
+      <c r="V76" s="20"/>
+      <c r="W76" s="20"/>
+      <c r="X76" s="20"/>
+      <c r="Y76" s="20"/>
+      <c r="Z76" s="20"/>
+      <c r="AA76" s="20"/>
+      <c r="AB76" s="20"/>
+      <c r="AC76" s="20"/>
+      <c r="AD76" s="21"/>
+    </row>
+    <row r="77" spans="1:30" ht="9" customHeight="1">
+      <c r="A77" s="46"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
+      <c r="L77" s="21"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="19"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="20"/>
+      <c r="V77" s="20"/>
+      <c r="W77" s="20"/>
+      <c r="X77" s="20"/>
+      <c r="Y77" s="20"/>
+      <c r="Z77" s="20"/>
+      <c r="AA77" s="20"/>
+      <c r="AB77" s="20"/>
+      <c r="AC77" s="20"/>
+      <c r="AD77" s="21"/>
+    </row>
+    <row r="78" spans="1:30" ht="9" customHeight="1">
+      <c r="A78" s="82"/>
+      <c r="B78" s="83"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33"/>
+      <c r="G78" s="33"/>
+      <c r="H78" s="33"/>
+      <c r="I78" s="33"/>
+      <c r="J78" s="33"/>
+      <c r="K78" s="33"/>
+      <c r="L78" s="34"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="19"/>
+      <c r="P78" s="20"/>
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="20"/>
+      <c r="U78" s="20"/>
+      <c r="V78" s="20"/>
+      <c r="W78" s="20"/>
+      <c r="X78" s="20"/>
+      <c r="Y78" s="20"/>
+      <c r="Z78" s="20"/>
+      <c r="AA78" s="20"/>
+      <c r="AB78" s="20"/>
+      <c r="AC78" s="20"/>
+      <c r="AD78" s="21"/>
+    </row>
+    <row r="79" spans="1:30" ht="9" customHeight="1">
+      <c r="A79" s="35">
+        <v>2021</v>
+      </c>
+      <c r="B79" s="25">
         <v>4</v>
       </c>
-      <c r="C46" s="34" t="s">
-        <v>27</v>
+      <c r="C79" s="28" t="s">
+        <v>43</v>
       </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="24"/>
-      <c r="R46" s="24"/>
-      <c r="S46" s="24"/>
-      <c r="T46" s="24"/>
-      <c r="U46" s="24"/>
-      <c r="V46" s="24"/>
-      <c r="W46" s="24"/>
-      <c r="X46" s="24"/>
-      <c r="Y46" s="24"/>
-      <c r="Z46" s="24"/>
-      <c r="AA46" s="24"/>
-      <c r="AB46" s="24"/>
-      <c r="AC46" s="24"/>
-      <c r="AD46" s="25"/>
-    </row>
-    <row r="47" spans="1:30" ht="9" customHeight="1">
-      <c r="A47" s="29"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="38"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="24"/>
-      <c r="R47" s="24"/>
-      <c r="S47" s="24"/>
-      <c r="T47" s="24"/>
-      <c r="U47" s="24"/>
-      <c r="V47" s="24"/>
-      <c r="W47" s="24"/>
-      <c r="X47" s="24"/>
-      <c r="Y47" s="24"/>
-      <c r="Z47" s="24"/>
-      <c r="AA47" s="24"/>
-      <c r="AB47" s="24"/>
-      <c r="AC47" s="24"/>
-      <c r="AD47" s="25"/>
-    </row>
-    <row r="48" spans="1:30" ht="9" customHeight="1">
-      <c r="A48" s="30"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
-      <c r="R48" s="24"/>
-      <c r="S48" s="24"/>
-      <c r="T48" s="24"/>
-      <c r="U48" s="24"/>
-      <c r="V48" s="24"/>
-      <c r="W48" s="24"/>
-      <c r="X48" s="24"/>
-      <c r="Y48" s="24"/>
-      <c r="Z48" s="24"/>
-      <c r="AA48" s="24"/>
-      <c r="AB48" s="24"/>
-      <c r="AC48" s="24"/>
-      <c r="AD48" s="25"/>
-    </row>
-    <row r="49" spans="1:30" ht="9" customHeight="1">
-      <c r="A49" s="28">
-        <v>2013</v>
+      <c r="D79" s="29"/>
+      <c r="E79" s="29"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="29"/>
+      <c r="K79" s="29"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="19"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="20"/>
+      <c r="U79" s="20"/>
+      <c r="V79" s="20"/>
+      <c r="W79" s="20"/>
+      <c r="X79" s="20"/>
+      <c r="Y79" s="20"/>
+      <c r="Z79" s="20"/>
+      <c r="AA79" s="20"/>
+      <c r="AB79" s="20"/>
+      <c r="AC79" s="20"/>
+      <c r="AD79" s="21"/>
+    </row>
+    <row r="80" spans="1:30" ht="9" customHeight="1">
+      <c r="A80" s="36"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="20"/>
+      <c r="L80" s="21"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="19"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="20"/>
+      <c r="U80" s="20"/>
+      <c r="V80" s="20"/>
+      <c r="W80" s="20"/>
+      <c r="X80" s="20"/>
+      <c r="Y80" s="20"/>
+      <c r="Z80" s="20"/>
+      <c r="AA80" s="20"/>
+      <c r="AB80" s="20"/>
+      <c r="AC80" s="20"/>
+      <c r="AD80" s="21"/>
+    </row>
+    <row r="81" spans="1:30" ht="9" customHeight="1">
+      <c r="A81" s="37"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33"/>
+      <c r="G81" s="33"/>
+      <c r="H81" s="33"/>
+      <c r="I81" s="33"/>
+      <c r="J81" s="33"/>
+      <c r="K81" s="33"/>
+      <c r="L81" s="34"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="19"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="20"/>
+      <c r="V81" s="20"/>
+      <c r="W81" s="20"/>
+      <c r="X81" s="20"/>
+      <c r="Y81" s="20"/>
+      <c r="Z81" s="20"/>
+      <c r="AA81" s="20"/>
+      <c r="AB81" s="20"/>
+      <c r="AC81" s="20"/>
+      <c r="AD81" s="21"/>
+    </row>
+    <row r="82" spans="1:30" ht="14">
+      <c r="A82" s="35">
+        <v>2025</v>
       </c>
-      <c r="B49" s="31">
-        <v>10</v>
+      <c r="B82" s="25">
+        <v>9</v>
       </c>
-      <c r="C49" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="35"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24"/>
-      <c r="R49" s="24"/>
-      <c r="S49" s="24"/>
-      <c r="T49" s="24"/>
-      <c r="U49" s="24"/>
-      <c r="V49" s="24"/>
-      <c r="W49" s="24"/>
-      <c r="X49" s="24"/>
-      <c r="Y49" s="24"/>
-      <c r="Z49" s="24"/>
-      <c r="AA49" s="24"/>
-      <c r="AB49" s="24"/>
-      <c r="AC49" s="24"/>
-      <c r="AD49" s="25"/>
-    </row>
-    <row r="50" spans="1:30" ht="9" customHeight="1">
-      <c r="A50" s="29"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="39"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="24"/>
-      <c r="R50" s="24"/>
-      <c r="S50" s="24"/>
-      <c r="T50" s="24"/>
-      <c r="U50" s="24"/>
-      <c r="V50" s="24"/>
-      <c r="W50" s="24"/>
-      <c r="X50" s="24"/>
-      <c r="Y50" s="24"/>
-      <c r="Z50" s="24"/>
-      <c r="AA50" s="24"/>
-      <c r="AB50" s="24"/>
-      <c r="AC50" s="24"/>
-      <c r="AD50" s="25"/>
-    </row>
-    <row r="51" spans="1:30" ht="9" customHeight="1">
-      <c r="A51" s="30"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="24"/>
-      <c r="R51" s="24"/>
-      <c r="S51" s="24"/>
-      <c r="T51" s="24"/>
-      <c r="U51" s="24"/>
-      <c r="V51" s="24"/>
-      <c r="W51" s="24"/>
-      <c r="X51" s="24"/>
-      <c r="Y51" s="24"/>
-      <c r="Z51" s="24"/>
-      <c r="AA51" s="24"/>
-      <c r="AB51" s="24"/>
-      <c r="AC51" s="24"/>
-      <c r="AD51" s="25"/>
-    </row>
-    <row r="52" spans="1:30" ht="9" customHeight="1">
-      <c r="A52" s="28">
-        <v>2013</v>
-      </c>
-      <c r="B52" s="31">
-        <v>11</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
-      <c r="R52" s="24"/>
-      <c r="S52" s="24"/>
-      <c r="T52" s="24"/>
-      <c r="U52" s="24"/>
-      <c r="V52" s="24"/>
-      <c r="W52" s="24"/>
-      <c r="X52" s="24"/>
-      <c r="Y52" s="24"/>
-      <c r="Z52" s="24"/>
-      <c r="AA52" s="24"/>
-      <c r="AB52" s="24"/>
-      <c r="AC52" s="24"/>
-      <c r="AD52" s="25"/>
-    </row>
-    <row r="53" spans="1:30" ht="9" customHeight="1">
-      <c r="A53" s="29"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="24"/>
-      <c r="R53" s="24"/>
-      <c r="S53" s="24"/>
-      <c r="T53" s="24"/>
-      <c r="U53" s="24"/>
-      <c r="V53" s="24"/>
-      <c r="W53" s="24"/>
-      <c r="X53" s="24"/>
-      <c r="Y53" s="24"/>
-      <c r="Z53" s="24"/>
-      <c r="AA53" s="24"/>
-      <c r="AB53" s="24"/>
-      <c r="AC53" s="24"/>
-      <c r="AD53" s="25"/>
-    </row>
-    <row r="54" spans="1:30" ht="9" customHeight="1">
-      <c r="A54" s="30"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="42"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="23" t="s">
+      <c r="C82" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="24"/>
-      <c r="R54" s="24"/>
-      <c r="S54" s="24"/>
-      <c r="T54" s="24"/>
-      <c r="U54" s="24"/>
-      <c r="V54" s="24"/>
-      <c r="W54" s="24"/>
-      <c r="X54" s="24"/>
-      <c r="Y54" s="24"/>
-      <c r="Z54" s="24"/>
-      <c r="AA54" s="24"/>
-      <c r="AB54" s="24"/>
-      <c r="AC54" s="24"/>
-      <c r="AD54" s="25"/>
-    </row>
-    <row r="55" spans="1:30" ht="9" customHeight="1">
-      <c r="A55" s="28">
-        <v>2014</v>
-      </c>
-      <c r="B55" s="31">
-        <v>3</v>
-      </c>
-      <c r="C55" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="24"/>
-      <c r="R55" s="24"/>
-      <c r="S55" s="24"/>
-      <c r="T55" s="24"/>
-      <c r="U55" s="24"/>
-      <c r="V55" s="24"/>
-      <c r="W55" s="24"/>
-      <c r="X55" s="24"/>
-      <c r="Y55" s="24"/>
-      <c r="Z55" s="24"/>
-      <c r="AA55" s="24"/>
-      <c r="AB55" s="24"/>
-      <c r="AC55" s="24"/>
-      <c r="AD55" s="25"/>
-    </row>
-    <row r="56" spans="1:30" ht="9" customHeight="1">
-      <c r="A56" s="29"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="23"/>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="24"/>
-      <c r="R56" s="24"/>
-      <c r="S56" s="24"/>
-      <c r="T56" s="24"/>
-      <c r="U56" s="24"/>
-      <c r="V56" s="24"/>
-      <c r="W56" s="24"/>
-      <c r="X56" s="24"/>
-      <c r="Y56" s="24"/>
-      <c r="Z56" s="24"/>
-      <c r="AA56" s="24"/>
-      <c r="AB56" s="24"/>
-      <c r="AC56" s="24"/>
-      <c r="AD56" s="25"/>
-    </row>
-    <row r="57" spans="1:30" ht="9" customHeight="1">
-      <c r="A57" s="30"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="24"/>
-      <c r="R57" s="24"/>
-      <c r="S57" s="24"/>
-      <c r="T57" s="24"/>
-      <c r="U57" s="24"/>
-      <c r="V57" s="24"/>
-      <c r="W57" s="24"/>
-      <c r="X57" s="24"/>
-      <c r="Y57" s="24"/>
-      <c r="Z57" s="24"/>
-      <c r="AA57" s="24"/>
-      <c r="AB57" s="24"/>
-      <c r="AC57" s="24"/>
-      <c r="AD57" s="25"/>
-    </row>
-    <row r="58" spans="1:30" ht="9" customHeight="1">
-      <c r="A58" s="28">
-        <v>2014</v>
-      </c>
-      <c r="B58" s="31">
-        <v>4</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="36"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="23"/>
-      <c r="P58" s="24"/>
-      <c r="Q58" s="24"/>
-      <c r="R58" s="24"/>
-      <c r="S58" s="24"/>
-      <c r="T58" s="24"/>
-      <c r="U58" s="24"/>
-      <c r="V58" s="24"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="24"/>
-      <c r="Y58" s="24"/>
-      <c r="Z58" s="24"/>
-      <c r="AA58" s="24"/>
-      <c r="AB58" s="24"/>
-      <c r="AC58" s="24"/>
-      <c r="AD58" s="25"/>
-    </row>
-    <row r="59" spans="1:30" ht="9" customHeight="1">
-      <c r="A59" s="29"/>
-      <c r="B59" s="32"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="23"/>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="24"/>
-      <c r="R59" s="24"/>
-      <c r="S59" s="24"/>
-      <c r="T59" s="24"/>
-      <c r="U59" s="24"/>
-      <c r="V59" s="24"/>
-      <c r="W59" s="24"/>
-      <c r="X59" s="24"/>
-      <c r="Y59" s="24"/>
-      <c r="Z59" s="24"/>
-      <c r="AA59" s="24"/>
-      <c r="AB59" s="24"/>
-      <c r="AC59" s="24"/>
-      <c r="AD59" s="25"/>
-    </row>
-    <row r="60" spans="1:30" ht="9" customHeight="1">
-      <c r="A60" s="30"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="42"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P60" s="24"/>
-      <c r="Q60" s="24"/>
-      <c r="R60" s="24"/>
-      <c r="S60" s="24"/>
-      <c r="T60" s="24"/>
-      <c r="U60" s="24"/>
-      <c r="V60" s="24"/>
-      <c r="W60" s="24"/>
-      <c r="X60" s="24"/>
-      <c r="Y60" s="24"/>
-      <c r="Z60" s="24"/>
-      <c r="AA60" s="24"/>
-      <c r="AB60" s="24"/>
-      <c r="AC60" s="24"/>
-      <c r="AD60" s="25"/>
-    </row>
-    <row r="61" spans="1:30" ht="9" customHeight="1">
-      <c r="A61" s="28">
-        <v>2017</v>
-      </c>
-      <c r="B61" s="31">
-        <v>3</v>
-      </c>
-      <c r="C61" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="36"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
-      <c r="R61" s="24"/>
-      <c r="S61" s="24"/>
-      <c r="T61" s="24"/>
-      <c r="U61" s="24"/>
-      <c r="V61" s="24"/>
-      <c r="W61" s="24"/>
-      <c r="X61" s="24"/>
-      <c r="Y61" s="24"/>
-      <c r="Z61" s="24"/>
-      <c r="AA61" s="24"/>
-      <c r="AB61" s="24"/>
-      <c r="AC61" s="24"/>
-      <c r="AD61" s="25"/>
-    </row>
-    <row r="62" spans="1:30" ht="9" customHeight="1">
-      <c r="A62" s="29"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="23"/>
-      <c r="P62" s="24"/>
-      <c r="Q62" s="24"/>
-      <c r="R62" s="24"/>
-      <c r="S62" s="24"/>
-      <c r="T62" s="24"/>
-      <c r="U62" s="24"/>
-      <c r="V62" s="24"/>
-      <c r="W62" s="24"/>
-      <c r="X62" s="24"/>
-      <c r="Y62" s="24"/>
-      <c r="Z62" s="24"/>
-      <c r="AA62" s="24"/>
-      <c r="AB62" s="24"/>
-      <c r="AC62" s="24"/>
-      <c r="AD62" s="25"/>
-    </row>
-    <row r="63" spans="1:30" ht="9" customHeight="1">
-      <c r="A63" s="30"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="42"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="P63" s="24"/>
-      <c r="Q63" s="24"/>
-      <c r="R63" s="24"/>
-      <c r="S63" s="24"/>
-      <c r="T63" s="24"/>
-      <c r="U63" s="24"/>
-      <c r="V63" s="24"/>
-      <c r="W63" s="24"/>
-      <c r="X63" s="24"/>
-      <c r="Y63" s="24"/>
-      <c r="Z63" s="24"/>
-      <c r="AA63" s="24"/>
-      <c r="AB63" s="24"/>
-      <c r="AC63" s="24"/>
-      <c r="AD63" s="25"/>
-    </row>
-    <row r="64" spans="1:30" ht="9" customHeight="1">
-      <c r="A64" s="28">
-        <v>2017</v>
-      </c>
-      <c r="B64" s="31">
-        <v>6</v>
-      </c>
-      <c r="C64" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-      <c r="L64" s="36"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="24"/>
-      <c r="Q64" s="24"/>
-      <c r="R64" s="24"/>
-      <c r="S64" s="24"/>
-      <c r="T64" s="24"/>
-      <c r="U64" s="24"/>
-      <c r="V64" s="24"/>
-      <c r="W64" s="24"/>
-      <c r="X64" s="24"/>
-      <c r="Y64" s="24"/>
-      <c r="Z64" s="24"/>
-      <c r="AA64" s="24"/>
-      <c r="AB64" s="24"/>
-      <c r="AC64" s="24"/>
-      <c r="AD64" s="25"/>
-    </row>
-    <row r="65" spans="1:30" ht="9" customHeight="1">
-      <c r="A65" s="29"/>
-      <c r="B65" s="32"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="23"/>
-      <c r="P65" s="24"/>
-      <c r="Q65" s="24"/>
-      <c r="R65" s="24"/>
-      <c r="S65" s="24"/>
-      <c r="T65" s="24"/>
-      <c r="U65" s="24"/>
-      <c r="V65" s="24"/>
-      <c r="W65" s="24"/>
-      <c r="X65" s="24"/>
-      <c r="Y65" s="24"/>
-      <c r="Z65" s="24"/>
-      <c r="AA65" s="24"/>
-      <c r="AB65" s="24"/>
-      <c r="AC65" s="24"/>
-      <c r="AD65" s="25"/>
-    </row>
-    <row r="66" spans="1:30" ht="9" customHeight="1">
-      <c r="A66" s="30"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="42"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="20"/>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
-      <c r="S66" s="16"/>
-      <c r="T66" s="16"/>
-      <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
-      <c r="W66" s="16"/>
-      <c r="X66" s="16"/>
-      <c r="Y66" s="16"/>
-      <c r="Z66" s="16"/>
-      <c r="AA66" s="16"/>
-      <c r="AB66" s="16"/>
-      <c r="AC66" s="16"/>
-      <c r="AD66" s="21"/>
-    </row>
-    <row r="67" spans="1:30" ht="9" customHeight="1">
-      <c r="A67" s="28">
-        <v>2019</v>
-      </c>
-      <c r="B67" s="31">
-        <v>4</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
-      <c r="L67" s="36"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="2"/>
-      <c r="AA67" s="2"/>
-      <c r="AB67" s="2"/>
-      <c r="AC67" s="2"/>
-      <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="1:30" ht="9" customHeight="1">
-      <c r="A68" s="29"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
-      <c r="L68" s="39"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="62" t="s">
-        <v>11</v>
-      </c>
-      <c r="P68" s="50"/>
-      <c r="Q68" s="50"/>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50"/>
-      <c r="T68" s="50"/>
-      <c r="U68" s="50"/>
-      <c r="V68" s="50"/>
-      <c r="W68" s="50"/>
-      <c r="X68" s="50"/>
-      <c r="Y68" s="50"/>
-      <c r="Z68" s="50"/>
-      <c r="AA68" s="50"/>
-      <c r="AB68" s="50"/>
-      <c r="AC68" s="50"/>
-      <c r="AD68" s="51"/>
-    </row>
-    <row r="69" spans="1:30" ht="9" customHeight="1">
-      <c r="A69" s="30"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="42"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="52"/>
-      <c r="P69" s="38"/>
-      <c r="Q69" s="38"/>
-      <c r="R69" s="38"/>
-      <c r="S69" s="38"/>
-      <c r="T69" s="38"/>
-      <c r="U69" s="38"/>
-      <c r="V69" s="38"/>
-      <c r="W69" s="38"/>
-      <c r="X69" s="38"/>
-      <c r="Y69" s="38"/>
-      <c r="Z69" s="38"/>
-      <c r="AA69" s="38"/>
-      <c r="AB69" s="38"/>
-      <c r="AC69" s="38"/>
-      <c r="AD69" s="39"/>
-    </row>
-    <row r="70" spans="1:30" ht="9" customHeight="1">
-      <c r="A70" s="28">
-        <v>2019</v>
-      </c>
-      <c r="B70" s="31">
-        <v>10</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
-      <c r="L70" s="36"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="52"/>
-      <c r="P70" s="38"/>
-      <c r="Q70" s="38"/>
-      <c r="R70" s="38"/>
-      <c r="S70" s="38"/>
-      <c r="T70" s="38"/>
-      <c r="U70" s="38"/>
-      <c r="V70" s="38"/>
-      <c r="W70" s="38"/>
-      <c r="X70" s="38"/>
-      <c r="Y70" s="38"/>
-      <c r="Z70" s="38"/>
-      <c r="AA70" s="38"/>
-      <c r="AB70" s="38"/>
-      <c r="AC70" s="38"/>
-      <c r="AD70" s="39"/>
-    </row>
-    <row r="71" spans="1:30" ht="9" customHeight="1">
-      <c r="A71" s="29"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P71" s="13"/>
-      <c r="Q71" s="13"/>
-      <c r="R71" s="13"/>
-      <c r="S71" s="13"/>
-      <c r="T71" s="13"/>
-      <c r="U71" s="13"/>
-      <c r="V71" s="13"/>
-      <c r="W71" s="13"/>
-      <c r="X71" s="13"/>
-      <c r="Y71" s="13"/>
-      <c r="Z71" s="13"/>
-      <c r="AA71" s="13"/>
-      <c r="AB71" s="13"/>
-      <c r="AC71" s="13"/>
-      <c r="AD71" s="14"/>
-    </row>
-    <row r="72" spans="1:30" ht="9" customHeight="1">
-      <c r="A72" s="30"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
-      <c r="L72" s="42"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="P72" s="24"/>
-      <c r="Q72" s="24"/>
-      <c r="R72" s="24"/>
-      <c r="S72" s="24"/>
-      <c r="T72" s="24"/>
-      <c r="U72" s="24"/>
-      <c r="V72" s="24"/>
-      <c r="W72" s="24"/>
-      <c r="X72" s="24"/>
-      <c r="Y72" s="24"/>
-      <c r="Z72" s="24"/>
-      <c r="AA72" s="24"/>
-      <c r="AB72" s="24"/>
-      <c r="AC72" s="24"/>
-      <c r="AD72" s="27"/>
-    </row>
-    <row r="73" spans="1:30" ht="9" customHeight="1">
-      <c r="A73" s="28">
-        <v>2021</v>
-      </c>
-      <c r="B73" s="31">
-        <v>3</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-      <c r="K73" s="35"/>
-      <c r="L73" s="36"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="26"/>
-      <c r="P73" s="24"/>
-      <c r="Q73" s="24"/>
-      <c r="R73" s="24"/>
-      <c r="S73" s="24"/>
-      <c r="T73" s="24"/>
-      <c r="U73" s="24"/>
-      <c r="V73" s="24"/>
-      <c r="W73" s="24"/>
-      <c r="X73" s="24"/>
-      <c r="Y73" s="24"/>
-      <c r="Z73" s="24"/>
-      <c r="AA73" s="24"/>
-      <c r="AB73" s="24"/>
-      <c r="AC73" s="24"/>
-      <c r="AD73" s="27"/>
-    </row>
-    <row r="74" spans="1:30" ht="9" customHeight="1">
-      <c r="A74" s="29"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="26"/>
-      <c r="P74" s="24"/>
-      <c r="Q74" s="24"/>
-      <c r="R74" s="24"/>
-      <c r="S74" s="24"/>
-      <c r="T74" s="24"/>
-      <c r="U74" s="24"/>
-      <c r="V74" s="24"/>
-      <c r="W74" s="24"/>
-      <c r="X74" s="24"/>
-      <c r="Y74" s="24"/>
-      <c r="Z74" s="24"/>
-      <c r="AA74" s="24"/>
-      <c r="AB74" s="24"/>
-      <c r="AC74" s="24"/>
-      <c r="AD74" s="27"/>
-    </row>
-    <row r="75" spans="1:30" ht="9" customHeight="1">
-      <c r="A75" s="30"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="41"/>
-      <c r="K75" s="41"/>
-      <c r="L75" s="42"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="12"/>
-      <c r="AD75" s="9"/>
-    </row>
-    <row r="76" spans="1:30" ht="9" customHeight="1">
-      <c r="A76" s="28">
-        <v>2021</v>
-      </c>
-      <c r="B76" s="31">
-        <v>4</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="36"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="12"/>
-      <c r="AD76" s="9"/>
-    </row>
-    <row r="77" spans="1:30" ht="9" customHeight="1">
-      <c r="A77" s="29"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="12"/>
-      <c r="AD77" s="9"/>
-    </row>
-    <row r="78" spans="1:30" ht="9" customHeight="1">
-      <c r="A78" s="30"/>
-      <c r="B78" s="33"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="41"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41"/>
-      <c r="J78" s="41"/>
-      <c r="K78" s="41"/>
-      <c r="L78" s="42"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="12"/>
-      <c r="AD78" s="9"/>
-    </row>
-    <row r="79" spans="1:30" ht="9" customHeight="1">
-      <c r="A79" s="28">
-        <v>2022</v>
-      </c>
-      <c r="B79" s="31">
-        <v>4</v>
-      </c>
-      <c r="C79" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
-      <c r="L79" s="36"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="15"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
-      <c r="V79" s="10"/>
-      <c r="W79" s="10"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="10"/>
-      <c r="Z79" s="10"/>
-      <c r="AA79" s="10"/>
-      <c r="AB79" s="10"/>
-      <c r="AC79" s="10"/>
-      <c r="AD79" s="11"/>
-    </row>
-    <row r="80" spans="1:30" ht="9" customHeight="1">
-      <c r="A80" s="29"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="8"/>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
-      <c r="AC80" s="8"/>
-      <c r="AD80" s="8"/>
-    </row>
-    <row r="81" spans="1:30" ht="9" customHeight="1">
-      <c r="A81" s="30"/>
-      <c r="B81" s="33"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="41"/>
-      <c r="J81" s="41"/>
-      <c r="K81" s="41"/>
-      <c r="L81" s="42"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-      <c r="Q81" s="3"/>
-      <c r="R81" s="3"/>
-      <c r="S81" s="3"/>
-      <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="3"/>
-      <c r="AA81" s="3"/>
-      <c r="AB81" s="3"/>
-      <c r="AC81" s="3"/>
-      <c r="AD81" s="3"/>
-    </row>
-    <row r="82" spans="1:30" ht="9" customHeight="1">
-      <c r="A82" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B82" s="79" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="50"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
+      <c r="L82" s="30"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="3"/>
-      <c r="P82" s="3"/>
-      <c r="Q82" s="3"/>
-      <c r="R82" s="3"/>
-      <c r="S82" s="3"/>
-      <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="3"/>
-      <c r="AA82" s="3"/>
-      <c r="AB82" s="3"/>
-      <c r="AC82" s="3"/>
-      <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="1:30" ht="9" customHeight="1">
-      <c r="A83" s="38"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
-      <c r="L83" s="38"/>
+      <c r="O82" s="19"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="20"/>
+      <c r="V82" s="20"/>
+      <c r="W82" s="20"/>
+      <c r="X82" s="20"/>
+      <c r="Y82" s="20"/>
+      <c r="Z82" s="20"/>
+      <c r="AA82" s="20"/>
+      <c r="AB82" s="20"/>
+      <c r="AC82" s="20"/>
+      <c r="AD82" s="21"/>
+    </row>
+    <row r="83" spans="1:30" ht="14">
+      <c r="A83" s="36"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
+      <c r="L83" s="21"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-      <c r="Q83" s="3"/>
-      <c r="R83" s="3"/>
-      <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="3"/>
-      <c r="AA83" s="3"/>
-      <c r="AB83" s="3"/>
-      <c r="AC83" s="3"/>
-      <c r="AD83" s="3"/>
-    </row>
-    <row r="84" spans="1:30" ht="9" customHeight="1">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
+      <c r="O83" s="19"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20"/>
+      <c r="U83" s="20"/>
+      <c r="V83" s="20"/>
+      <c r="W83" s="20"/>
+      <c r="X83" s="20"/>
+      <c r="Y83" s="20"/>
+      <c r="Z83" s="20"/>
+      <c r="AA83" s="20"/>
+      <c r="AB83" s="20"/>
+      <c r="AC83" s="20"/>
+      <c r="AD83" s="21"/>
+    </row>
+    <row r="84" spans="1:30" ht="14">
+      <c r="A84" s="37"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="33"/>
+      <c r="G84" s="33"/>
+      <c r="H84" s="33"/>
+      <c r="I84" s="33"/>
+      <c r="J84" s="33"/>
+      <c r="K84" s="33"/>
+      <c r="L84" s="34"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-      <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
-      <c r="R84" s="3"/>
-      <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3"/>
-      <c r="AA84" s="3"/>
-      <c r="AB84" s="3"/>
-      <c r="AC84" s="3"/>
-      <c r="AD84" s="3"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="20"/>
+      <c r="V84" s="20"/>
+      <c r="W84" s="20"/>
+      <c r="X84" s="20"/>
+      <c r="Y84" s="20"/>
+      <c r="Z84" s="20"/>
+      <c r="AA84" s="20"/>
+      <c r="AB84" s="20"/>
+      <c r="AC84" s="20"/>
+      <c r="AD84" s="21"/>
     </row>
     <row r="85" spans="1:30" ht="9" customHeight="1">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
+      <c r="A85" s="66"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="40"/>
+      <c r="K85" s="40"/>
+      <c r="L85" s="40"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3"/>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="3"/>
-      <c r="AA85" s="3"/>
-      <c r="AB85" s="3"/>
-      <c r="AC85" s="3"/>
-      <c r="AD85" s="3"/>
+      <c r="O85" s="22"/>
+      <c r="P85" s="23"/>
+      <c r="Q85" s="23"/>
+      <c r="R85" s="23"/>
+      <c r="S85" s="23"/>
+      <c r="T85" s="23"/>
+      <c r="U85" s="23"/>
+      <c r="V85" s="23"/>
+      <c r="W85" s="23"/>
+      <c r="X85" s="23"/>
+      <c r="Y85" s="23"/>
+      <c r="Z85" s="23"/>
+      <c r="AA85" s="23"/>
+      <c r="AB85" s="23"/>
+      <c r="AC85" s="23"/>
+      <c r="AD85" s="24"/>
     </row>
     <row r="86" spans="1:30" ht="9" customHeight="1">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
@@ -5167,7 +4665,7 @@
       <c r="AC87" s="3"/>
       <c r="AD87" s="3"/>
     </row>
-    <row r="88" spans="1:30" ht="9" customHeight="1">
+    <row r="88" spans="1:30" ht="27.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -5199,7 +4697,7 @@
       <c r="AC88" s="3"/>
       <c r="AD88" s="3"/>
     </row>
-    <row r="89" spans="1:30" ht="9" customHeight="1">
+    <row r="89" spans="1:30" ht="12.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -5231,7 +4729,7 @@
       <c r="AC89" s="3"/>
       <c r="AD89" s="3"/>
     </row>
-    <row r="90" spans="1:30" ht="9" customHeight="1">
+    <row r="90" spans="1:30" ht="12.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -5263,7 +4761,7 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
     </row>
-    <row r="91" spans="1:30" ht="27.75" customHeight="1">
+    <row r="91" spans="1:30" ht="12.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -33662,22 +33160,6 @@
       <c r="L978" s="3"/>
       <c r="M978" s="3"/>
       <c r="N978" s="3"/>
-      <c r="O978" s="3"/>
-      <c r="P978" s="3"/>
-      <c r="Q978" s="3"/>
-      <c r="R978" s="3"/>
-      <c r="S978" s="3"/>
-      <c r="T978" s="3"/>
-      <c r="U978" s="3"/>
-      <c r="V978" s="3"/>
-      <c r="W978" s="3"/>
-      <c r="X978" s="3"/>
-      <c r="Y978" s="3"/>
-      <c r="Z978" s="3"/>
-      <c r="AA978" s="3"/>
-      <c r="AB978" s="3"/>
-      <c r="AC978" s="3"/>
-      <c r="AD978" s="3"/>
     </row>
     <row r="979" spans="1:30" ht="12.75" customHeight="1">
       <c r="A979" s="3"/>
@@ -33694,22 +33176,6 @@
       <c r="L979" s="3"/>
       <c r="M979" s="3"/>
       <c r="N979" s="3"/>
-      <c r="O979" s="3"/>
-      <c r="P979" s="3"/>
-      <c r="Q979" s="3"/>
-      <c r="R979" s="3"/>
-      <c r="S979" s="3"/>
-      <c r="T979" s="3"/>
-      <c r="U979" s="3"/>
-      <c r="V979" s="3"/>
-      <c r="W979" s="3"/>
-      <c r="X979" s="3"/>
-      <c r="Y979" s="3"/>
-      <c r="Z979" s="3"/>
-      <c r="AA979" s="3"/>
-      <c r="AB979" s="3"/>
-      <c r="AC979" s="3"/>
-      <c r="AD979" s="3"/>
     </row>
     <row r="980" spans="1:30" ht="12.75" customHeight="1">
       <c r="A980" s="3"/>
@@ -33726,22 +33192,6 @@
       <c r="L980" s="3"/>
       <c r="M980" s="3"/>
       <c r="N980" s="3"/>
-      <c r="O980" s="3"/>
-      <c r="P980" s="3"/>
-      <c r="Q980" s="3"/>
-      <c r="R980" s="3"/>
-      <c r="S980" s="3"/>
-      <c r="T980" s="3"/>
-      <c r="U980" s="3"/>
-      <c r="V980" s="3"/>
-      <c r="W980" s="3"/>
-      <c r="X980" s="3"/>
-      <c r="Y980" s="3"/>
-      <c r="Z980" s="3"/>
-      <c r="AA980" s="3"/>
-      <c r="AB980" s="3"/>
-      <c r="AC980" s="3"/>
-      <c r="AD980" s="3"/>
     </row>
     <row r="981" spans="1:30" ht="12.75" customHeight="1">
       <c r="A981" s="3"/>
@@ -33758,22 +33208,6 @@
       <c r="L981" s="3"/>
       <c r="M981" s="3"/>
       <c r="N981" s="3"/>
-      <c r="O981" s="3"/>
-      <c r="P981" s="3"/>
-      <c r="Q981" s="3"/>
-      <c r="R981" s="3"/>
-      <c r="S981" s="3"/>
-      <c r="T981" s="3"/>
-      <c r="U981" s="3"/>
-      <c r="V981" s="3"/>
-      <c r="W981" s="3"/>
-      <c r="X981" s="3"/>
-      <c r="Y981" s="3"/>
-      <c r="Z981" s="3"/>
-      <c r="AA981" s="3"/>
-      <c r="AB981" s="3"/>
-      <c r="AC981" s="3"/>
-      <c r="AD981" s="3"/>
     </row>
     <row r="982" spans="1:30" ht="12.75" customHeight="1">
       <c r="A982" s="3"/>
@@ -33790,22 +33224,6 @@
       <c r="L982" s="3"/>
       <c r="M982" s="3"/>
       <c r="N982" s="3"/>
-      <c r="O982" s="3"/>
-      <c r="P982" s="3"/>
-      <c r="Q982" s="3"/>
-      <c r="R982" s="3"/>
-      <c r="S982" s="3"/>
-      <c r="T982" s="3"/>
-      <c r="U982" s="3"/>
-      <c r="V982" s="3"/>
-      <c r="W982" s="3"/>
-      <c r="X982" s="3"/>
-      <c r="Y982" s="3"/>
-      <c r="Z982" s="3"/>
-      <c r="AA982" s="3"/>
-      <c r="AB982" s="3"/>
-      <c r="AC982" s="3"/>
-      <c r="AD982" s="3"/>
     </row>
     <row r="983" spans="1:30" ht="12.75" customHeight="1">
       <c r="A983" s="3"/>
@@ -33822,22 +33240,6 @@
       <c r="L983" s="3"/>
       <c r="M983" s="3"/>
       <c r="N983" s="3"/>
-      <c r="O983" s="3"/>
-      <c r="P983" s="3"/>
-      <c r="Q983" s="3"/>
-      <c r="R983" s="3"/>
-      <c r="S983" s="3"/>
-      <c r="T983" s="3"/>
-      <c r="U983" s="3"/>
-      <c r="V983" s="3"/>
-      <c r="W983" s="3"/>
-      <c r="X983" s="3"/>
-      <c r="Y983" s="3"/>
-      <c r="Z983" s="3"/>
-      <c r="AA983" s="3"/>
-      <c r="AB983" s="3"/>
-      <c r="AC983" s="3"/>
-      <c r="AD983" s="3"/>
     </row>
     <row r="984" spans="1:30" ht="12.75" customHeight="1">
       <c r="A984" s="3"/>
@@ -33854,22 +33256,6 @@
       <c r="L984" s="3"/>
       <c r="M984" s="3"/>
       <c r="N984" s="3"/>
-      <c r="O984" s="3"/>
-      <c r="P984" s="3"/>
-      <c r="Q984" s="3"/>
-      <c r="R984" s="3"/>
-      <c r="S984" s="3"/>
-      <c r="T984" s="3"/>
-      <c r="U984" s="3"/>
-      <c r="V984" s="3"/>
-      <c r="W984" s="3"/>
-      <c r="X984" s="3"/>
-      <c r="Y984" s="3"/>
-      <c r="Z984" s="3"/>
-      <c r="AA984" s="3"/>
-      <c r="AB984" s="3"/>
-      <c r="AC984" s="3"/>
-      <c r="AD984" s="3"/>
     </row>
     <row r="985" spans="1:30" ht="12.75" customHeight="1">
       <c r="A985" s="3"/>
@@ -33886,22 +33272,6 @@
       <c r="L985" s="3"/>
       <c r="M985" s="3"/>
       <c r="N985" s="3"/>
-      <c r="O985" s="3"/>
-      <c r="P985" s="3"/>
-      <c r="Q985" s="3"/>
-      <c r="R985" s="3"/>
-      <c r="S985" s="3"/>
-      <c r="T985" s="3"/>
-      <c r="U985" s="3"/>
-      <c r="V985" s="3"/>
-      <c r="W985" s="3"/>
-      <c r="X985" s="3"/>
-      <c r="Y985" s="3"/>
-      <c r="Z985" s="3"/>
-      <c r="AA985" s="3"/>
-      <c r="AB985" s="3"/>
-      <c r="AC985" s="3"/>
-      <c r="AD985" s="3"/>
     </row>
     <row r="986" spans="1:30" ht="12.75" customHeight="1">
       <c r="A986" s="3"/>
@@ -33918,22 +33288,6 @@
       <c r="L986" s="3"/>
       <c r="M986" s="3"/>
       <c r="N986" s="3"/>
-      <c r="O986" s="3"/>
-      <c r="P986" s="3"/>
-      <c r="Q986" s="3"/>
-      <c r="R986" s="3"/>
-      <c r="S986" s="3"/>
-      <c r="T986" s="3"/>
-      <c r="U986" s="3"/>
-      <c r="V986" s="3"/>
-      <c r="W986" s="3"/>
-      <c r="X986" s="3"/>
-      <c r="Y986" s="3"/>
-      <c r="Z986" s="3"/>
-      <c r="AA986" s="3"/>
-      <c r="AB986" s="3"/>
-      <c r="AC986" s="3"/>
-      <c r="AD986" s="3"/>
     </row>
     <row r="987" spans="1:30" ht="12.75" customHeight="1">
       <c r="A987" s="3"/>
@@ -33950,22 +33304,6 @@
       <c r="L987" s="3"/>
       <c r="M987" s="3"/>
       <c r="N987" s="3"/>
-      <c r="O987" s="3"/>
-      <c r="P987" s="3"/>
-      <c r="Q987" s="3"/>
-      <c r="R987" s="3"/>
-      <c r="S987" s="3"/>
-      <c r="T987" s="3"/>
-      <c r="U987" s="3"/>
-      <c r="V987" s="3"/>
-      <c r="W987" s="3"/>
-      <c r="X987" s="3"/>
-      <c r="Y987" s="3"/>
-      <c r="Z987" s="3"/>
-      <c r="AA987" s="3"/>
-      <c r="AB987" s="3"/>
-      <c r="AC987" s="3"/>
-      <c r="AD987" s="3"/>
     </row>
     <row r="988" spans="1:30" ht="12.75" customHeight="1">
       <c r="A988" s="3"/>
@@ -33982,22 +33320,6 @@
       <c r="L988" s="3"/>
       <c r="M988" s="3"/>
       <c r="N988" s="3"/>
-      <c r="O988" s="3"/>
-      <c r="P988" s="3"/>
-      <c r="Q988" s="3"/>
-      <c r="R988" s="3"/>
-      <c r="S988" s="3"/>
-      <c r="T988" s="3"/>
-      <c r="U988" s="3"/>
-      <c r="V988" s="3"/>
-      <c r="W988" s="3"/>
-      <c r="X988" s="3"/>
-      <c r="Y988" s="3"/>
-      <c r="Z988" s="3"/>
-      <c r="AA988" s="3"/>
-      <c r="AB988" s="3"/>
-      <c r="AC988" s="3"/>
-      <c r="AD988" s="3"/>
     </row>
     <row r="989" spans="1:30" ht="12.75" customHeight="1">
       <c r="A989" s="3"/>
@@ -34014,22 +33336,6 @@
       <c r="L989" s="3"/>
       <c r="M989" s="3"/>
       <c r="N989" s="3"/>
-      <c r="O989" s="3"/>
-      <c r="P989" s="3"/>
-      <c r="Q989" s="3"/>
-      <c r="R989" s="3"/>
-      <c r="S989" s="3"/>
-      <c r="T989" s="3"/>
-      <c r="U989" s="3"/>
-      <c r="V989" s="3"/>
-      <c r="W989" s="3"/>
-      <c r="X989" s="3"/>
-      <c r="Y989" s="3"/>
-      <c r="Z989" s="3"/>
-      <c r="AA989" s="3"/>
-      <c r="AB989" s="3"/>
-      <c r="AC989" s="3"/>
-      <c r="AD989" s="3"/>
     </row>
     <row r="990" spans="1:30" ht="12.75" customHeight="1">
       <c r="A990" s="3"/>
@@ -34046,22 +33352,6 @@
       <c r="L990" s="3"/>
       <c r="M990" s="3"/>
       <c r="N990" s="3"/>
-      <c r="O990" s="3"/>
-      <c r="P990" s="3"/>
-      <c r="Q990" s="3"/>
-      <c r="R990" s="3"/>
-      <c r="S990" s="3"/>
-      <c r="T990" s="3"/>
-      <c r="U990" s="3"/>
-      <c r="V990" s="3"/>
-      <c r="W990" s="3"/>
-      <c r="X990" s="3"/>
-      <c r="Y990" s="3"/>
-      <c r="Z990" s="3"/>
-      <c r="AA990" s="3"/>
-      <c r="AB990" s="3"/>
-      <c r="AC990" s="3"/>
-      <c r="AD990" s="3"/>
     </row>
     <row r="991" spans="1:30" ht="12.75" customHeight="1">
       <c r="A991" s="3"/>
@@ -34078,22 +33368,6 @@
       <c r="L991" s="3"/>
       <c r="M991" s="3"/>
       <c r="N991" s="3"/>
-      <c r="O991" s="3"/>
-      <c r="P991" s="3"/>
-      <c r="Q991" s="3"/>
-      <c r="R991" s="3"/>
-      <c r="S991" s="3"/>
-      <c r="T991" s="3"/>
-      <c r="U991" s="3"/>
-      <c r="V991" s="3"/>
-      <c r="W991" s="3"/>
-      <c r="X991" s="3"/>
-      <c r="Y991" s="3"/>
-      <c r="Z991" s="3"/>
-      <c r="AA991" s="3"/>
-      <c r="AB991" s="3"/>
-      <c r="AC991" s="3"/>
-      <c r="AD991" s="3"/>
     </row>
     <row r="992" spans="1:30" ht="12.75" customHeight="1">
       <c r="A992" s="3"/>
@@ -34110,24 +33384,8 @@
       <c r="L992" s="3"/>
       <c r="M992" s="3"/>
       <c r="N992" s="3"/>
-      <c r="O992" s="3"/>
-      <c r="P992" s="3"/>
-      <c r="Q992" s="3"/>
-      <c r="R992" s="3"/>
-      <c r="S992" s="3"/>
-      <c r="T992" s="3"/>
-      <c r="U992" s="3"/>
-      <c r="V992" s="3"/>
-      <c r="W992" s="3"/>
-      <c r="X992" s="3"/>
-      <c r="Y992" s="3"/>
-      <c r="Z992" s="3"/>
-      <c r="AA992" s="3"/>
-      <c r="AB992" s="3"/>
-      <c r="AC992" s="3"/>
-      <c r="AD992" s="3"/>
-    </row>
-    <row r="993" spans="1:30" ht="12.75" customHeight="1">
+    </row>
+    <row r="993" spans="1:14" ht="12.75" customHeight="1">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -34142,24 +33400,8 @@
       <c r="L993" s="3"/>
       <c r="M993" s="3"/>
       <c r="N993" s="3"/>
-      <c r="O993" s="3"/>
-      <c r="P993" s="3"/>
-      <c r="Q993" s="3"/>
-      <c r="R993" s="3"/>
-      <c r="S993" s="3"/>
-      <c r="T993" s="3"/>
-      <c r="U993" s="3"/>
-      <c r="V993" s="3"/>
-      <c r="W993" s="3"/>
-      <c r="X993" s="3"/>
-      <c r="Y993" s="3"/>
-      <c r="Z993" s="3"/>
-      <c r="AA993" s="3"/>
-      <c r="AB993" s="3"/>
-      <c r="AC993" s="3"/>
-      <c r="AD993" s="3"/>
-    </row>
-    <row r="994" spans="1:30" ht="12.75" customHeight="1">
+    </row>
+    <row r="994" spans="1:14" ht="12.75" customHeight="1">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -34175,7 +33417,7 @@
       <c r="M994" s="3"/>
       <c r="N994" s="3"/>
     </row>
-    <row r="995" spans="1:30" ht="12.75" customHeight="1">
+    <row r="995" spans="1:14" ht="12.75" customHeight="1">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -34191,40 +33433,89 @@
       <c r="M995" s="3"/>
       <c r="N995" s="3"/>
     </row>
-    <row r="996" spans="1:30" ht="12.75" customHeight="1">
+    <row r="996" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A996" s="3"/>
+      <c r="B996" s="3"/>
+      <c r="C996" s="3"/>
+      <c r="D996" s="3"/>
+      <c r="E996" s="3"/>
+      <c r="F996" s="3"/>
+      <c r="G996" s="3"/>
+      <c r="H996" s="3"/>
+      <c r="I996" s="3"/>
+      <c r="J996" s="3"/>
+      <c r="K996" s="3"/>
+      <c r="L996" s="3"/>
       <c r="M996" s="3"/>
       <c r="N996" s="3"/>
     </row>
-    <row r="997" spans="1:30" ht="12.75" customHeight="1">
+    <row r="997" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A997" s="3"/>
+      <c r="B997" s="3"/>
+      <c r="C997" s="3"/>
+      <c r="D997" s="3"/>
+      <c r="E997" s="3"/>
+      <c r="F997" s="3"/>
+      <c r="G997" s="3"/>
+      <c r="H997" s="3"/>
+      <c r="I997" s="3"/>
+      <c r="J997" s="3"/>
+      <c r="K997" s="3"/>
+      <c r="L997" s="3"/>
       <c r="M997" s="3"/>
       <c r="N997" s="3"/>
     </row>
-    <row r="998" spans="1:30" ht="12.75" customHeight="1">
+    <row r="998" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A998" s="3"/>
+      <c r="B998" s="3"/>
+      <c r="C998" s="3"/>
+      <c r="D998" s="3"/>
+      <c r="E998" s="3"/>
+      <c r="F998" s="3"/>
+      <c r="G998" s="3"/>
+      <c r="H998" s="3"/>
+      <c r="I998" s="3"/>
+      <c r="J998" s="3"/>
+      <c r="K998" s="3"/>
+      <c r="L998" s="3"/>
       <c r="M998" s="3"/>
       <c r="N998" s="3"/>
     </row>
-    <row r="999" spans="1:30" ht="12.75" customHeight="1">
+    <row r="999" spans="1:14" ht="12.75" customHeight="1">
       <c r="M999" s="3"/>
       <c r="N999" s="3"/>
     </row>
-    <row r="1000" spans="1:30" ht="12.75" customHeight="1">
+    <row r="1000" spans="1:14" ht="12.75" customHeight="1">
       <c r="M1000" s="3"/>
       <c r="N1000" s="3"/>
     </row>
-    <row r="1001" spans="1:30" ht="12.75" customHeight="1">
-      <c r="M1001" s="3"/>
-      <c r="N1001" s="3"/>
-    </row>
-    <row r="1002" spans="1:30" ht="12.75" customHeight="1">
-      <c r="M1002" s="3"/>
-      <c r="N1002" s="3"/>
-    </row>
-    <row r="1003" spans="1:30" ht="12.75" customHeight="1">
-      <c r="M1003" s="3"/>
-      <c r="N1003" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="106">
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:L60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:L63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:L66"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:L33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="P22:P24"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="B19:J20"/>
     <mergeCell ref="B21:J22"/>
     <mergeCell ref="B10:I15"/>
@@ -34234,36 +33525,19 @@
     <mergeCell ref="K19:L20"/>
     <mergeCell ref="B23:J26"/>
     <mergeCell ref="K25:L26"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:L39"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="C28:L30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:L36"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:L33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:L83"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="C70:L72"/>
+    <mergeCell ref="A82:A84"/>
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B75"/>
     <mergeCell ref="C73:L75"/>
-    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:L54"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:L42"/>
+    <mergeCell ref="A40:A42"/>
     <mergeCell ref="A76:A78"/>
+    <mergeCell ref="C76:L78"/>
     <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:L78"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:I9"/>
-    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="P1:P3"/>
@@ -34271,35 +33545,37 @@
     <mergeCell ref="F2:I3"/>
     <mergeCell ref="A4:C6"/>
     <mergeCell ref="F5:I6"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="O13:O15"/>
-    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:I9"/>
     <mergeCell ref="Q4:AD6"/>
     <mergeCell ref="Q7:AD9"/>
-    <mergeCell ref="O68:AD70"/>
     <mergeCell ref="O4:O6"/>
     <mergeCell ref="P4:P6"/>
     <mergeCell ref="O7:O9"/>
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q10:AD12"/>
-    <mergeCell ref="O57:AD59"/>
-    <mergeCell ref="O60:AD62"/>
-    <mergeCell ref="O63:AD65"/>
-    <mergeCell ref="O54:AD56"/>
-    <mergeCell ref="O51:AD53"/>
-    <mergeCell ref="O27:AD29"/>
-    <mergeCell ref="O39:AD41"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="C67:L69"/>
     <mergeCell ref="Q13:AD15"/>
     <mergeCell ref="Q16:AD18"/>
     <mergeCell ref="Q19:AD21"/>
-    <mergeCell ref="O23:AD25"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C79:L81"/>
+    <mergeCell ref="Q22:AD24"/>
+    <mergeCell ref="O26:AD28"/>
+    <mergeCell ref="O29:AD46"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:L39"/>
+    <mergeCell ref="C28:L30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:L36"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="O71:AD85"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:L84"/>
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="C49:L51"/>
     <mergeCell ref="A55:A57"/>
@@ -34312,33 +33588,17 @@
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="C46:L48"/>
     <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:L54"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:L42"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="O42:AD44"/>
-    <mergeCell ref="O45:AD47"/>
-    <mergeCell ref="O48:AD50"/>
-    <mergeCell ref="O72:AD74"/>
-    <mergeCell ref="O30:AD32"/>
-    <mergeCell ref="O33:AD35"/>
-    <mergeCell ref="O36:AD38"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:L69"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:L60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C61:L63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:L66"/>
+    <mergeCell ref="O68:AD70"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:L86"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="C70:L72"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C79:L81"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/履歴書・職務経歴書/履歴書.xlsx
+++ b/履歴書・職務経歴書/履歴書.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Documents/GitHub/private/履歴書・職務経歴書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853E8EC-999A-5542-BD70-0BC294ABB911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C4960-ECA5-9A49-903C-D0E5F5DDF555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37140" yWindow="-21100" windowWidth="29000" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="28800" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書フォーマット" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mjYVIu8yOR9cIBx7KgQ3S2DCndKug=="/>
     </ext>
@@ -24,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>履 歴 書</t>
   </si>
@@ -57,9 +90,6 @@
     <t>学  歴 ・ 職  歴 （各別にまとめて書く）</t>
   </si>
   <si>
-    <t>志望の動機・経歴の補足・アピールポイントなど</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 本人希望記入欄（特に給料・職種・勤務時間・勤務地・その他についての希望などがあれば記入）</t>
   </si>
   <si>
@@ -74,23 +104,23 @@
     <rPh sb="2" eb="5">
       <t>チカコ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>くぬぎ ちかこ</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>※　女</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>chikakokunugi@icloud.com</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>090-5046-6489</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸女学院高等学部 卒業</t>
@@ -103,7 +133,7 @@
     <rPh sb="10" eb="12">
       <t>ソツギョウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸女学院大学音楽学部ピアノ専攻 卒業</t>
@@ -116,7 +146,7 @@
     <rPh sb="17" eb="19">
       <t>ソツギョウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸女学院大学大学院音楽研究科 終了</t>
@@ -126,7 +156,7 @@
     <rPh sb="16" eb="18">
       <t>シュウリョウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸市立有野北中学校常勤講師 任用</t>
@@ -142,11 +172,11 @@
     <rPh sb="15" eb="17">
       <t>ニn</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸市立有野北中学校常勤講師 任用満了</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>久元きぞう講演会連合会 勤務</t>
@@ -159,7 +189,7 @@
     <rPh sb="12" eb="14">
       <t>キンム</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>久元きぞう講演会連合会 退職</t>
@@ -175,7 +205,7 @@
     <rPh sb="12" eb="14">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸女学院大学 入試広報室 / 大学図書館 勤務</t>
@@ -191,14 +221,14 @@
     <rPh sb="22" eb="24">
       <t>キンム</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸女学院大学 入試広報室 / 大学図書館 退職</t>
     <rPh sb="22" eb="24">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸山手女子高等学校音楽科 常勤講師 任用</t>
@@ -217,14 +247,14 @@
     <rPh sb="19" eb="21">
       <t>ニンヨウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>神戸山手女子高等学校音楽科 常勤講師 任用満了</t>
     <rPh sb="21" eb="23">
       <t>マンリョウタイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社CBSデザイン 入社</t>
@@ -234,7 +264,7 @@
     <rPh sb="12" eb="14">
       <t>ニュウシャ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社ワサビ 入社 (9月より正社員、2019年4月よりアルバイト)</t>
@@ -256,7 +286,7 @@
     <rPh sb="26" eb="27">
       <t>ガツヨリ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社ワサビ / 株式会社CBSデザイン 退職</t>
@@ -269,14 +299,14 @@
     <rPh sb="22" eb="24">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>普通自動車第一種運転免許 取得</t>
     <rPh sb="13" eb="15">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>高等学校教諭専修免許状  取得</t>
@@ -289,7 +319,7 @@
     <rPh sb="8" eb="11">
       <t>m</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>中学校教諭専修免許状  取得</t>
@@ -302,7 +332,7 @@
     <rPh sb="7" eb="10">
       <t>m</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>高等学校教諭一種免許状  取得</t>
@@ -318,7 +348,7 @@
     <rPh sb="8" eb="11">
       <t>メn</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>中学校教諭一種免許状  取得</t>
@@ -334,15 +364,11 @@
     <rPh sb="7" eb="10">
       <t>メn</t>
     </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>1984年　　　　9　月　　　　1　日生　（満　　39　歳）　</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>〒652-0008</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>兵庫県神戸市兵庫区上祇園町 11-1 サニーハイツ上祇園303</t>
@@ -352,7 +378,7 @@
     <rPh sb="25" eb="28">
       <t>ウエ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社浜学園退職</t>
@@ -365,7 +391,7 @@
     <rPh sb="7" eb="9">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社浜学園入社</t>
@@ -378,33 +404,7 @@
     <rPh sb="7" eb="9">
       <t>ニュウシャ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>　　　令和6　年　9　　月　　10　日現在</t>
-    <rPh sb="3" eb="5">
-      <t>レイワ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>株式会社かもめ 入社 2022年4月よりリ取締役員</t>
-    <rPh sb="0" eb="4">
-      <t>カブシキ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ニュウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ネn</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ガツヨリ</t>
-    </rPh>
-    <rPh sb="21" eb="25">
-      <t>トリシマリ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>株式会社かもめ 退職</t>
@@ -414,14 +414,45 @@
     <rPh sb="8" eb="10">
       <t>タイショク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社かもめ 入社 </t>
+    <rPh sb="0" eb="4">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウシャ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>　　　令和7　年　3　　月　　16　日現在</t>
+    <rPh sb="3" eb="5">
+      <t>レイワ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1984年　　　　9　月　　　　1　日生　（満　　41　歳）　</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>志望の動機・経歴の補足・アピールポイントなど</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>教職からWEB業界へ転身し、サポートエンジニアから制作、ディレクションまで経験を積んできました。
+前職では取締役としてリユース事業全体を統括し、主要ECモールの運営やSEO施策、チームマネジメント、採用にいたるまで幅広く従事。実務面においても、VBA等を活用したDX推進によりオペレーションコストの削減を実現するなど、経営・現場両方の視点から事業の成長と組織の安定化に尽力しました。 
+これまでのWeb・EC領域における実務経験とマネジメント実績を活かしつつ、新しい環境や未経験の領域にも柔軟かつ積極的に挑戦し、貴社の事業発展に貢献したいと考えております。</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -476,13 +507,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="MS PMincho"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -496,6 +520,18 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="MS PMincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS PMincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="MS PMincho"/>
       <family val="1"/>
       <charset val="128"/>
@@ -999,7 +1035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1021,63 +1057,35 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1086,6 +1094,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1097,26 +1111,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1130,11 +1126,92 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1160,34 +1237,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1196,53 +1258,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1261,441 +1296,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1219200" cy="1628775"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Shape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4741163" y="2967200"/>
-          <a:ext cx="1209675" cy="1625600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525" cap="flat" cmpd="sng">
-          <a:solidFill>
-            <a:srgbClr val="7F7F7F"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-          <a:headEnd type="none" w="sm" len="sm"/>
-          <a:tailEnd type="none" w="sm" len="sm"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="t" anchorCtr="0">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="700"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="700" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>　                                 </a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>   写真をはる位置</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="Arial"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:endParaRPr sz="750" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="MS Mincho"/>
-            <a:ea typeface="MS Mincho"/>
-            <a:cs typeface="MS Mincho"/>
-            <a:sym typeface="MS Mincho"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>  写真をはる必要が </a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>  ある場合</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t> 1．縦  36～40mm</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>    横  24～30mm　</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t> 2.本人単身胸から上</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t> 3.裏面のりづけ</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="FF0000"/>
-            </a:buClr>
-            <a:buSzPts val="800"/>
-            <a:buFont typeface="Arial"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>※写真データが無い</a:t>
-          </a:r>
-          <a:endParaRPr sz="800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="FF0000"/>
-            </a:buClr>
-            <a:buSzPts val="800"/>
-            <a:buFont typeface="Arial"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>　場合は貼付不要です</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="000000"/>
-            </a:buClr>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="MS Mincho"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="750" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="MS Mincho"/>
-              <a:ea typeface="MS Mincho"/>
-              <a:cs typeface="MS Mincho"/>
-              <a:sym typeface="MS Mincho"/>
-            </a:rPr>
-            <a:t>　</a:t>
-          </a:r>
-          <a:endParaRPr sz="750" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="MS Mincho"/>
-            <a:ea typeface="MS Mincho"/>
-            <a:cs typeface="MS Mincho"/>
-            <a:sym typeface="MS Mincho"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buSzPts val="750"/>
-            <a:buFont typeface="Arial"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:endParaRPr sz="750" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="MS Mincho"/>
-            <a:ea typeface="MS Mincho"/>
-            <a:cs typeface="MS Mincho"/>
-            <a:sym typeface="MS Mincho"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1910,7 +1572,7 @@
     <col min="9" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="9.1640625" customWidth="1"/>
     <col min="11" max="11" width="3.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.5" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" customWidth="1"/>
     <col min="13" max="13" width="9.1640625" customWidth="1"/>
     <col min="14" max="14" width="4.6640625" customWidth="1"/>
     <col min="15" max="15" width="8.6640625" customWidth="1"/>
@@ -1932,9 +1594,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="9" customHeight="1">
-      <c r="A1" s="57"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1946,93 +1608,93 @@
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
     </row>
     <row r="2" spans="1:30" ht="9" customHeight="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
     </row>
     <row r="3" spans="1:30" ht="9" customHeight="1">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
     </row>
     <row r="4" spans="1:30" ht="9" customHeight="1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2"/>
       <c r="F4" s="5"/>
@@ -2040,100 +1702,102 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="K4" s="55" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L4" s="55"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="42" t="s">
+      <c r="O4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="44" t="s">
+      <c r="P4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="62" t="s">
+      <c r="Q4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="40"/>
-      <c r="AB4" s="40"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="41"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="34"/>
     </row>
     <row r="5" spans="1:30" ht="9" customHeight="1">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
-      <c r="AC5" s="20"/>
-      <c r="AD5" s="21"/>
-    </row>
-    <row r="6" spans="1:30" ht="9" customHeight="1">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
+      <c r="AC5" s="22"/>
+      <c r="AD5" s="23"/>
+    </row>
+    <row r="6" spans="1:30" ht="9" customHeight="1" thickBot="1">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="63"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="64"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="64"/>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="64"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="64"/>
-      <c r="AD6" s="65"/>
-    </row>
-    <row r="7" spans="1:30" ht="9" customHeight="1">
+      <c r="O6" s="29"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="59"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="59"/>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="59"/>
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="60"/>
+    </row>
+    <row r="7" spans="1:30" ht="9" customHeight="1" thickTop="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2144,642 +1808,642 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="46">
+      <c r="O7" s="50">
         <v>2008</v>
       </c>
-      <c r="P7" s="47">
+      <c r="P7" s="52">
         <v>3</v>
       </c>
-      <c r="Q7" s="48" t="s">
-        <v>36</v>
+      <c r="Q7" s="61" t="s">
+        <v>35</v>
       </c>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="21"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="23"/>
     </row>
     <row r="8" spans="1:30" ht="9" customHeight="1">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="23"/>
+    </row>
+    <row r="9" spans="1:30" ht="9" customHeight="1">
+      <c r="A9" s="14"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="26"/>
+    </row>
+    <row r="10" spans="1:30" ht="9" customHeight="1">
+      <c r="A10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="50">
+        <v>2008</v>
+      </c>
+      <c r="P10" s="52">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="23"/>
+    </row>
+    <row r="11" spans="1:30" ht="9" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="23"/>
+    </row>
+    <row r="12" spans="1:30" ht="9" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="26"/>
+    </row>
+    <row r="13" spans="1:30" ht="9" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="12">
+        <v>2010</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="20"/>
+    </row>
+    <row r="14" spans="1:30" ht="9" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="23"/>
+    </row>
+    <row r="15" spans="1:30" ht="9" customHeight="1">
+      <c r="A15" s="17"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="26"/>
+    </row>
+    <row r="16" spans="1:30" ht="9" customHeight="1">
+      <c r="A16" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="21"/>
-    </row>
-    <row r="9" spans="1:30" ht="9" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="34"/>
-    </row>
-    <row r="10" spans="1:30" ht="9" customHeight="1">
-      <c r="A10" s="70" t="s">
-        <v>4</v>
+      <c r="I16" s="34"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="12">
+        <v>2010</v>
       </c>
-      <c r="B10" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="46">
-        <v>2008</v>
-      </c>
-      <c r="P10" s="47">
+      <c r="P16" s="9">
         <v>3</v>
       </c>
-      <c r="Q10" s="48" t="s">
-        <v>35</v>
+      <c r="Q16" s="27" t="s">
+        <v>32</v>
       </c>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="21"/>
-    </row>
-    <row r="11" spans="1:30" ht="9" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="21"/>
-    </row>
-    <row r="12" spans="1:30" ht="9" customHeight="1">
-      <c r="A12" s="36"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="34"/>
-    </row>
-    <row r="13" spans="1:30" ht="9" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="35">
-        <v>2010</v>
-      </c>
-      <c r="P13" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="30"/>
-    </row>
-    <row r="14" spans="1:30" ht="9" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="21"/>
-    </row>
-    <row r="15" spans="1:30" ht="9" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="34"/>
-    </row>
-    <row r="16" spans="1:30" ht="9" customHeight="1">
-      <c r="A16" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="41"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="35">
-        <v>2010</v>
-      </c>
-      <c r="P16" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="30"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="20"/>
     </row>
     <row r="17" spans="1:30" ht="9" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="21"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="23"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="21"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="23"/>
     </row>
     <row r="18" spans="1:30" ht="9" customHeight="1">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="24"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="34"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="26"/>
     </row>
     <row r="19" spans="1:30" ht="9" customHeight="1">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="76" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="41"/>
+      <c r="L19" s="34"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="35">
+      <c r="O19" s="12">
         <v>2010</v>
       </c>
-      <c r="P19" s="25">
+      <c r="P19" s="9">
         <v>3</v>
       </c>
-      <c r="Q19" s="28" t="s">
-        <v>32</v>
+      <c r="Q19" s="27" t="s">
+        <v>31</v>
       </c>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="29"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="30"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="20"/>
     </row>
     <row r="20" spans="1:30" ht="9" customHeight="1">
-      <c r="A20" s="37"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="21"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="23"/>
       <c r="M20" s="7"/>
       <c r="N20" s="8"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="21"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="23"/>
     </row>
     <row r="21" spans="1:30" ht="9" customHeight="1">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="73" t="s">
-        <v>38</v>
+      <c r="B21" s="35" t="s">
+        <v>36</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="68" t="s">
-        <v>17</v>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="69" t="s">
+        <v>16</v>
       </c>
-      <c r="L21" s="30"/>
+      <c r="L21" s="20"/>
       <c r="M21" s="7"/>
       <c r="N21" s="8"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="34"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="26"/>
     </row>
     <row r="22" spans="1:30" ht="9" customHeight="1">
-      <c r="A22" s="36"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="24"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="38"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29"/>
-      <c r="Y22" s="29"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="30"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="19"/>
+      <c r="AA22" s="19"/>
+      <c r="AB22" s="19"/>
+      <c r="AC22" s="19"/>
+      <c r="AD22" s="20"/>
     </row>
     <row r="23" spans="1:30" ht="9" customHeight="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="77" t="s">
-        <v>39</v>
+      <c r="A23" s="13"/>
+      <c r="B23" s="45" t="s">
+        <v>37</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="69" t="s">
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="21"/>
+      <c r="L23" s="23"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="21"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="23"/>
     </row>
     <row r="24" spans="1:30" ht="9" customHeight="1">
-      <c r="A24" s="36"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="21"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="23"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AC24" s="23"/>
-      <c r="AD24" s="24"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="38"/>
     </row>
     <row r="25" spans="1:30" ht="9" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="78" t="s">
-        <v>16</v>
+      <c r="A25" s="13"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="46" t="s">
+        <v>15</v>
       </c>
-      <c r="L25" s="79"/>
+      <c r="L25" s="47"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2800,38 +2464,38 @@
       <c r="AD25" s="3"/>
     </row>
     <row r="26" spans="1:30" ht="9" customHeight="1">
-      <c r="A26" s="71"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="81"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="49"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="50" t="s">
-        <v>10</v>
+      <c r="O26" s="63" t="s">
+        <v>44</v>
       </c>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="51"/>
-      <c r="AA26" s="51"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="52"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="64"/>
+      <c r="S26" s="64"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="64"/>
+      <c r="AB26" s="64"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="65"/>
     </row>
     <row r="27" spans="1:30" ht="9" customHeight="1">
       <c r="A27" s="3"/>
@@ -2848,1092 +2512,1332 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="54"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="67"/>
     </row>
     <row r="28" spans="1:30" ht="9" customHeight="1">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="41"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="34"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="55"/>
-      <c r="AB28" s="55"/>
-      <c r="AC28" s="55"/>
-      <c r="AD28" s="54"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="68"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="68"/>
+      <c r="V28" s="68"/>
+      <c r="W28" s="68"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="68"/>
+      <c r="Z28" s="68"/>
+      <c r="AA28" s="68"/>
+      <c r="AB28" s="68"/>
+      <c r="AC28" s="68"/>
+      <c r="AD28" s="67"/>
     </row>
     <row r="29" spans="1:30" ht="9" customHeight="1">
-      <c r="A29" s="36"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="21"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="23"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="55"/>
-      <c r="Z29" s="55"/>
-      <c r="AA29" s="55"/>
-      <c r="AB29" s="55"/>
-      <c r="AC29" s="55"/>
-      <c r="AD29" s="54"/>
+      <c r="O29" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="77"/>
+      <c r="R29" s="77"/>
+      <c r="S29" s="77"/>
+      <c r="T29" s="77"/>
+      <c r="U29" s="77"/>
+      <c r="V29" s="77"/>
+      <c r="W29" s="77"/>
+      <c r="X29" s="77"/>
+      <c r="Y29" s="77"/>
+      <c r="Z29" s="77"/>
+      <c r="AA29" s="77"/>
+      <c r="AB29" s="77"/>
+      <c r="AC29" s="77"/>
+      <c r="AD29" s="78"/>
     </row>
     <row r="30" spans="1:30" ht="9" customHeight="1" thickBot="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="65"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="60"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="54"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="77"/>
+      <c r="Q30" s="77"/>
+      <c r="R30" s="77"/>
+      <c r="S30" s="77"/>
+      <c r="T30" s="77"/>
+      <c r="U30" s="77"/>
+      <c r="V30" s="77"/>
+      <c r="W30" s="77"/>
+      <c r="X30" s="77"/>
+      <c r="Y30" s="77"/>
+      <c r="Z30" s="77"/>
+      <c r="AA30" s="77"/>
+      <c r="AB30" s="77"/>
+      <c r="AC30" s="77"/>
+      <c r="AD30" s="78"/>
     </row>
     <row r="31" spans="1:30" ht="9" customHeight="1" thickTop="1">
-      <c r="A31" s="35">
+      <c r="A31" s="12">
         <v>2003</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="9">
         <v>3</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="77"/>
+      <c r="R31" s="77"/>
+      <c r="S31" s="77"/>
+      <c r="T31" s="77"/>
+      <c r="U31" s="77"/>
+      <c r="V31" s="77"/>
+      <c r="W31" s="77"/>
+      <c r="X31" s="77"/>
+      <c r="Y31" s="77"/>
+      <c r="Z31" s="77"/>
+      <c r="AA31" s="77"/>
+      <c r="AB31" s="77"/>
+      <c r="AC31" s="77"/>
+      <c r="AD31" s="78"/>
+    </row>
+    <row r="32" spans="1:30" ht="9" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="77"/>
+      <c r="U32" s="77"/>
+      <c r="V32" s="77"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="77"/>
+      <c r="Y32" s="77"/>
+      <c r="Z32" s="77"/>
+      <c r="AA32" s="77"/>
+      <c r="AB32" s="77"/>
+      <c r="AC32" s="77"/>
+      <c r="AD32" s="78"/>
+    </row>
+    <row r="33" spans="1:30" ht="9" customHeight="1">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="77"/>
+      <c r="R33" s="77"/>
+      <c r="S33" s="77"/>
+      <c r="T33" s="77"/>
+      <c r="U33" s="77"/>
+      <c r="V33" s="77"/>
+      <c r="W33" s="77"/>
+      <c r="X33" s="77"/>
+      <c r="Y33" s="77"/>
+      <c r="Z33" s="77"/>
+      <c r="AA33" s="77"/>
+      <c r="AB33" s="77"/>
+      <c r="AC33" s="77"/>
+      <c r="AD33" s="78"/>
+    </row>
+    <row r="34" spans="1:30" ht="9" customHeight="1">
+      <c r="A34" s="12">
+        <v>2008</v>
+      </c>
+      <c r="B34" s="9">
+        <v>3</v>
+      </c>
+      <c r="C34" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="54"/>
-    </row>
-    <row r="32" spans="1:30" ht="9" customHeight="1">
-      <c r="A32" s="36"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="54"/>
-    </row>
-    <row r="33" spans="1:30" ht="9" customHeight="1">
-      <c r="A33" s="37"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="54"/>
-    </row>
-    <row r="34" spans="1:30" ht="9" customHeight="1">
-      <c r="A34" s="35">
-        <v>2008</v>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="77"/>
+      <c r="R34" s="77"/>
+      <c r="S34" s="77"/>
+      <c r="T34" s="77"/>
+      <c r="U34" s="77"/>
+      <c r="V34" s="77"/>
+      <c r="W34" s="77"/>
+      <c r="X34" s="77"/>
+      <c r="Y34" s="77"/>
+      <c r="Z34" s="77"/>
+      <c r="AA34" s="77"/>
+      <c r="AB34" s="77"/>
+      <c r="AC34" s="77"/>
+      <c r="AD34" s="78"/>
+    </row>
+    <row r="35" spans="1:30" ht="9" customHeight="1">
+      <c r="A35" s="13"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="77"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="77"/>
+      <c r="U35" s="77"/>
+      <c r="V35" s="77"/>
+      <c r="W35" s="77"/>
+      <c r="X35" s="77"/>
+      <c r="Y35" s="77"/>
+      <c r="Z35" s="77"/>
+      <c r="AA35" s="77"/>
+      <c r="AB35" s="77"/>
+      <c r="AC35" s="77"/>
+      <c r="AD35" s="78"/>
+    </row>
+    <row r="36" spans="1:30" ht="9" customHeight="1">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="77"/>
+      <c r="Q36" s="77"/>
+      <c r="R36" s="77"/>
+      <c r="S36" s="77"/>
+      <c r="T36" s="77"/>
+      <c r="U36" s="77"/>
+      <c r="V36" s="77"/>
+      <c r="W36" s="77"/>
+      <c r="X36" s="77"/>
+      <c r="Y36" s="77"/>
+      <c r="Z36" s="77"/>
+      <c r="AA36" s="77"/>
+      <c r="AB36" s="77"/>
+      <c r="AC36" s="77"/>
+      <c r="AD36" s="78"/>
+    </row>
+    <row r="37" spans="1:30" ht="9" customHeight="1">
+      <c r="A37" s="12">
+        <v>2010</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B37" s="9">
         <v>3</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C37" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="20"/>
-      <c r="AC34" s="20"/>
-      <c r="AD34" s="54"/>
-    </row>
-    <row r="35" spans="1:30" ht="9" customHeight="1">
-      <c r="A35" s="36"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="20"/>
-      <c r="AC35" s="20"/>
-      <c r="AD35" s="54"/>
-    </row>
-    <row r="36" spans="1:30" ht="9" customHeight="1">
-      <c r="A36" s="37"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
-      <c r="U36" s="20"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="20"/>
-      <c r="AC36" s="20"/>
-      <c r="AD36" s="54"/>
-    </row>
-    <row r="37" spans="1:30" ht="9" customHeight="1">
-      <c r="A37" s="35">
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="77"/>
+      <c r="Q37" s="77"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
+      <c r="U37" s="77"/>
+      <c r="V37" s="77"/>
+      <c r="W37" s="77"/>
+      <c r="X37" s="77"/>
+      <c r="Y37" s="77"/>
+      <c r="Z37" s="77"/>
+      <c r="AA37" s="77"/>
+      <c r="AB37" s="77"/>
+      <c r="AC37" s="77"/>
+      <c r="AD37" s="78"/>
+    </row>
+    <row r="38" spans="1:30" ht="9" customHeight="1">
+      <c r="A38" s="13"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="77"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="77"/>
+      <c r="S38" s="77"/>
+      <c r="T38" s="77"/>
+      <c r="U38" s="77"/>
+      <c r="V38" s="77"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="77"/>
+      <c r="Y38" s="77"/>
+      <c r="Z38" s="77"/>
+      <c r="AA38" s="77"/>
+      <c r="AB38" s="77"/>
+      <c r="AC38" s="77"/>
+      <c r="AD38" s="78"/>
+    </row>
+    <row r="39" spans="1:30" ht="9" customHeight="1">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="76"/>
+      <c r="P39" s="77"/>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="77"/>
+      <c r="V39" s="77"/>
+      <c r="W39" s="77"/>
+      <c r="X39" s="77"/>
+      <c r="Y39" s="77"/>
+      <c r="Z39" s="77"/>
+      <c r="AA39" s="77"/>
+      <c r="AB39" s="77"/>
+      <c r="AC39" s="77"/>
+      <c r="AD39" s="78"/>
+    </row>
+    <row r="40" spans="1:30" ht="9" customHeight="1">
+      <c r="A40" s="12">
         <v>2010</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B40" s="9">
+        <v>4</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="76"/>
+      <c r="P40" s="77"/>
+      <c r="Q40" s="77"/>
+      <c r="R40" s="77"/>
+      <c r="S40" s="77"/>
+      <c r="T40" s="77"/>
+      <c r="U40" s="77"/>
+      <c r="V40" s="77"/>
+      <c r="W40" s="77"/>
+      <c r="X40" s="77"/>
+      <c r="Y40" s="77"/>
+      <c r="Z40" s="77"/>
+      <c r="AA40" s="77"/>
+      <c r="AB40" s="77"/>
+      <c r="AC40" s="77"/>
+      <c r="AD40" s="78"/>
+    </row>
+    <row r="41" spans="1:30" ht="9" customHeight="1">
+      <c r="A41" s="13"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="76"/>
+      <c r="P41" s="77"/>
+      <c r="Q41" s="77"/>
+      <c r="R41" s="77"/>
+      <c r="S41" s="77"/>
+      <c r="T41" s="77"/>
+      <c r="U41" s="77"/>
+      <c r="V41" s="77"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="77"/>
+      <c r="Y41" s="77"/>
+      <c r="Z41" s="77"/>
+      <c r="AA41" s="77"/>
+      <c r="AB41" s="77"/>
+      <c r="AC41" s="77"/>
+      <c r="AD41" s="78"/>
+    </row>
+    <row r="42" spans="1:30" ht="9" customHeight="1">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="76"/>
+      <c r="P42" s="77"/>
+      <c r="Q42" s="77"/>
+      <c r="R42" s="77"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="77"/>
+      <c r="U42" s="77"/>
+      <c r="V42" s="77"/>
+      <c r="W42" s="77"/>
+      <c r="X42" s="77"/>
+      <c r="Y42" s="77"/>
+      <c r="Z42" s="77"/>
+      <c r="AA42" s="77"/>
+      <c r="AB42" s="77"/>
+      <c r="AC42" s="77"/>
+      <c r="AD42" s="78"/>
+    </row>
+    <row r="43" spans="1:30" ht="9" customHeight="1">
+      <c r="A43" s="12">
+        <v>2013</v>
+      </c>
+      <c r="B43" s="9">
         <v>3</v>
       </c>
-      <c r="C37" s="28" t="s">
-        <v>20</v>
+      <c r="C43" s="27" t="s">
+        <v>21</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="20"/>
-      <c r="AD37" s="54"/>
-    </row>
-    <row r="38" spans="1:30" ht="9" customHeight="1">
-      <c r="A38" s="36"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="20"/>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="20"/>
-      <c r="AC38" s="20"/>
-      <c r="AD38" s="54"/>
-    </row>
-    <row r="39" spans="1:30" ht="9" customHeight="1">
-      <c r="A39" s="37"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="20"/>
-      <c r="AA39" s="20"/>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="20"/>
-      <c r="AD39" s="54"/>
-    </row>
-    <row r="40" spans="1:30" ht="9" customHeight="1">
-      <c r="A40" s="35">
-        <v>2010</v>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="77"/>
+      <c r="S43" s="77"/>
+      <c r="T43" s="77"/>
+      <c r="U43" s="77"/>
+      <c r="V43" s="77"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="77"/>
+      <c r="Y43" s="77"/>
+      <c r="Z43" s="77"/>
+      <c r="AA43" s="77"/>
+      <c r="AB43" s="77"/>
+      <c r="AC43" s="77"/>
+      <c r="AD43" s="78"/>
+    </row>
+    <row r="44" spans="1:30" ht="9" customHeight="1">
+      <c r="A44" s="13"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="76"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="77"/>
+      <c r="S44" s="77"/>
+      <c r="T44" s="77"/>
+      <c r="U44" s="77"/>
+      <c r="V44" s="77"/>
+      <c r="W44" s="77"/>
+      <c r="X44" s="77"/>
+      <c r="Y44" s="77"/>
+      <c r="Z44" s="77"/>
+      <c r="AA44" s="77"/>
+      <c r="AB44" s="77"/>
+      <c r="AC44" s="77"/>
+      <c r="AD44" s="78"/>
+    </row>
+    <row r="45" spans="1:30" ht="9" customHeight="1">
+      <c r="A45" s="14"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="76"/>
+      <c r="P45" s="77"/>
+      <c r="Q45" s="77"/>
+      <c r="R45" s="77"/>
+      <c r="S45" s="77"/>
+      <c r="T45" s="77"/>
+      <c r="U45" s="77"/>
+      <c r="V45" s="77"/>
+      <c r="W45" s="77"/>
+      <c r="X45" s="77"/>
+      <c r="Y45" s="77"/>
+      <c r="Z45" s="77"/>
+      <c r="AA45" s="77"/>
+      <c r="AB45" s="77"/>
+      <c r="AC45" s="77"/>
+      <c r="AD45" s="78"/>
+    </row>
+    <row r="46" spans="1:30" ht="9" customHeight="1">
+      <c r="A46" s="12">
+        <v>2013</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B46" s="9">
         <v>4</v>
       </c>
-      <c r="C40" s="28" t="s">
-        <v>21</v>
+      <c r="C46" s="27" t="s">
+        <v>22</v>
       </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40" s="20"/>
-      <c r="AB40" s="20"/>
-      <c r="AC40" s="20"/>
-      <c r="AD40" s="54"/>
-    </row>
-    <row r="41" spans="1:30" ht="9" customHeight="1">
-      <c r="A41" s="36"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="20"/>
-      <c r="AA41" s="20"/>
-      <c r="AB41" s="20"/>
-      <c r="AC41" s="20"/>
-      <c r="AD41" s="54"/>
-    </row>
-    <row r="42" spans="1:30" ht="9" customHeight="1">
-      <c r="A42" s="37"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="53"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="20"/>
-      <c r="AA42" s="20"/>
-      <c r="AB42" s="20"/>
-      <c r="AC42" s="20"/>
-      <c r="AD42" s="54"/>
-    </row>
-    <row r="43" spans="1:30" ht="9" customHeight="1">
-      <c r="A43" s="35">
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="76"/>
+      <c r="P46" s="77"/>
+      <c r="Q46" s="77"/>
+      <c r="R46" s="77"/>
+      <c r="S46" s="77"/>
+      <c r="T46" s="77"/>
+      <c r="U46" s="77"/>
+      <c r="V46" s="77"/>
+      <c r="W46" s="77"/>
+      <c r="X46" s="77"/>
+      <c r="Y46" s="77"/>
+      <c r="Z46" s="77"/>
+      <c r="AA46" s="77"/>
+      <c r="AB46" s="77"/>
+      <c r="AC46" s="77"/>
+      <c r="AD46" s="78"/>
+    </row>
+    <row r="47" spans="1:30" ht="9" customHeight="1">
+      <c r="A47" s="13"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="77"/>
+      <c r="Q47" s="77"/>
+      <c r="R47" s="77"/>
+      <c r="S47" s="77"/>
+      <c r="T47" s="77"/>
+      <c r="U47" s="77"/>
+      <c r="V47" s="77"/>
+      <c r="W47" s="77"/>
+      <c r="X47" s="77"/>
+      <c r="Y47" s="77"/>
+      <c r="Z47" s="77"/>
+      <c r="AA47" s="77"/>
+      <c r="AB47" s="77"/>
+      <c r="AC47" s="77"/>
+      <c r="AD47" s="78"/>
+    </row>
+    <row r="48" spans="1:30" ht="9" customHeight="1">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="76"/>
+      <c r="P48" s="77"/>
+      <c r="Q48" s="77"/>
+      <c r="R48" s="77"/>
+      <c r="S48" s="77"/>
+      <c r="T48" s="77"/>
+      <c r="U48" s="77"/>
+      <c r="V48" s="77"/>
+      <c r="W48" s="77"/>
+      <c r="X48" s="77"/>
+      <c r="Y48" s="77"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+      <c r="AC48" s="77"/>
+      <c r="AD48" s="78"/>
+    </row>
+    <row r="49" spans="1:30" ht="9" customHeight="1">
+      <c r="A49" s="12">
         <v>2013</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B49" s="9">
+        <v>10</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="76"/>
+      <c r="P49" s="77"/>
+      <c r="Q49" s="77"/>
+      <c r="R49" s="77"/>
+      <c r="S49" s="77"/>
+      <c r="T49" s="77"/>
+      <c r="U49" s="77"/>
+      <c r="V49" s="77"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="77"/>
+      <c r="Y49" s="77"/>
+      <c r="Z49" s="77"/>
+      <c r="AA49" s="77"/>
+      <c r="AB49" s="77"/>
+      <c r="AC49" s="77"/>
+      <c r="AD49" s="78"/>
+    </row>
+    <row r="50" spans="1:30" ht="9" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="76"/>
+      <c r="P50" s="77"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="77"/>
+      <c r="S50" s="77"/>
+      <c r="T50" s="77"/>
+      <c r="U50" s="77"/>
+      <c r="V50" s="77"/>
+      <c r="W50" s="77"/>
+      <c r="X50" s="77"/>
+      <c r="Y50" s="77"/>
+      <c r="Z50" s="77"/>
+      <c r="AA50" s="77"/>
+      <c r="AB50" s="77"/>
+      <c r="AC50" s="77"/>
+      <c r="AD50" s="78"/>
+    </row>
+    <row r="51" spans="1:30" ht="9" customHeight="1">
+      <c r="A51" s="14"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="76"/>
+      <c r="P51" s="77"/>
+      <c r="Q51" s="77"/>
+      <c r="R51" s="77"/>
+      <c r="S51" s="77"/>
+      <c r="T51" s="77"/>
+      <c r="U51" s="77"/>
+      <c r="V51" s="77"/>
+      <c r="W51" s="77"/>
+      <c r="X51" s="77"/>
+      <c r="Y51" s="77"/>
+      <c r="Z51" s="77"/>
+      <c r="AA51" s="77"/>
+      <c r="AB51" s="77"/>
+      <c r="AC51" s="77"/>
+      <c r="AD51" s="78"/>
+    </row>
+    <row r="52" spans="1:30" ht="9" customHeight="1">
+      <c r="A52" s="12">
+        <v>2013</v>
+      </c>
+      <c r="B52" s="9">
+        <v>11</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="76"/>
+      <c r="P52" s="77"/>
+      <c r="Q52" s="77"/>
+      <c r="R52" s="77"/>
+      <c r="S52" s="77"/>
+      <c r="T52" s="77"/>
+      <c r="U52" s="77"/>
+      <c r="V52" s="77"/>
+      <c r="W52" s="77"/>
+      <c r="X52" s="77"/>
+      <c r="Y52" s="77"/>
+      <c r="Z52" s="77"/>
+      <c r="AA52" s="77"/>
+      <c r="AB52" s="77"/>
+      <c r="AC52" s="77"/>
+      <c r="AD52" s="78"/>
+    </row>
+    <row r="53" spans="1:30" ht="9" customHeight="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="76"/>
+      <c r="P53" s="77"/>
+      <c r="Q53" s="77"/>
+      <c r="R53" s="77"/>
+      <c r="S53" s="77"/>
+      <c r="T53" s="77"/>
+      <c r="U53" s="77"/>
+      <c r="V53" s="77"/>
+      <c r="W53" s="77"/>
+      <c r="X53" s="77"/>
+      <c r="Y53" s="77"/>
+      <c r="Z53" s="77"/>
+      <c r="AA53" s="77"/>
+      <c r="AB53" s="77"/>
+      <c r="AC53" s="77"/>
+      <c r="AD53" s="78"/>
+    </row>
+    <row r="54" spans="1:30" ht="9" customHeight="1">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="76"/>
+      <c r="P54" s="77"/>
+      <c r="Q54" s="77"/>
+      <c r="R54" s="77"/>
+      <c r="S54" s="77"/>
+      <c r="T54" s="77"/>
+      <c r="U54" s="77"/>
+      <c r="V54" s="77"/>
+      <c r="W54" s="77"/>
+      <c r="X54" s="77"/>
+      <c r="Y54" s="77"/>
+      <c r="Z54" s="77"/>
+      <c r="AA54" s="77"/>
+      <c r="AB54" s="77"/>
+      <c r="AC54" s="77"/>
+      <c r="AD54" s="78"/>
+    </row>
+    <row r="55" spans="1:30" ht="9" customHeight="1">
+      <c r="A55" s="12">
+        <v>2014</v>
+      </c>
+      <c r="B55" s="9">
         <v>3</v>
       </c>
-      <c r="C43" s="28" t="s">
-        <v>22</v>
+      <c r="C55" s="18" t="s">
+        <v>25</v>
       </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="53"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="20"/>
-      <c r="AA43" s="20"/>
-      <c r="AB43" s="20"/>
-      <c r="AC43" s="20"/>
-      <c r="AD43" s="54"/>
-    </row>
-    <row r="44" spans="1:30" ht="9" customHeight="1">
-      <c r="A44" s="36"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="53"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="20"/>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-      <c r="Z44" s="20"/>
-      <c r="AA44" s="20"/>
-      <c r="AB44" s="20"/>
-      <c r="AC44" s="20"/>
-      <c r="AD44" s="54"/>
-    </row>
-    <row r="45" spans="1:30" ht="9" customHeight="1">
-      <c r="A45" s="37"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="20"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
-      <c r="AA45" s="20"/>
-      <c r="AB45" s="20"/>
-      <c r="AC45" s="20"/>
-      <c r="AD45" s="54"/>
-    </row>
-    <row r="46" spans="1:30" ht="9" customHeight="1">
-      <c r="A46" s="35">
-        <v>2013</v>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="76"/>
+      <c r="P55" s="77"/>
+      <c r="Q55" s="77"/>
+      <c r="R55" s="77"/>
+      <c r="S55" s="77"/>
+      <c r="T55" s="77"/>
+      <c r="U55" s="77"/>
+      <c r="V55" s="77"/>
+      <c r="W55" s="77"/>
+      <c r="X55" s="77"/>
+      <c r="Y55" s="77"/>
+      <c r="Z55" s="77"/>
+      <c r="AA55" s="77"/>
+      <c r="AB55" s="77"/>
+      <c r="AC55" s="77"/>
+      <c r="AD55" s="78"/>
+    </row>
+    <row r="56" spans="1:30" ht="9" customHeight="1">
+      <c r="A56" s="13"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="23"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="76"/>
+      <c r="P56" s="77"/>
+      <c r="Q56" s="77"/>
+      <c r="R56" s="77"/>
+      <c r="S56" s="77"/>
+      <c r="T56" s="77"/>
+      <c r="U56" s="77"/>
+      <c r="V56" s="77"/>
+      <c r="W56" s="77"/>
+      <c r="X56" s="77"/>
+      <c r="Y56" s="77"/>
+      <c r="Z56" s="77"/>
+      <c r="AA56" s="77"/>
+      <c r="AB56" s="77"/>
+      <c r="AC56" s="77"/>
+      <c r="AD56" s="78"/>
+    </row>
+    <row r="57" spans="1:30" ht="9" customHeight="1">
+      <c r="A57" s="14"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="76"/>
+      <c r="P57" s="77"/>
+      <c r="Q57" s="77"/>
+      <c r="R57" s="77"/>
+      <c r="S57" s="77"/>
+      <c r="T57" s="77"/>
+      <c r="U57" s="77"/>
+      <c r="V57" s="77"/>
+      <c r="W57" s="77"/>
+      <c r="X57" s="77"/>
+      <c r="Y57" s="77"/>
+      <c r="Z57" s="77"/>
+      <c r="AA57" s="77"/>
+      <c r="AB57" s="77"/>
+      <c r="AC57" s="77"/>
+      <c r="AD57" s="78"/>
+    </row>
+    <row r="58" spans="1:30" ht="9" customHeight="1">
+      <c r="A58" s="12">
+        <v>2014</v>
       </c>
-      <c r="B46" s="25">
+      <c r="B58" s="9">
         <v>4</v>
       </c>
-      <c r="C46" s="28" t="s">
-        <v>23</v>
+      <c r="C58" s="18" t="s">
+        <v>26</v>
       </c>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="53"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="20"/>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-      <c r="Z46" s="20"/>
-      <c r="AA46" s="20"/>
-      <c r="AB46" s="20"/>
-      <c r="AC46" s="20"/>
-      <c r="AD46" s="54"/>
-    </row>
-    <row r="47" spans="1:30" ht="9" customHeight="1">
-      <c r="A47" s="36"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2"/>
-      <c r="AB47" s="2"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="10"/>
-    </row>
-    <row r="48" spans="1:30" ht="9" customHeight="1">
-      <c r="A48" s="37"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="11"/>
-      <c r="AD48" s="12"/>
-    </row>
-    <row r="49" spans="1:30" ht="9" customHeight="1">
-      <c r="A49" s="35">
-        <v>2013</v>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="76"/>
+      <c r="P58" s="77"/>
+      <c r="Q58" s="77"/>
+      <c r="R58" s="77"/>
+      <c r="S58" s="77"/>
+      <c r="T58" s="77"/>
+      <c r="U58" s="77"/>
+      <c r="V58" s="77"/>
+      <c r="W58" s="77"/>
+      <c r="X58" s="77"/>
+      <c r="Y58" s="77"/>
+      <c r="Z58" s="77"/>
+      <c r="AA58" s="77"/>
+      <c r="AB58" s="77"/>
+      <c r="AC58" s="77"/>
+      <c r="AD58" s="78"/>
+    </row>
+    <row r="59" spans="1:30" ht="9" customHeight="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="76"/>
+      <c r="P59" s="77"/>
+      <c r="Q59" s="77"/>
+      <c r="R59" s="77"/>
+      <c r="S59" s="77"/>
+      <c r="T59" s="77"/>
+      <c r="U59" s="77"/>
+      <c r="V59" s="77"/>
+      <c r="W59" s="77"/>
+      <c r="X59" s="77"/>
+      <c r="Y59" s="77"/>
+      <c r="Z59" s="77"/>
+      <c r="AA59" s="77"/>
+      <c r="AB59" s="77"/>
+      <c r="AC59" s="77"/>
+      <c r="AD59" s="78"/>
+    </row>
+    <row r="60" spans="1:30" ht="9" customHeight="1">
+      <c r="A60" s="14"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="77"/>
+      <c r="Q60" s="77"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="77"/>
+      <c r="T60" s="77"/>
+      <c r="U60" s="77"/>
+      <c r="V60" s="77"/>
+      <c r="W60" s="77"/>
+      <c r="X60" s="77"/>
+      <c r="Y60" s="77"/>
+      <c r="Z60" s="77"/>
+      <c r="AA60" s="77"/>
+      <c r="AB60" s="77"/>
+      <c r="AC60" s="77"/>
+      <c r="AD60" s="78"/>
+    </row>
+    <row r="61" spans="1:30" ht="9" customHeight="1">
+      <c r="A61" s="12">
+        <v>2017</v>
       </c>
-      <c r="B49" s="25">
-        <v>10</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="11"/>
-      <c r="AD49" s="12"/>
-    </row>
-    <row r="50" spans="1:30" ht="9" customHeight="1">
-      <c r="A50" s="36"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="11"/>
-      <c r="AD50" s="12"/>
-    </row>
-    <row r="51" spans="1:30" ht="9" customHeight="1">
-      <c r="A51" s="37"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="11"/>
-      <c r="AD51" s="12"/>
-    </row>
-    <row r="52" spans="1:30" ht="9" customHeight="1">
-      <c r="A52" s="35">
-        <v>2013</v>
-      </c>
-      <c r="B52" s="25">
-        <v>11</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="11"/>
-      <c r="AD52" s="12"/>
-    </row>
-    <row r="53" spans="1:30" ht="9" customHeight="1">
-      <c r="A53" s="36"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="11"/>
-      <c r="AD53" s="12"/>
-    </row>
-    <row r="54" spans="1:30" ht="9" customHeight="1">
-      <c r="A54" s="37"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="34"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="11"/>
-      <c r="AD54" s="12"/>
-    </row>
-    <row r="55" spans="1:30" ht="9" customHeight="1">
-      <c r="A55" s="35">
-        <v>2014</v>
-      </c>
-      <c r="B55" s="25">
+      <c r="B61" s="9">
         <v>3</v>
       </c>
-      <c r="C55" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="11"/>
-      <c r="AD55" s="12"/>
-    </row>
-    <row r="56" spans="1:30" ht="9" customHeight="1">
-      <c r="A56" s="36"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="11"/>
-      <c r="AD56" s="12"/>
-    </row>
-    <row r="57" spans="1:30" ht="9" customHeight="1">
-      <c r="A57" s="37"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="34"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="11"/>
-      <c r="AD57" s="12"/>
-    </row>
-    <row r="58" spans="1:30" ht="9" customHeight="1">
-      <c r="A58" s="35">
-        <v>2014</v>
-      </c>
-      <c r="B58" s="25">
-        <v>4</v>
-      </c>
-      <c r="C58" s="38" t="s">
+      <c r="C61" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="11"/>
-      <c r="AD58" s="12"/>
-    </row>
-    <row r="59" spans="1:30" ht="9" customHeight="1">
-      <c r="A59" s="36"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="11"/>
-      <c r="AD59" s="12"/>
-    </row>
-    <row r="60" spans="1:30" ht="9" customHeight="1">
-      <c r="A60" s="37"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="11"/>
-      <c r="AD60" s="12"/>
-    </row>
-    <row r="61" spans="1:30" ht="9" customHeight="1">
-      <c r="A61" s="35">
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="76"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="77"/>
+      <c r="U61" s="77"/>
+      <c r="V61" s="77"/>
+      <c r="W61" s="77"/>
+      <c r="X61" s="77"/>
+      <c r="Y61" s="77"/>
+      <c r="Z61" s="77"/>
+      <c r="AA61" s="77"/>
+      <c r="AB61" s="77"/>
+      <c r="AC61" s="77"/>
+      <c r="AD61" s="78"/>
+    </row>
+    <row r="62" spans="1:30" ht="9" customHeight="1">
+      <c r="A62" s="13"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="76"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="77"/>
+      <c r="U62" s="77"/>
+      <c r="V62" s="77"/>
+      <c r="W62" s="77"/>
+      <c r="X62" s="77"/>
+      <c r="Y62" s="77"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="77"/>
+      <c r="AB62" s="77"/>
+      <c r="AC62" s="77"/>
+      <c r="AD62" s="78"/>
+    </row>
+    <row r="63" spans="1:30" ht="9" customHeight="1">
+      <c r="A63" s="14"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="25"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="76"/>
+      <c r="P63" s="77"/>
+      <c r="Q63" s="77"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="77"/>
+      <c r="U63" s="77"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="77"/>
+      <c r="X63" s="77"/>
+      <c r="Y63" s="77"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="77"/>
+      <c r="AB63" s="77"/>
+      <c r="AC63" s="77"/>
+      <c r="AD63" s="78"/>
+    </row>
+    <row r="64" spans="1:30" ht="9" customHeight="1">
+      <c r="A64" s="12">
         <v>2017</v>
       </c>
-      <c r="B61" s="25">
-        <v>3</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="11"/>
-      <c r="AD61" s="12"/>
-    </row>
-    <row r="62" spans="1:30" ht="9" customHeight="1">
-      <c r="A62" s="36"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="11"/>
-      <c r="AD62" s="12"/>
-    </row>
-    <row r="63" spans="1:30" ht="9" customHeight="1">
-      <c r="A63" s="37"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="34"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="11"/>
-      <c r="AD63" s="12"/>
-    </row>
-    <row r="64" spans="1:30" ht="9" customHeight="1">
-      <c r="A64" s="35">
-        <v>2017</v>
-      </c>
-      <c r="B64" s="25">
+      <c r="B64" s="9">
         <v>6</v>
       </c>
-      <c r="C64" s="38" t="s">
-        <v>30</v>
+      <c r="C64" s="18" t="s">
+        <v>29</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="30"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="20"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-      <c r="O64" s="11"/>
-      <c r="AD64" s="12"/>
+      <c r="O64" s="76"/>
+      <c r="P64" s="77"/>
+      <c r="Q64" s="77"/>
+      <c r="R64" s="77"/>
+      <c r="S64" s="77"/>
+      <c r="T64" s="77"/>
+      <c r="U64" s="77"/>
+      <c r="V64" s="77"/>
+      <c r="W64" s="77"/>
+      <c r="X64" s="77"/>
+      <c r="Y64" s="77"/>
+      <c r="Z64" s="77"/>
+      <c r="AA64" s="77"/>
+      <c r="AB64" s="77"/>
+      <c r="AC64" s="77"/>
+      <c r="AD64" s="78"/>
     </row>
     <row r="65" spans="1:30" ht="9" customHeight="1">
-      <c r="A65" s="36"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="21"/>
+      <c r="A65" s="13"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="23"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
-      <c r="O65" s="13"/>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="14"/>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
-      <c r="T65" s="14"/>
-      <c r="U65" s="14"/>
-      <c r="V65" s="14"/>
-      <c r="W65" s="14"/>
-      <c r="X65" s="14"/>
-      <c r="Y65" s="14"/>
-      <c r="Z65" s="14"/>
-      <c r="AA65" s="14"/>
-      <c r="AB65" s="14"/>
-      <c r="AC65" s="14"/>
-      <c r="AD65" s="15"/>
+      <c r="O65" s="79"/>
+      <c r="P65" s="80"/>
+      <c r="Q65" s="80"/>
+      <c r="R65" s="80"/>
+      <c r="S65" s="80"/>
+      <c r="T65" s="80"/>
+      <c r="U65" s="80"/>
+      <c r="V65" s="80"/>
+      <c r="W65" s="80"/>
+      <c r="X65" s="80"/>
+      <c r="Y65" s="80"/>
+      <c r="Z65" s="80"/>
+      <c r="AA65" s="80"/>
+      <c r="AB65" s="80"/>
+      <c r="AC65" s="80"/>
+      <c r="AD65" s="81"/>
     </row>
     <row r="66" spans="1:30" ht="9" customHeight="1">
-      <c r="A66" s="37"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="34"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="25"/>
+      <c r="L66" s="26"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
@@ -3954,24 +3858,24 @@
       <c r="AD66" s="3"/>
     </row>
     <row r="67" spans="1:30" ht="9" customHeight="1">
-      <c r="A67" s="35">
+      <c r="A67" s="12">
         <v>2019</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B67" s="9">
         <v>4</v>
       </c>
-      <c r="C67" s="28" t="s">
-        <v>29</v>
+      <c r="C67" s="27" t="s">
+        <v>28</v>
       </c>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="30"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="20"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
@@ -3992,628 +3896,628 @@
       <c r="AD67" s="3"/>
     </row>
     <row r="68" spans="1:30" ht="9" customHeight="1">
-      <c r="A68" s="36"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
-      <c r="L68" s="21"/>
+      <c r="A68" s="13"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="23"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="39" t="s">
+      <c r="O68" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="33"/>
+      <c r="R68" s="33"/>
+      <c r="S68" s="33"/>
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="33"/>
+      <c r="W68" s="33"/>
+      <c r="X68" s="33"/>
+      <c r="Y68" s="33"/>
+      <c r="Z68" s="33"/>
+      <c r="AA68" s="33"/>
+      <c r="AB68" s="33"/>
+      <c r="AC68" s="33"/>
+      <c r="AD68" s="34"/>
+    </row>
+    <row r="69" spans="1:30" ht="9" customHeight="1">
+      <c r="A69" s="14"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="40"/>
+      <c r="P69" s="22"/>
+      <c r="Q69" s="22"/>
+      <c r="R69" s="22"/>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
+      <c r="U69" s="22"/>
+      <c r="V69" s="22"/>
+      <c r="W69" s="22"/>
+      <c r="X69" s="22"/>
+      <c r="Y69" s="22"/>
+      <c r="Z69" s="22"/>
+      <c r="AA69" s="22"/>
+      <c r="AB69" s="22"/>
+      <c r="AC69" s="22"/>
+      <c r="AD69" s="23"/>
+    </row>
+    <row r="70" spans="1:30" ht="9" customHeight="1" thickBot="1">
+      <c r="A70" s="12">
+        <v>2019</v>
+      </c>
+      <c r="B70" s="9">
+        <v>10</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="40"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
+      <c r="R70" s="22"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
+      <c r="U70" s="22"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="22"/>
+      <c r="X70" s="22"/>
+      <c r="Y70" s="22"/>
+      <c r="Z70" s="22"/>
+      <c r="AA70" s="22"/>
+      <c r="AB70" s="22"/>
+      <c r="AC70" s="22"/>
+      <c r="AD70" s="23"/>
+    </row>
+    <row r="71" spans="1:30" ht="9" customHeight="1" thickTop="1">
+      <c r="A71" s="13"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="P68" s="40"/>
-      <c r="Q68" s="40"/>
-      <c r="R68" s="40"/>
-      <c r="S68" s="40"/>
-      <c r="T68" s="40"/>
-      <c r="U68" s="40"/>
-      <c r="V68" s="40"/>
-      <c r="W68" s="40"/>
-      <c r="X68" s="40"/>
-      <c r="Y68" s="40"/>
-      <c r="Z68" s="40"/>
-      <c r="AA68" s="40"/>
-      <c r="AB68" s="40"/>
-      <c r="AC68" s="40"/>
-      <c r="AD68" s="41"/>
-    </row>
-    <row r="69" spans="1:30" ht="9" customHeight="1">
-      <c r="A69" s="37"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="34"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="19"/>
-      <c r="P69" s="20"/>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="20"/>
-      <c r="S69" s="20"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="20"/>
-      <c r="V69" s="20"/>
-      <c r="W69" s="20"/>
-      <c r="X69" s="20"/>
-      <c r="Y69" s="20"/>
-      <c r="Z69" s="20"/>
-      <c r="AA69" s="20"/>
-      <c r="AB69" s="20"/>
-      <c r="AC69" s="20"/>
-      <c r="AD69" s="21"/>
-    </row>
-    <row r="70" spans="1:30" ht="9" customHeight="1" thickBot="1">
-      <c r="A70" s="35">
-        <v>2019</v>
+      <c r="P71" s="72"/>
+      <c r="Q71" s="72"/>
+      <c r="R71" s="72"/>
+      <c r="S71" s="72"/>
+      <c r="T71" s="72"/>
+      <c r="U71" s="72"/>
+      <c r="V71" s="72"/>
+      <c r="W71" s="72"/>
+      <c r="X71" s="72"/>
+      <c r="Y71" s="72"/>
+      <c r="Z71" s="72"/>
+      <c r="AA71" s="72"/>
+      <c r="AB71" s="72"/>
+      <c r="AC71" s="72"/>
+      <c r="AD71" s="73"/>
+    </row>
+    <row r="72" spans="1:30" ht="9" customHeight="1">
+      <c r="A72" s="14"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="40"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="22"/>
+      <c r="AA72" s="22"/>
+      <c r="AB72" s="22"/>
+      <c r="AC72" s="22"/>
+      <c r="AD72" s="23"/>
+    </row>
+    <row r="73" spans="1:30" ht="9" customHeight="1">
+      <c r="A73" s="12">
+        <v>2020</v>
       </c>
-      <c r="B70" s="25">
-        <v>10</v>
+      <c r="B73" s="9">
+        <v>3</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C73" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="40"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
+      <c r="R73" s="22"/>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="22"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="22"/>
+      <c r="Y73" s="22"/>
+      <c r="Z73" s="22"/>
+      <c r="AA73" s="22"/>
+      <c r="AB73" s="22"/>
+      <c r="AC73" s="22"/>
+      <c r="AD73" s="23"/>
+    </row>
+    <row r="74" spans="1:30" ht="9" customHeight="1">
+      <c r="A74" s="13"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="40"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="22"/>
+      <c r="AA74" s="22"/>
+      <c r="AB74" s="22"/>
+      <c r="AC74" s="22"/>
+      <c r="AD74" s="23"/>
+    </row>
+    <row r="75" spans="1:30" ht="9" customHeight="1">
+      <c r="A75" s="14"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="40"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="22"/>
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="22"/>
+      <c r="AC75" s="22"/>
+      <c r="AD75" s="23"/>
+    </row>
+    <row r="76" spans="1:30" ht="9" customHeight="1">
+      <c r="A76" s="12">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="9">
+        <v>3</v>
+      </c>
+      <c r="C76" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="20"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="40"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="22"/>
+      <c r="Y76" s="22"/>
+      <c r="Z76" s="22"/>
+      <c r="AA76" s="22"/>
+      <c r="AB76" s="22"/>
+      <c r="AC76" s="22"/>
+      <c r="AD76" s="23"/>
+    </row>
+    <row r="77" spans="1:30" ht="9" customHeight="1">
+      <c r="A77" s="50"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="22"/>
+      <c r="L77" s="23"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="40"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="W77" s="22"/>
+      <c r="X77" s="22"/>
+      <c r="Y77" s="22"/>
+      <c r="Z77" s="22"/>
+      <c r="AA77" s="22"/>
+      <c r="AB77" s="22"/>
+      <c r="AC77" s="22"/>
+      <c r="AD77" s="23"/>
+    </row>
+    <row r="78" spans="1:30" ht="9" customHeight="1">
+      <c r="A78" s="51"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="40"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
+      <c r="U78" s="22"/>
+      <c r="V78" s="22"/>
+      <c r="W78" s="22"/>
+      <c r="X78" s="22"/>
+      <c r="Y78" s="22"/>
+      <c r="Z78" s="22"/>
+      <c r="AA78" s="22"/>
+      <c r="AB78" s="22"/>
+      <c r="AC78" s="22"/>
+      <c r="AD78" s="23"/>
+    </row>
+    <row r="79" spans="1:30" ht="9" customHeight="1">
+      <c r="A79" s="12">
+        <v>2021</v>
+      </c>
+      <c r="B79" s="9">
+        <v>4</v>
+      </c>
+      <c r="C79" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="19"/>
-      <c r="P70" s="20"/>
-      <c r="Q70" s="20"/>
-      <c r="R70" s="20"/>
-      <c r="S70" s="20"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="20"/>
-      <c r="V70" s="20"/>
-      <c r="W70" s="20"/>
-      <c r="X70" s="20"/>
-      <c r="Y70" s="20"/>
-      <c r="Z70" s="20"/>
-      <c r="AA70" s="20"/>
-      <c r="AB70" s="20"/>
-      <c r="AC70" s="20"/>
-      <c r="AD70" s="21"/>
-    </row>
-    <row r="71" spans="1:30" ht="9" customHeight="1" thickTop="1">
-      <c r="A71" s="36"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="16" t="s">
-        <v>12</v>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="40"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="T79" s="22"/>
+      <c r="U79" s="22"/>
+      <c r="V79" s="22"/>
+      <c r="W79" s="22"/>
+      <c r="X79" s="22"/>
+      <c r="Y79" s="22"/>
+      <c r="Z79" s="22"/>
+      <c r="AA79" s="22"/>
+      <c r="AB79" s="22"/>
+      <c r="AC79" s="22"/>
+      <c r="AD79" s="23"/>
+    </row>
+    <row r="80" spans="1:30" ht="9" customHeight="1">
+      <c r="A80" s="13"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="23"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="40"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="T80" s="22"/>
+      <c r="U80" s="22"/>
+      <c r="V80" s="22"/>
+      <c r="W80" s="22"/>
+      <c r="X80" s="22"/>
+      <c r="Y80" s="22"/>
+      <c r="Z80" s="22"/>
+      <c r="AA80" s="22"/>
+      <c r="AB80" s="22"/>
+      <c r="AC80" s="22"/>
+      <c r="AD80" s="23"/>
+    </row>
+    <row r="81" spans="1:30" ht="9" customHeight="1">
+      <c r="A81" s="14"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="40"/>
+      <c r="P81" s="22"/>
+      <c r="Q81" s="22"/>
+      <c r="R81" s="22"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
+      <c r="U81" s="22"/>
+      <c r="V81" s="22"/>
+      <c r="W81" s="22"/>
+      <c r="X81" s="22"/>
+      <c r="Y81" s="22"/>
+      <c r="Z81" s="22"/>
+      <c r="AA81" s="22"/>
+      <c r="AB81" s="22"/>
+      <c r="AC81" s="22"/>
+      <c r="AD81" s="23"/>
+    </row>
+    <row r="82" spans="1:30" ht="14">
+      <c r="A82" s="12">
+        <v>2025</v>
       </c>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-      <c r="W71" s="17"/>
-      <c r="X71" s="17"/>
-      <c r="Y71" s="17"/>
-      <c r="Z71" s="17"/>
-      <c r="AA71" s="17"/>
-      <c r="AB71" s="17"/>
-      <c r="AC71" s="17"/>
-      <c r="AD71" s="18"/>
-    </row>
-    <row r="72" spans="1:30" ht="9" customHeight="1">
-      <c r="A72" s="37"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="34"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="19"/>
-      <c r="P72" s="20"/>
-      <c r="Q72" s="20"/>
-      <c r="R72" s="20"/>
-      <c r="S72" s="20"/>
-      <c r="T72" s="20"/>
-      <c r="U72" s="20"/>
-      <c r="V72" s="20"/>
-      <c r="W72" s="20"/>
-      <c r="X72" s="20"/>
-      <c r="Y72" s="20"/>
-      <c r="Z72" s="20"/>
-      <c r="AA72" s="20"/>
-      <c r="AB72" s="20"/>
-      <c r="AC72" s="20"/>
-      <c r="AD72" s="21"/>
-    </row>
-    <row r="73" spans="1:30" ht="9" customHeight="1">
-      <c r="A73" s="35">
-        <v>2020</v>
+      <c r="B82" s="9">
+        <v>9</v>
       </c>
-      <c r="B73" s="25">
-        <v>3</v>
-      </c>
-      <c r="C73" s="28" t="s">
+      <c r="C82" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="29"/>
-      <c r="L73" s="30"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="19"/>
-      <c r="P73" s="20"/>
-      <c r="Q73" s="20"/>
-      <c r="R73" s="20"/>
-      <c r="S73" s="20"/>
-      <c r="T73" s="20"/>
-      <c r="U73" s="20"/>
-      <c r="V73" s="20"/>
-      <c r="W73" s="20"/>
-      <c r="X73" s="20"/>
-      <c r="Y73" s="20"/>
-      <c r="Z73" s="20"/>
-      <c r="AA73" s="20"/>
-      <c r="AB73" s="20"/>
-      <c r="AC73" s="20"/>
-      <c r="AD73" s="21"/>
-    </row>
-    <row r="74" spans="1:30" ht="9" customHeight="1">
-      <c r="A74" s="36"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-      <c r="K74" s="20"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="19"/>
-      <c r="P74" s="20"/>
-      <c r="Q74" s="20"/>
-      <c r="R74" s="20"/>
-      <c r="S74" s="20"/>
-      <c r="T74" s="20"/>
-      <c r="U74" s="20"/>
-      <c r="V74" s="20"/>
-      <c r="W74" s="20"/>
-      <c r="X74" s="20"/>
-      <c r="Y74" s="20"/>
-      <c r="Z74" s="20"/>
-      <c r="AA74" s="20"/>
-      <c r="AB74" s="20"/>
-      <c r="AC74" s="20"/>
-      <c r="AD74" s="21"/>
-    </row>
-    <row r="75" spans="1:30" ht="9" customHeight="1">
-      <c r="A75" s="37"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="33"/>
-      <c r="L75" s="34"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="19"/>
-      <c r="P75" s="20"/>
-      <c r="Q75" s="20"/>
-      <c r="R75" s="20"/>
-      <c r="S75" s="20"/>
-      <c r="T75" s="20"/>
-      <c r="U75" s="20"/>
-      <c r="V75" s="20"/>
-      <c r="W75" s="20"/>
-      <c r="X75" s="20"/>
-      <c r="Y75" s="20"/>
-      <c r="Z75" s="20"/>
-      <c r="AA75" s="20"/>
-      <c r="AB75" s="20"/>
-      <c r="AC75" s="20"/>
-      <c r="AD75" s="21"/>
-    </row>
-    <row r="76" spans="1:30" ht="9" customHeight="1">
-      <c r="A76" s="35">
-        <v>2021</v>
-      </c>
-      <c r="B76" s="25">
-        <v>3</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
-      <c r="L76" s="30"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="19"/>
-      <c r="P76" s="20"/>
-      <c r="Q76" s="20"/>
-      <c r="R76" s="20"/>
-      <c r="S76" s="20"/>
-      <c r="T76" s="20"/>
-      <c r="U76" s="20"/>
-      <c r="V76" s="20"/>
-      <c r="W76" s="20"/>
-      <c r="X76" s="20"/>
-      <c r="Y76" s="20"/>
-      <c r="Z76" s="20"/>
-      <c r="AA76" s="20"/>
-      <c r="AB76" s="20"/>
-      <c r="AC76" s="20"/>
-      <c r="AD76" s="21"/>
-    </row>
-    <row r="77" spans="1:30" ht="9" customHeight="1">
-      <c r="A77" s="46"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="20"/>
-      <c r="K77" s="20"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="19"/>
-      <c r="P77" s="20"/>
-      <c r="Q77" s="20"/>
-      <c r="R77" s="20"/>
-      <c r="S77" s="20"/>
-      <c r="T77" s="20"/>
-      <c r="U77" s="20"/>
-      <c r="V77" s="20"/>
-      <c r="W77" s="20"/>
-      <c r="X77" s="20"/>
-      <c r="Y77" s="20"/>
-      <c r="Z77" s="20"/>
-      <c r="AA77" s="20"/>
-      <c r="AB77" s="20"/>
-      <c r="AC77" s="20"/>
-      <c r="AD77" s="21"/>
-    </row>
-    <row r="78" spans="1:30" ht="9" customHeight="1">
-      <c r="A78" s="82"/>
-      <c r="B78" s="83"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="33"/>
-      <c r="J78" s="33"/>
-      <c r="K78" s="33"/>
-      <c r="L78" s="34"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="19"/>
-      <c r="P78" s="20"/>
-      <c r="Q78" s="20"/>
-      <c r="R78" s="20"/>
-      <c r="S78" s="20"/>
-      <c r="T78" s="20"/>
-      <c r="U78" s="20"/>
-      <c r="V78" s="20"/>
-      <c r="W78" s="20"/>
-      <c r="X78" s="20"/>
-      <c r="Y78" s="20"/>
-      <c r="Z78" s="20"/>
-      <c r="AA78" s="20"/>
-      <c r="AB78" s="20"/>
-      <c r="AC78" s="20"/>
-      <c r="AD78" s="21"/>
-    </row>
-    <row r="79" spans="1:30" ht="9" customHeight="1">
-      <c r="A79" s="35">
-        <v>2021</v>
-      </c>
-      <c r="B79" s="25">
-        <v>4</v>
-      </c>
-      <c r="C79" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="29"/>
-      <c r="L79" s="30"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="19"/>
-      <c r="P79" s="20"/>
-      <c r="Q79" s="20"/>
-      <c r="R79" s="20"/>
-      <c r="S79" s="20"/>
-      <c r="T79" s="20"/>
-      <c r="U79" s="20"/>
-      <c r="V79" s="20"/>
-      <c r="W79" s="20"/>
-      <c r="X79" s="20"/>
-      <c r="Y79" s="20"/>
-      <c r="Z79" s="20"/>
-      <c r="AA79" s="20"/>
-      <c r="AB79" s="20"/>
-      <c r="AC79" s="20"/>
-      <c r="AD79" s="21"/>
-    </row>
-    <row r="80" spans="1:30" ht="9" customHeight="1">
-      <c r="A80" s="36"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="20"/>
-      <c r="K80" s="20"/>
-      <c r="L80" s="21"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3"/>
-      <c r="O80" s="19"/>
-      <c r="P80" s="20"/>
-      <c r="Q80" s="20"/>
-      <c r="R80" s="20"/>
-      <c r="S80" s="20"/>
-      <c r="T80" s="20"/>
-      <c r="U80" s="20"/>
-      <c r="V80" s="20"/>
-      <c r="W80" s="20"/>
-      <c r="X80" s="20"/>
-      <c r="Y80" s="20"/>
-      <c r="Z80" s="20"/>
-      <c r="AA80" s="20"/>
-      <c r="AB80" s="20"/>
-      <c r="AC80" s="20"/>
-      <c r="AD80" s="21"/>
-    </row>
-    <row r="81" spans="1:30" ht="9" customHeight="1">
-      <c r="A81" s="37"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="32"/>
-      <c r="D81" s="33"/>
-      <c r="E81" s="33"/>
-      <c r="F81" s="33"/>
-      <c r="G81" s="33"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="33"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="34"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
-      <c r="O81" s="19"/>
-      <c r="P81" s="20"/>
-      <c r="Q81" s="20"/>
-      <c r="R81" s="20"/>
-      <c r="S81" s="20"/>
-      <c r="T81" s="20"/>
-      <c r="U81" s="20"/>
-      <c r="V81" s="20"/>
-      <c r="W81" s="20"/>
-      <c r="X81" s="20"/>
-      <c r="Y81" s="20"/>
-      <c r="Z81" s="20"/>
-      <c r="AA81" s="20"/>
-      <c r="AB81" s="20"/>
-      <c r="AC81" s="20"/>
-      <c r="AD81" s="21"/>
-    </row>
-    <row r="82" spans="1:30" ht="14">
-      <c r="A82" s="35">
-        <v>2025</v>
-      </c>
-      <c r="B82" s="25">
-        <v>9</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
-      <c r="L82" s="30"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="20"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="19"/>
-      <c r="P82" s="20"/>
-      <c r="Q82" s="20"/>
-      <c r="R82" s="20"/>
-      <c r="S82" s="20"/>
-      <c r="T82" s="20"/>
-      <c r="U82" s="20"/>
-      <c r="V82" s="20"/>
-      <c r="W82" s="20"/>
-      <c r="X82" s="20"/>
-      <c r="Y82" s="20"/>
-      <c r="Z82" s="20"/>
-      <c r="AA82" s="20"/>
-      <c r="AB82" s="20"/>
-      <c r="AC82" s="20"/>
-      <c r="AD82" s="21"/>
+      <c r="O82" s="40"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="T82" s="22"/>
+      <c r="U82" s="22"/>
+      <c r="V82" s="22"/>
+      <c r="W82" s="22"/>
+      <c r="X82" s="22"/>
+      <c r="Y82" s="22"/>
+      <c r="Z82" s="22"/>
+      <c r="AA82" s="22"/>
+      <c r="AB82" s="22"/>
+      <c r="AC82" s="22"/>
+      <c r="AD82" s="23"/>
     </row>
     <row r="83" spans="1:30" ht="14">
-      <c r="A83" s="36"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
-      <c r="L83" s="21"/>
+      <c r="A83" s="13"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="22"/>
+      <c r="J83" s="22"/>
+      <c r="K83" s="22"/>
+      <c r="L83" s="23"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="19"/>
-      <c r="P83" s="20"/>
-      <c r="Q83" s="20"/>
-      <c r="R83" s="20"/>
-      <c r="S83" s="20"/>
-      <c r="T83" s="20"/>
-      <c r="U83" s="20"/>
-      <c r="V83" s="20"/>
-      <c r="W83" s="20"/>
-      <c r="X83" s="20"/>
-      <c r="Y83" s="20"/>
-      <c r="Z83" s="20"/>
-      <c r="AA83" s="20"/>
-      <c r="AB83" s="20"/>
-      <c r="AC83" s="20"/>
-      <c r="AD83" s="21"/>
+      <c r="O83" s="40"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="T83" s="22"/>
+      <c r="U83" s="22"/>
+      <c r="V83" s="22"/>
+      <c r="W83" s="22"/>
+      <c r="X83" s="22"/>
+      <c r="Y83" s="22"/>
+      <c r="Z83" s="22"/>
+      <c r="AA83" s="22"/>
+      <c r="AB83" s="22"/>
+      <c r="AC83" s="22"/>
+      <c r="AD83" s="23"/>
     </row>
     <row r="84" spans="1:30" ht="14">
-      <c r="A84" s="37"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="33"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="33"/>
-      <c r="J84" s="33"/>
-      <c r="K84" s="33"/>
-      <c r="L84" s="34"/>
+      <c r="A84" s="14"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+      <c r="L84" s="26"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-      <c r="O84" s="19"/>
-      <c r="P84" s="20"/>
-      <c r="Q84" s="20"/>
-      <c r="R84" s="20"/>
-      <c r="S84" s="20"/>
-      <c r="T84" s="20"/>
-      <c r="U84" s="20"/>
-      <c r="V84" s="20"/>
-      <c r="W84" s="20"/>
-      <c r="X84" s="20"/>
-      <c r="Y84" s="20"/>
-      <c r="Z84" s="20"/>
-      <c r="AA84" s="20"/>
-      <c r="AB84" s="20"/>
-      <c r="AC84" s="20"/>
-      <c r="AD84" s="21"/>
+      <c r="O84" s="40"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="T84" s="22"/>
+      <c r="U84" s="22"/>
+      <c r="V84" s="22"/>
+      <c r="W84" s="22"/>
+      <c r="X84" s="22"/>
+      <c r="Y84" s="22"/>
+      <c r="Z84" s="22"/>
+      <c r="AA84" s="22"/>
+      <c r="AB84" s="22"/>
+      <c r="AC84" s="22"/>
+      <c r="AD84" s="23"/>
     </row>
     <row r="85" spans="1:30" ht="9" customHeight="1">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="40"/>
-      <c r="J85" s="40"/>
-      <c r="K85" s="40"/>
-      <c r="L85" s="40"/>
+      <c r="A85" s="74"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="33"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="33"/>
+      <c r="G85" s="33"/>
+      <c r="H85" s="33"/>
+      <c r="I85" s="33"/>
+      <c r="J85" s="33"/>
+      <c r="K85" s="33"/>
+      <c r="L85" s="33"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="22"/>
-      <c r="P85" s="23"/>
-      <c r="Q85" s="23"/>
-      <c r="R85" s="23"/>
-      <c r="S85" s="23"/>
-      <c r="T85" s="23"/>
-      <c r="U85" s="23"/>
-      <c r="V85" s="23"/>
-      <c r="W85" s="23"/>
-      <c r="X85" s="23"/>
-      <c r="Y85" s="23"/>
-      <c r="Z85" s="23"/>
-      <c r="AA85" s="23"/>
-      <c r="AB85" s="23"/>
-      <c r="AC85" s="23"/>
-      <c r="AD85" s="24"/>
+      <c r="O85" s="41"/>
+      <c r="P85" s="37"/>
+      <c r="Q85" s="37"/>
+      <c r="R85" s="37"/>
+      <c r="S85" s="37"/>
+      <c r="T85" s="37"/>
+      <c r="U85" s="37"/>
+      <c r="V85" s="37"/>
+      <c r="W85" s="37"/>
+      <c r="X85" s="37"/>
+      <c r="Y85" s="37"/>
+      <c r="Z85" s="37"/>
+      <c r="AA85" s="37"/>
+      <c r="AB85" s="37"/>
+      <c r="AC85" s="37"/>
+      <c r="AD85" s="38"/>
     </row>
     <row r="86" spans="1:30" ht="9" customHeight="1">
-      <c r="A86" s="20"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="20"/>
-      <c r="K86" s="20"/>
-      <c r="L86" s="20"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="22"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="22"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
@@ -33490,89 +33394,7 @@
       <c r="N1000" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="106">
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:L60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C61:L63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:L66"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:L33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="O22:O24"/>
-    <mergeCell ref="P22:P24"/>
-    <mergeCell ref="O13:O15"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B19:J20"/>
-    <mergeCell ref="B21:J22"/>
-    <mergeCell ref="B10:I15"/>
-    <mergeCell ref="A16:G18"/>
-    <mergeCell ref="H16:I18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="B23:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:L75"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:L54"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:L42"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="C76:L78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="O1:O3"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="Q1:AD3"/>
-    <mergeCell ref="F2:I3"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="F5:I6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:I9"/>
-    <mergeCell ref="Q4:AD6"/>
-    <mergeCell ref="Q7:AD9"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="P4:P6"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q10:AD12"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:L69"/>
-    <mergeCell ref="Q13:AD15"/>
-    <mergeCell ref="Q16:AD18"/>
-    <mergeCell ref="Q19:AD21"/>
-    <mergeCell ref="Q22:AD24"/>
-    <mergeCell ref="O26:AD28"/>
-    <mergeCell ref="O29:AD46"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:L39"/>
-    <mergeCell ref="C28:L30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:L36"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A31:A33"/>
+  <mergeCells count="107">
     <mergeCell ref="O71:AD85"/>
     <mergeCell ref="B82:B84"/>
     <mergeCell ref="C82:L84"/>
@@ -33597,10 +33419,92 @@
     <mergeCell ref="A79:A81"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="C79:L81"/>
+    <mergeCell ref="Q19:AD21"/>
+    <mergeCell ref="Q22:AD24"/>
+    <mergeCell ref="O26:AD28"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:L39"/>
+    <mergeCell ref="C28:L30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:L36"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="O29:AD65"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="Q1:AD3"/>
+    <mergeCell ref="F2:I3"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="F5:I6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:I9"/>
+    <mergeCell ref="Q4:AD6"/>
+    <mergeCell ref="Q7:AD9"/>
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="P4:P6"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="K4:L17"/>
+    <mergeCell ref="Q10:AD12"/>
+    <mergeCell ref="Q13:AD15"/>
+    <mergeCell ref="Q16:AD18"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:L75"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:L54"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:L42"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="C76:L78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:L63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:L66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="C67:L69"/>
+    <mergeCell ref="P22:P24"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:L60"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:L33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B19:J20"/>
+    <mergeCell ref="B21:J22"/>
+    <mergeCell ref="B10:I15"/>
+    <mergeCell ref="A16:G18"/>
+    <mergeCell ref="H16:I18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="B23:J26"/>
+    <mergeCell ref="K25:L26"/>
   </mergeCells>
-  <phoneticPr fontId="9"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/履歴書・職務経歴書/履歴書.xlsx
+++ b/履歴書・職務経歴書/履歴書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Documents/GitHub/private/履歴書・職務経歴書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C4960-ECA5-9A49-903C-D0E5F5DDF555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BF0533-4E9D-524F-B80E-3D6A6B75614C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="28800" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書フォーマット" sheetId="1" r:id="rId1"/>
@@ -427,13 +427,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>　　　令和7　年　3　　月　　16　日現在</t>
-    <rPh sb="3" eb="5">
-      <t>レイワ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>1984年　　　　9　月　　　　1　日生　（満　　41　歳）　</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -445,6 +438,13 @@
     <t>教職からWEB業界へ転身し、サポートエンジニアから制作、ディレクションまで経験を積んできました。
 前職では取締役としてリユース事業全体を統括し、主要ECモールの運営やSEO施策、チームマネジメント、採用にいたるまで幅広く従事。実務面においても、VBA等を活用したDX推進によりオペレーションコストの削減を実現するなど、経営・現場両方の視点から事業の成長と組織の安定化に尽力しました。 
 これまでのWeb・EC領域における実務経験とマネジメント実績を活かしつつ、新しい環境や未経験の領域にも柔軟かつ積極的に挑戦し、貴社の事業発展に貢献したいと考えております。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>　　　令和8　年　3　　月　　16　日現在</t>
+    <rPh sb="3" eb="5">
+      <t>レイワ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1057,13 +1057,61 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1075,59 +1123,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1135,86 +1135,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1243,28 +1168,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1276,8 +1207,77 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1594,9 +1594,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="9" customHeight="1">
-      <c r="A1" s="54"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1608,93 +1608,93 @@
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
     </row>
     <row r="2" spans="1:30" ht="9" customHeight="1">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
     </row>
     <row r="3" spans="1:30" ht="9" customHeight="1">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
     </row>
     <row r="4" spans="1:30" ht="9" customHeight="1">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2"/>
       <c r="F4" s="5"/>
@@ -1702,19 +1702,19 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="55" t="e" vm="1">
+      <c r="K4" s="60" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="L4" s="55"/>
+      <c r="L4" s="60"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="57" t="s">
+      <c r="Q4" s="46" t="s">
         <v>8</v>
       </c>
       <c r="R4" s="33"/>
@@ -1732,70 +1732,70 @@
       <c r="AD4" s="34"/>
     </row>
     <row r="5" spans="1:30" ht="9" customHeight="1">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="56" t="s">
-        <v>42</v>
+      <c r="F5" s="61" t="s">
+        <v>45</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="23"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="14"/>
     </row>
     <row r="6" spans="1:30" ht="9" customHeight="1" thickBot="1">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="59"/>
-      <c r="W6" s="59"/>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="60"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="48"/>
+      <c r="AD6" s="49"/>
     </row>
     <row r="7" spans="1:30" ht="9" customHeight="1" thickTop="1">
       <c r="A7" s="2"/>
@@ -1808,38 +1808,38 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="50">
+      <c r="O7" s="69">
         <v>2008</v>
       </c>
-      <c r="P7" s="52">
+      <c r="P7" s="70">
         <v>3</v>
       </c>
-      <c r="Q7" s="61" t="s">
+      <c r="Q7" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="23"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="14"/>
     </row>
     <row r="8" spans="1:30" ht="9" customHeight="1">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="63" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="33"/>
@@ -1850,270 +1850,270 @@
       <c r="H8" s="33"/>
       <c r="I8" s="34"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="23"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="14"/>
     </row>
     <row r="9" spans="1:30" ht="9" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="27"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="26"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="27"/>
     </row>
     <row r="10" spans="1:30" ht="9" customHeight="1">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="50">
+      <c r="O10" s="69">
         <v>2008</v>
       </c>
-      <c r="P10" s="52">
+      <c r="P10" s="70">
         <v>3</v>
       </c>
-      <c r="Q10" s="61" t="s">
+      <c r="Q10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="23"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="14"/>
     </row>
     <row r="11" spans="1:30" ht="9" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="23"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="23"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="14"/>
     </row>
     <row r="12" spans="1:30" ht="9" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="26"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
+      <c r="AC12" s="26"/>
+      <c r="AD12" s="27"/>
     </row>
     <row r="13" spans="1:30" ht="9" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="23"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="12">
+      <c r="O13" s="28">
         <v>2010</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="18">
         <v>3</v>
       </c>
-      <c r="Q13" s="27" t="s">
+      <c r="Q13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="20"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="23"/>
     </row>
     <row r="14" spans="1:30" ht="9" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="23"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="14"/>
     </row>
     <row r="15" spans="1:30" ht="9" customHeight="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="38"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="17"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="26"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="27"/>
     </row>
     <row r="16" spans="1:30" ht="9" customHeight="1">
-      <c r="A16" s="39" t="s">
-        <v>43</v>
+      <c r="A16" s="76" t="s">
+        <v>42</v>
       </c>
       <c r="B16" s="33"/>
       <c r="C16" s="33"/>
@@ -2121,107 +2121,107 @@
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
       <c r="G16" s="34"/>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="32" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="34"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="12">
+      <c r="O16" s="28">
         <v>2010</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="18">
         <v>3</v>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="20"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="23"/>
     </row>
     <row r="17" spans="1:30" ht="9" customHeight="1">
-      <c r="A17" s="40"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="23"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="23"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="14"/>
     </row>
     <row r="18" spans="1:30" ht="9" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="38"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="17"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="25"/>
-      <c r="Y18" s="25"/>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="25"/>
-      <c r="AD18" s="26"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
+      <c r="AC18" s="26"/>
+      <c r="AD18" s="27"/>
     </row>
     <row r="19" spans="1:30" ht="9" customHeight="1">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="32"/>
+      <c r="B19" s="63"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
       <c r="E19" s="33"/>
@@ -2230,220 +2230,220 @@
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
       <c r="J19" s="34"/>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="77" t="s">
         <v>5</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="12">
+      <c r="O19" s="28">
         <v>2010</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="18">
         <v>3</v>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="Q19" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="20"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="23"/>
     </row>
     <row r="20" spans="1:30" ht="9" customHeight="1">
-      <c r="A20" s="14"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="23"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="14"/>
       <c r="M20" s="7"/>
       <c r="N20" s="8"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="22"/>
-      <c r="X20" s="22"/>
-      <c r="Y20" s="22"/>
-      <c r="Z20" s="22"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="22"/>
-      <c r="AC20" s="22"/>
-      <c r="AD20" s="23"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="14"/>
     </row>
     <row r="21" spans="1:30" ht="9" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="69" t="s">
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="20"/>
+      <c r="L21" s="23"/>
       <c r="M21" s="7"/>
       <c r="N21" s="8"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
-      <c r="AC21" s="25"/>
-      <c r="AD21" s="26"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="26"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="26"/>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="26"/>
+      <c r="AA21" s="26"/>
+      <c r="AB21" s="26"/>
+      <c r="AC21" s="26"/>
+      <c r="AD21" s="27"/>
     </row>
     <row r="22" spans="1:30" ht="9" customHeight="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="38"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="17"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="20"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="23"/>
     </row>
     <row r="23" spans="1:30" ht="9" customHeight="1">
-      <c r="A23" s="13"/>
-      <c r="B23" s="45" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="70" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="23"/>
+      <c r="L23" s="14"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="23"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="14"/>
     </row>
     <row r="24" spans="1:30" ht="9" customHeight="1">
-      <c r="A24" s="13"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="23"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="14"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="37"/>
-      <c r="S24" s="37"/>
-      <c r="T24" s="37"/>
-      <c r="U24" s="37"/>
-      <c r="V24" s="37"/>
-      <c r="W24" s="37"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="37"/>
-      <c r="Z24" s="37"/>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="37"/>
-      <c r="AD24" s="38"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="16"/>
+      <c r="AB24" s="16"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="17"/>
     </row>
     <row r="25" spans="1:30" ht="9" customHeight="1">
-      <c r="A25" s="13"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="46" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2464,38 +2464,38 @@
       <c r="AD25" s="3"/>
     </row>
     <row r="26" spans="1:30" ht="9" customHeight="1">
-      <c r="A26" s="17"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="49"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="82"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="63" t="s">
-        <v>44</v>
+      <c r="O26" s="38" t="s">
+        <v>43</v>
       </c>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="64"/>
-      <c r="R26" s="64"/>
-      <c r="S26" s="64"/>
-      <c r="T26" s="64"/>
-      <c r="U26" s="64"/>
-      <c r="V26" s="64"/>
-      <c r="W26" s="64"/>
-      <c r="X26" s="64"/>
-      <c r="Y26" s="64"/>
-      <c r="Z26" s="64"/>
-      <c r="AA26" s="64"/>
-      <c r="AB26" s="64"/>
-      <c r="AC26" s="64"/>
-      <c r="AD26" s="65"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="40"/>
     </row>
     <row r="27" spans="1:30" ht="9" customHeight="1">
       <c r="A27" s="3"/>
@@ -2512,31 +2512,31 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="67"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="42"/>
     </row>
     <row r="28" spans="1:30" ht="9" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="46" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="33"/>
@@ -2550,1294 +2550,1294 @@
       <c r="L28" s="34"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="68"/>
-      <c r="Q28" s="68"/>
-      <c r="R28" s="68"/>
-      <c r="S28" s="68"/>
-      <c r="T28" s="68"/>
-      <c r="U28" s="68"/>
-      <c r="V28" s="68"/>
-      <c r="W28" s="68"/>
-      <c r="X28" s="68"/>
-      <c r="Y28" s="68"/>
-      <c r="Z28" s="68"/>
-      <c r="AA28" s="68"/>
-      <c r="AB28" s="68"/>
-      <c r="AC28" s="68"/>
-      <c r="AD28" s="67"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43"/>
+      <c r="X28" s="43"/>
+      <c r="Y28" s="43"/>
+      <c r="Z28" s="43"/>
+      <c r="AA28" s="43"/>
+      <c r="AB28" s="43"/>
+      <c r="AC28" s="43"/>
+      <c r="AD28" s="42"/>
     </row>
     <row r="29" spans="1:30" ht="9" customHeight="1">
-      <c r="A29" s="13"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="23"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="14"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="82" t="s">
-        <v>45</v>
+      <c r="O29" s="52" t="s">
+        <v>44</v>
       </c>
-      <c r="P29" s="77"/>
-      <c r="Q29" s="77"/>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="77"/>
-      <c r="W29" s="77"/>
-      <c r="X29" s="77"/>
-      <c r="Y29" s="77"/>
-      <c r="Z29" s="77"/>
-      <c r="AA29" s="77"/>
-      <c r="AB29" s="77"/>
-      <c r="AC29" s="77"/>
-      <c r="AD29" s="78"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="53"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="53"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="53"/>
+      <c r="Z29" s="53"/>
+      <c r="AA29" s="53"/>
+      <c r="AB29" s="53"/>
+      <c r="AC29" s="53"/>
+      <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="9" customHeight="1" thickBot="1">
-      <c r="A30" s="29"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="60"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="49"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="77"/>
-      <c r="Q30" s="77"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="77"/>
-      <c r="U30" s="77"/>
-      <c r="V30" s="77"/>
-      <c r="W30" s="77"/>
-      <c r="X30" s="77"/>
-      <c r="Y30" s="77"/>
-      <c r="Z30" s="77"/>
-      <c r="AA30" s="77"/>
-      <c r="AB30" s="77"/>
-      <c r="AC30" s="77"/>
-      <c r="AD30" s="78"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
+      <c r="U30" s="53"/>
+      <c r="V30" s="53"/>
+      <c r="W30" s="53"/>
+      <c r="X30" s="53"/>
+      <c r="Y30" s="53"/>
+      <c r="Z30" s="53"/>
+      <c r="AA30" s="53"/>
+      <c r="AB30" s="53"/>
+      <c r="AC30" s="53"/>
+      <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="9" customHeight="1" thickTop="1">
-      <c r="A31" s="12">
+      <c r="A31" s="28">
         <v>2003</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="18">
         <v>3</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="20"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="23"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="77"/>
-      <c r="R31" s="77"/>
-      <c r="S31" s="77"/>
-      <c r="T31" s="77"/>
-      <c r="U31" s="77"/>
-      <c r="V31" s="77"/>
-      <c r="W31" s="77"/>
-      <c r="X31" s="77"/>
-      <c r="Y31" s="77"/>
-      <c r="Z31" s="77"/>
-      <c r="AA31" s="77"/>
-      <c r="AB31" s="77"/>
-      <c r="AC31" s="77"/>
-      <c r="AD31" s="78"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="53"/>
+      <c r="U31" s="53"/>
+      <c r="V31" s="53"/>
+      <c r="W31" s="53"/>
+      <c r="X31" s="53"/>
+      <c r="Y31" s="53"/>
+      <c r="Z31" s="53"/>
+      <c r="AA31" s="53"/>
+      <c r="AB31" s="53"/>
+      <c r="AC31" s="53"/>
+      <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="9" customHeight="1">
-      <c r="A32" s="13"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="23"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="14"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="77"/>
-      <c r="W32" s="77"/>
-      <c r="X32" s="77"/>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="77"/>
-      <c r="AA32" s="77"/>
-      <c r="AB32" s="77"/>
-      <c r="AC32" s="77"/>
-      <c r="AD32" s="78"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
+      <c r="U32" s="53"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="53"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="53"/>
+      <c r="Z32" s="53"/>
+      <c r="AA32" s="53"/>
+      <c r="AB32" s="53"/>
+      <c r="AC32" s="53"/>
+      <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="9" customHeight="1">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="26"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="77"/>
-      <c r="Q33" s="77"/>
-      <c r="R33" s="77"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="77"/>
-      <c r="U33" s="77"/>
-      <c r="V33" s="77"/>
-      <c r="W33" s="77"/>
-      <c r="X33" s="77"/>
-      <c r="Y33" s="77"/>
-      <c r="Z33" s="77"/>
-      <c r="AA33" s="77"/>
-      <c r="AB33" s="77"/>
-      <c r="AC33" s="77"/>
-      <c r="AD33" s="78"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
+      <c r="U33" s="53"/>
+      <c r="V33" s="53"/>
+      <c r="W33" s="53"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="53"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="53"/>
+      <c r="AB33" s="53"/>
+      <c r="AC33" s="53"/>
+      <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="9" customHeight="1">
-      <c r="A34" s="12">
+      <c r="A34" s="28">
         <v>2008</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="18">
         <v>3</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="20"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="23"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="77"/>
-      <c r="Q34" s="77"/>
-      <c r="R34" s="77"/>
-      <c r="S34" s="77"/>
-      <c r="T34" s="77"/>
-      <c r="U34" s="77"/>
-      <c r="V34" s="77"/>
-      <c r="W34" s="77"/>
-      <c r="X34" s="77"/>
-      <c r="Y34" s="77"/>
-      <c r="Z34" s="77"/>
-      <c r="AA34" s="77"/>
-      <c r="AB34" s="77"/>
-      <c r="AC34" s="77"/>
-      <c r="AD34" s="78"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="53"/>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="53"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="53"/>
+      <c r="V34" s="53"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="53"/>
+      <c r="Y34" s="53"/>
+      <c r="Z34" s="53"/>
+      <c r="AA34" s="53"/>
+      <c r="AB34" s="53"/>
+      <c r="AC34" s="53"/>
+      <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="9" customHeight="1">
-      <c r="A35" s="13"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="23"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="14"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="77"/>
-      <c r="Q35" s="77"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="77"/>
-      <c r="U35" s="77"/>
-      <c r="V35" s="77"/>
-      <c r="W35" s="77"/>
-      <c r="X35" s="77"/>
-      <c r="Y35" s="77"/>
-      <c r="Z35" s="77"/>
-      <c r="AA35" s="77"/>
-      <c r="AB35" s="77"/>
-      <c r="AC35" s="77"/>
-      <c r="AD35" s="78"/>
+      <c r="O35" s="55"/>
+      <c r="P35" s="53"/>
+      <c r="Q35" s="53"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="53"/>
+      <c r="T35" s="53"/>
+      <c r="U35" s="53"/>
+      <c r="V35" s="53"/>
+      <c r="W35" s="53"/>
+      <c r="X35" s="53"/>
+      <c r="Y35" s="53"/>
+      <c r="Z35" s="53"/>
+      <c r="AA35" s="53"/>
+      <c r="AB35" s="53"/>
+      <c r="AC35" s="53"/>
+      <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="9" customHeight="1">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="26"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="77"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="77"/>
-      <c r="T36" s="77"/>
-      <c r="U36" s="77"/>
-      <c r="V36" s="77"/>
-      <c r="W36" s="77"/>
-      <c r="X36" s="77"/>
-      <c r="Y36" s="77"/>
-      <c r="Z36" s="77"/>
-      <c r="AA36" s="77"/>
-      <c r="AB36" s="77"/>
-      <c r="AC36" s="77"/>
-      <c r="AD36" s="78"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="53"/>
+      <c r="U36" s="53"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="53"/>
+      <c r="AC36" s="53"/>
+      <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="9" customHeight="1">
-      <c r="A37" s="12">
+      <c r="A37" s="28">
         <v>2010</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="18">
         <v>3</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="20"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="23"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="78"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="53"/>
+      <c r="U37" s="53"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
+      <c r="AA37" s="53"/>
+      <c r="AB37" s="53"/>
+      <c r="AC37" s="53"/>
+      <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="9" customHeight="1">
-      <c r="A38" s="13"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="23"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="14"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="77"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="77"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="77"/>
-      <c r="X38" s="77"/>
-      <c r="Y38" s="77"/>
-      <c r="Z38" s="77"/>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-      <c r="AC38" s="77"/>
-      <c r="AD38" s="78"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="53"/>
+      <c r="Q38" s="53"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="53"/>
+      <c r="T38" s="53"/>
+      <c r="U38" s="53"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="53"/>
+      <c r="X38" s="53"/>
+      <c r="Y38" s="53"/>
+      <c r="Z38" s="53"/>
+      <c r="AA38" s="53"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="53"/>
+      <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="9" customHeight="1">
-      <c r="A39" s="14"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="26"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="27"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="76"/>
-      <c r="P39" s="77"/>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
-      <c r="X39" s="77"/>
-      <c r="Y39" s="77"/>
-      <c r="Z39" s="77"/>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-      <c r="AC39" s="77"/>
-      <c r="AD39" s="78"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="53"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="53"/>
+      <c r="T39" s="53"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="53"/>
+      <c r="W39" s="53"/>
+      <c r="X39" s="53"/>
+      <c r="Y39" s="53"/>
+      <c r="Z39" s="53"/>
+      <c r="AA39" s="53"/>
+      <c r="AB39" s="53"/>
+      <c r="AC39" s="53"/>
+      <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="9" customHeight="1">
-      <c r="A40" s="12">
+      <c r="A40" s="28">
         <v>2010</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="18">
         <v>4</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="20"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="23"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="76"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="77"/>
-      <c r="AB40" s="77"/>
-      <c r="AC40" s="77"/>
-      <c r="AD40" s="78"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="53"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="53"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="53"/>
+      <c r="X40" s="53"/>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="53"/>
+      <c r="AC40" s="53"/>
+      <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="9" customHeight="1">
-      <c r="A41" s="13"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="23"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="14"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-      <c r="O41" s="76"/>
-      <c r="P41" s="77"/>
-      <c r="Q41" s="77"/>
-      <c r="R41" s="77"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="77"/>
-      <c r="U41" s="77"/>
-      <c r="V41" s="77"/>
-      <c r="W41" s="77"/>
-      <c r="X41" s="77"/>
-      <c r="Y41" s="77"/>
-      <c r="Z41" s="77"/>
-      <c r="AA41" s="77"/>
-      <c r="AB41" s="77"/>
-      <c r="AC41" s="77"/>
-      <c r="AD41" s="78"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="53"/>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="53"/>
+      <c r="T41" s="53"/>
+      <c r="U41" s="53"/>
+      <c r="V41" s="53"/>
+      <c r="W41" s="53"/>
+      <c r="X41" s="53"/>
+      <c r="Y41" s="53"/>
+      <c r="Z41" s="53"/>
+      <c r="AA41" s="53"/>
+      <c r="AB41" s="53"/>
+      <c r="AC41" s="53"/>
+      <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="9" customHeight="1">
-      <c r="A42" s="14"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="26"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="27"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
-      <c r="O42" s="76"/>
-      <c r="P42" s="77"/>
-      <c r="Q42" s="77"/>
-      <c r="R42" s="77"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="77"/>
-      <c r="U42" s="77"/>
-      <c r="V42" s="77"/>
-      <c r="W42" s="77"/>
-      <c r="X42" s="77"/>
-      <c r="Y42" s="77"/>
-      <c r="Z42" s="77"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="77"/>
-      <c r="AC42" s="77"/>
-      <c r="AD42" s="78"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="53"/>
+      <c r="Q42" s="53"/>
+      <c r="R42" s="53"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="53"/>
+      <c r="U42" s="53"/>
+      <c r="V42" s="53"/>
+      <c r="W42" s="53"/>
+      <c r="X42" s="53"/>
+      <c r="Y42" s="53"/>
+      <c r="Z42" s="53"/>
+      <c r="AA42" s="53"/>
+      <c r="AB42" s="53"/>
+      <c r="AC42" s="53"/>
+      <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="9" customHeight="1">
-      <c r="A43" s="12">
+      <c r="A43" s="28">
         <v>2013</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="18">
         <v>3</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="20"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="23"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="77"/>
-      <c r="Q43" s="77"/>
-      <c r="R43" s="77"/>
-      <c r="S43" s="77"/>
-      <c r="T43" s="77"/>
-      <c r="U43" s="77"/>
-      <c r="V43" s="77"/>
-      <c r="W43" s="77"/>
-      <c r="X43" s="77"/>
-      <c r="Y43" s="77"/>
-      <c r="Z43" s="77"/>
-      <c r="AA43" s="77"/>
-      <c r="AB43" s="77"/>
-      <c r="AC43" s="77"/>
-      <c r="AD43" s="78"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="53"/>
+      <c r="Q43" s="53"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="53"/>
+      <c r="T43" s="53"/>
+      <c r="U43" s="53"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="53"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="53"/>
+      <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="9" customHeight="1">
-      <c r="A44" s="13"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="23"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="14"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
-      <c r="O44" s="76"/>
-      <c r="P44" s="77"/>
-      <c r="Q44" s="77"/>
-      <c r="R44" s="77"/>
-      <c r="S44" s="77"/>
-      <c r="T44" s="77"/>
-      <c r="U44" s="77"/>
-      <c r="V44" s="77"/>
-      <c r="W44" s="77"/>
-      <c r="X44" s="77"/>
-      <c r="Y44" s="77"/>
-      <c r="Z44" s="77"/>
-      <c r="AA44" s="77"/>
-      <c r="AB44" s="77"/>
-      <c r="AC44" s="77"/>
-      <c r="AD44" s="78"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="53"/>
+      <c r="Q44" s="53"/>
+      <c r="R44" s="53"/>
+      <c r="S44" s="53"/>
+      <c r="T44" s="53"/>
+      <c r="U44" s="53"/>
+      <c r="V44" s="53"/>
+      <c r="W44" s="53"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="53"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="53"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="53"/>
+      <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="9" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="26"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="27"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
-      <c r="O45" s="76"/>
-      <c r="P45" s="77"/>
-      <c r="Q45" s="77"/>
-      <c r="R45" s="77"/>
-      <c r="S45" s="77"/>
-      <c r="T45" s="77"/>
-      <c r="U45" s="77"/>
-      <c r="V45" s="77"/>
-      <c r="W45" s="77"/>
-      <c r="X45" s="77"/>
-      <c r="Y45" s="77"/>
-      <c r="Z45" s="77"/>
-      <c r="AA45" s="77"/>
-      <c r="AB45" s="77"/>
-      <c r="AC45" s="77"/>
-      <c r="AD45" s="78"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="53"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="53"/>
+      <c r="T45" s="53"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="53"/>
+      <c r="W45" s="53"/>
+      <c r="X45" s="53"/>
+      <c r="Y45" s="53"/>
+      <c r="Z45" s="53"/>
+      <c r="AA45" s="53"/>
+      <c r="AB45" s="53"/>
+      <c r="AC45" s="53"/>
+      <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="9" customHeight="1">
-      <c r="A46" s="12">
+      <c r="A46" s="28">
         <v>2013</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="18">
         <v>4</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="20"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="23"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
-      <c r="O46" s="76"/>
-      <c r="P46" s="77"/>
-      <c r="Q46" s="77"/>
-      <c r="R46" s="77"/>
-      <c r="S46" s="77"/>
-      <c r="T46" s="77"/>
-      <c r="U46" s="77"/>
-      <c r="V46" s="77"/>
-      <c r="W46" s="77"/>
-      <c r="X46" s="77"/>
-      <c r="Y46" s="77"/>
-      <c r="Z46" s="77"/>
-      <c r="AA46" s="77"/>
-      <c r="AB46" s="77"/>
-      <c r="AC46" s="77"/>
-      <c r="AD46" s="78"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="53"/>
+      <c r="Q46" s="53"/>
+      <c r="R46" s="53"/>
+      <c r="S46" s="53"/>
+      <c r="T46" s="53"/>
+      <c r="U46" s="53"/>
+      <c r="V46" s="53"/>
+      <c r="W46" s="53"/>
+      <c r="X46" s="53"/>
+      <c r="Y46" s="53"/>
+      <c r="Z46" s="53"/>
+      <c r="AA46" s="53"/>
+      <c r="AB46" s="53"/>
+      <c r="AC46" s="53"/>
+      <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="9" customHeight="1">
-      <c r="A47" s="13"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="23"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="14"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="77"/>
-      <c r="Q47" s="77"/>
-      <c r="R47" s="77"/>
-      <c r="S47" s="77"/>
-      <c r="T47" s="77"/>
-      <c r="U47" s="77"/>
-      <c r="V47" s="77"/>
-      <c r="W47" s="77"/>
-      <c r="X47" s="77"/>
-      <c r="Y47" s="77"/>
-      <c r="Z47" s="77"/>
-      <c r="AA47" s="77"/>
-      <c r="AB47" s="77"/>
-      <c r="AC47" s="77"/>
-      <c r="AD47" s="78"/>
+      <c r="O47" s="55"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
+      <c r="R47" s="53"/>
+      <c r="S47" s="53"/>
+      <c r="T47" s="53"/>
+      <c r="U47" s="53"/>
+      <c r="V47" s="53"/>
+      <c r="W47" s="53"/>
+      <c r="X47" s="53"/>
+      <c r="Y47" s="53"/>
+      <c r="Z47" s="53"/>
+      <c r="AA47" s="53"/>
+      <c r="AB47" s="53"/>
+      <c r="AC47" s="53"/>
+      <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="9" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="25"/>
-      <c r="K48" s="25"/>
-      <c r="L48" s="26"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="27"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
-      <c r="O48" s="76"/>
-      <c r="P48" s="77"/>
-      <c r="Q48" s="77"/>
-      <c r="R48" s="77"/>
-      <c r="S48" s="77"/>
-      <c r="T48" s="77"/>
-      <c r="U48" s="77"/>
-      <c r="V48" s="77"/>
-      <c r="W48" s="77"/>
-      <c r="X48" s="77"/>
-      <c r="Y48" s="77"/>
-      <c r="Z48" s="77"/>
-      <c r="AA48" s="77"/>
-      <c r="AB48" s="77"/>
-      <c r="AC48" s="77"/>
-      <c r="AD48" s="78"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="53"/>
+      <c r="AB48" s="53"/>
+      <c r="AC48" s="53"/>
+      <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="9" customHeight="1">
-      <c r="A49" s="12">
+      <c r="A49" s="28">
         <v>2013</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="18">
         <v>10</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="20"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="23"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="77"/>
-      <c r="Q49" s="77"/>
-      <c r="R49" s="77"/>
-      <c r="S49" s="77"/>
-      <c r="T49" s="77"/>
-      <c r="U49" s="77"/>
-      <c r="V49" s="77"/>
-      <c r="W49" s="77"/>
-      <c r="X49" s="77"/>
-      <c r="Y49" s="77"/>
-      <c r="Z49" s="77"/>
-      <c r="AA49" s="77"/>
-      <c r="AB49" s="77"/>
-      <c r="AC49" s="77"/>
-      <c r="AD49" s="78"/>
+      <c r="O49" s="55"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="53"/>
+      <c r="R49" s="53"/>
+      <c r="S49" s="53"/>
+      <c r="T49" s="53"/>
+      <c r="U49" s="53"/>
+      <c r="V49" s="53"/>
+      <c r="W49" s="53"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="53"/>
+      <c r="Z49" s="53"/>
+      <c r="AA49" s="53"/>
+      <c r="AB49" s="53"/>
+      <c r="AC49" s="53"/>
+      <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="9" customHeight="1">
-      <c r="A50" s="13"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="23"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="14"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="76"/>
-      <c r="P50" s="77"/>
-      <c r="Q50" s="77"/>
-      <c r="R50" s="77"/>
-      <c r="S50" s="77"/>
-      <c r="T50" s="77"/>
-      <c r="U50" s="77"/>
-      <c r="V50" s="77"/>
-      <c r="W50" s="77"/>
-      <c r="X50" s="77"/>
-      <c r="Y50" s="77"/>
-      <c r="Z50" s="77"/>
-      <c r="AA50" s="77"/>
-      <c r="AB50" s="77"/>
-      <c r="AC50" s="77"/>
-      <c r="AD50" s="78"/>
+      <c r="O50" s="55"/>
+      <c r="P50" s="53"/>
+      <c r="Q50" s="53"/>
+      <c r="R50" s="53"/>
+      <c r="S50" s="53"/>
+      <c r="T50" s="53"/>
+      <c r="U50" s="53"/>
+      <c r="V50" s="53"/>
+      <c r="W50" s="53"/>
+      <c r="X50" s="53"/>
+      <c r="Y50" s="53"/>
+      <c r="Z50" s="53"/>
+      <c r="AA50" s="53"/>
+      <c r="AB50" s="53"/>
+      <c r="AC50" s="53"/>
+      <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="9" customHeight="1">
-      <c r="A51" s="14"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="25"/>
-      <c r="L51" s="26"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="27"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
-      <c r="O51" s="76"/>
-      <c r="P51" s="77"/>
-      <c r="Q51" s="77"/>
-      <c r="R51" s="77"/>
-      <c r="S51" s="77"/>
-      <c r="T51" s="77"/>
-      <c r="U51" s="77"/>
-      <c r="V51" s="77"/>
-      <c r="W51" s="77"/>
-      <c r="X51" s="77"/>
-      <c r="Y51" s="77"/>
-      <c r="Z51" s="77"/>
-      <c r="AA51" s="77"/>
-      <c r="AB51" s="77"/>
-      <c r="AC51" s="77"/>
-      <c r="AD51" s="78"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="53"/>
+      <c r="R51" s="53"/>
+      <c r="S51" s="53"/>
+      <c r="T51" s="53"/>
+      <c r="U51" s="53"/>
+      <c r="V51" s="53"/>
+      <c r="W51" s="53"/>
+      <c r="X51" s="53"/>
+      <c r="Y51" s="53"/>
+      <c r="Z51" s="53"/>
+      <c r="AA51" s="53"/>
+      <c r="AB51" s="53"/>
+      <c r="AC51" s="53"/>
+      <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="9" customHeight="1">
-      <c r="A52" s="12">
+      <c r="A52" s="28">
         <v>2013</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="18">
         <v>11</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="20"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="23"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-      <c r="O52" s="76"/>
-      <c r="P52" s="77"/>
-      <c r="Q52" s="77"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="77"/>
-      <c r="T52" s="77"/>
-      <c r="U52" s="77"/>
-      <c r="V52" s="77"/>
-      <c r="W52" s="77"/>
-      <c r="X52" s="77"/>
-      <c r="Y52" s="77"/>
-      <c r="Z52" s="77"/>
-      <c r="AA52" s="77"/>
-      <c r="AB52" s="77"/>
-      <c r="AC52" s="77"/>
-      <c r="AD52" s="78"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="53"/>
+      <c r="Q52" s="53"/>
+      <c r="R52" s="53"/>
+      <c r="S52" s="53"/>
+      <c r="T52" s="53"/>
+      <c r="U52" s="53"/>
+      <c r="V52" s="53"/>
+      <c r="W52" s="53"/>
+      <c r="X52" s="53"/>
+      <c r="Y52" s="53"/>
+      <c r="Z52" s="53"/>
+      <c r="AA52" s="53"/>
+      <c r="AB52" s="53"/>
+      <c r="AC52" s="53"/>
+      <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="9" customHeight="1">
-      <c r="A53" s="13"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="23"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="14"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
-      <c r="O53" s="76"/>
-      <c r="P53" s="77"/>
-      <c r="Q53" s="77"/>
-      <c r="R53" s="77"/>
-      <c r="S53" s="77"/>
-      <c r="T53" s="77"/>
-      <c r="U53" s="77"/>
-      <c r="V53" s="77"/>
-      <c r="W53" s="77"/>
-      <c r="X53" s="77"/>
-      <c r="Y53" s="77"/>
-      <c r="Z53" s="77"/>
-      <c r="AA53" s="77"/>
-      <c r="AB53" s="77"/>
-      <c r="AC53" s="77"/>
-      <c r="AD53" s="78"/>
+      <c r="O53" s="55"/>
+      <c r="P53" s="53"/>
+      <c r="Q53" s="53"/>
+      <c r="R53" s="53"/>
+      <c r="S53" s="53"/>
+      <c r="T53" s="53"/>
+      <c r="U53" s="53"/>
+      <c r="V53" s="53"/>
+      <c r="W53" s="53"/>
+      <c r="X53" s="53"/>
+      <c r="Y53" s="53"/>
+      <c r="Z53" s="53"/>
+      <c r="AA53" s="53"/>
+      <c r="AB53" s="53"/>
+      <c r="AC53" s="53"/>
+      <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="9" customHeight="1">
-      <c r="A54" s="14"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="26"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="27"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
-      <c r="O54" s="76"/>
-      <c r="P54" s="77"/>
-      <c r="Q54" s="77"/>
-      <c r="R54" s="77"/>
-      <c r="S54" s="77"/>
-      <c r="T54" s="77"/>
-      <c r="U54" s="77"/>
-      <c r="V54" s="77"/>
-      <c r="W54" s="77"/>
-      <c r="X54" s="77"/>
-      <c r="Y54" s="77"/>
-      <c r="Z54" s="77"/>
-      <c r="AA54" s="77"/>
-      <c r="AB54" s="77"/>
-      <c r="AC54" s="77"/>
-      <c r="AD54" s="78"/>
+      <c r="O54" s="55"/>
+      <c r="P54" s="53"/>
+      <c r="Q54" s="53"/>
+      <c r="R54" s="53"/>
+      <c r="S54" s="53"/>
+      <c r="T54" s="53"/>
+      <c r="U54" s="53"/>
+      <c r="V54" s="53"/>
+      <c r="W54" s="53"/>
+      <c r="X54" s="53"/>
+      <c r="Y54" s="53"/>
+      <c r="Z54" s="53"/>
+      <c r="AA54" s="53"/>
+      <c r="AB54" s="53"/>
+      <c r="AC54" s="53"/>
+      <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="9" customHeight="1">
-      <c r="A55" s="12">
+      <c r="A55" s="28">
         <v>2014</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="18">
         <v>3</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="20"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="23"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="76"/>
-      <c r="P55" s="77"/>
-      <c r="Q55" s="77"/>
-      <c r="R55" s="77"/>
-      <c r="S55" s="77"/>
-      <c r="T55" s="77"/>
-      <c r="U55" s="77"/>
-      <c r="V55" s="77"/>
-      <c r="W55" s="77"/>
-      <c r="X55" s="77"/>
-      <c r="Y55" s="77"/>
-      <c r="Z55" s="77"/>
-      <c r="AA55" s="77"/>
-      <c r="AB55" s="77"/>
-      <c r="AC55" s="77"/>
-      <c r="AD55" s="78"/>
+      <c r="O55" s="55"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="53"/>
+      <c r="S55" s="53"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="53"/>
+      <c r="W55" s="53"/>
+      <c r="X55" s="53"/>
+      <c r="Y55" s="53"/>
+      <c r="Z55" s="53"/>
+      <c r="AA55" s="53"/>
+      <c r="AB55" s="53"/>
+      <c r="AC55" s="53"/>
+      <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="9" customHeight="1">
-      <c r="A56" s="13"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="23"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="14"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-      <c r="O56" s="76"/>
-      <c r="P56" s="77"/>
-      <c r="Q56" s="77"/>
-      <c r="R56" s="77"/>
-      <c r="S56" s="77"/>
-      <c r="T56" s="77"/>
-      <c r="U56" s="77"/>
-      <c r="V56" s="77"/>
-      <c r="W56" s="77"/>
-      <c r="X56" s="77"/>
-      <c r="Y56" s="77"/>
-      <c r="Z56" s="77"/>
-      <c r="AA56" s="77"/>
-      <c r="AB56" s="77"/>
-      <c r="AC56" s="77"/>
-      <c r="AD56" s="78"/>
+      <c r="O56" s="55"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
+      <c r="R56" s="53"/>
+      <c r="S56" s="53"/>
+      <c r="T56" s="53"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="53"/>
+      <c r="X56" s="53"/>
+      <c r="Y56" s="53"/>
+      <c r="Z56" s="53"/>
+      <c r="AA56" s="53"/>
+      <c r="AB56" s="53"/>
+      <c r="AC56" s="53"/>
+      <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="9" customHeight="1">
-      <c r="A57" s="14"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="25"/>
-      <c r="K57" s="25"/>
-      <c r="L57" s="26"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="27"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-      <c r="O57" s="76"/>
-      <c r="P57" s="77"/>
-      <c r="Q57" s="77"/>
-      <c r="R57" s="77"/>
-      <c r="S57" s="77"/>
-      <c r="T57" s="77"/>
-      <c r="U57" s="77"/>
-      <c r="V57" s="77"/>
-      <c r="W57" s="77"/>
-      <c r="X57" s="77"/>
-      <c r="Y57" s="77"/>
-      <c r="Z57" s="77"/>
-      <c r="AA57" s="77"/>
-      <c r="AB57" s="77"/>
-      <c r="AC57" s="77"/>
-      <c r="AD57" s="78"/>
+      <c r="O57" s="55"/>
+      <c r="P57" s="53"/>
+      <c r="Q57" s="53"/>
+      <c r="R57" s="53"/>
+      <c r="S57" s="53"/>
+      <c r="T57" s="53"/>
+      <c r="U57" s="53"/>
+      <c r="V57" s="53"/>
+      <c r="W57" s="53"/>
+      <c r="X57" s="53"/>
+      <c r="Y57" s="53"/>
+      <c r="Z57" s="53"/>
+      <c r="AA57" s="53"/>
+      <c r="AB57" s="53"/>
+      <c r="AC57" s="53"/>
+      <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="9" customHeight="1">
-      <c r="A58" s="12">
+      <c r="A58" s="28">
         <v>2014</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="18">
         <v>4</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="19"/>
-      <c r="L58" s="20"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="23"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="76"/>
-      <c r="P58" s="77"/>
-      <c r="Q58" s="77"/>
-      <c r="R58" s="77"/>
-      <c r="S58" s="77"/>
-      <c r="T58" s="77"/>
-      <c r="U58" s="77"/>
-      <c r="V58" s="77"/>
-      <c r="W58" s="77"/>
-      <c r="X58" s="77"/>
-      <c r="Y58" s="77"/>
-      <c r="Z58" s="77"/>
-      <c r="AA58" s="77"/>
-      <c r="AB58" s="77"/>
-      <c r="AC58" s="77"/>
-      <c r="AD58" s="78"/>
+      <c r="O58" s="55"/>
+      <c r="P58" s="53"/>
+      <c r="Q58" s="53"/>
+      <c r="R58" s="53"/>
+      <c r="S58" s="53"/>
+      <c r="T58" s="53"/>
+      <c r="U58" s="53"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="53"/>
+      <c r="Z58" s="53"/>
+      <c r="AA58" s="53"/>
+      <c r="AB58" s="53"/>
+      <c r="AC58" s="53"/>
+      <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="9" customHeight="1">
-      <c r="A59" s="13"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="23"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="14"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
-      <c r="O59" s="76"/>
-      <c r="P59" s="77"/>
-      <c r="Q59" s="77"/>
-      <c r="R59" s="77"/>
-      <c r="S59" s="77"/>
-      <c r="T59" s="77"/>
-      <c r="U59" s="77"/>
-      <c r="V59" s="77"/>
-      <c r="W59" s="77"/>
-      <c r="X59" s="77"/>
-      <c r="Y59" s="77"/>
-      <c r="Z59" s="77"/>
-      <c r="AA59" s="77"/>
-      <c r="AB59" s="77"/>
-      <c r="AC59" s="77"/>
-      <c r="AD59" s="78"/>
+      <c r="O59" s="55"/>
+      <c r="P59" s="53"/>
+      <c r="Q59" s="53"/>
+      <c r="R59" s="53"/>
+      <c r="S59" s="53"/>
+      <c r="T59" s="53"/>
+      <c r="U59" s="53"/>
+      <c r="V59" s="53"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="53"/>
+      <c r="Z59" s="53"/>
+      <c r="AA59" s="53"/>
+      <c r="AB59" s="53"/>
+      <c r="AC59" s="53"/>
+      <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="9" customHeight="1">
-      <c r="A60" s="14"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-      <c r="J60" s="25"/>
-      <c r="K60" s="25"/>
-      <c r="L60" s="26"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="27"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="77"/>
-      <c r="Q60" s="77"/>
-      <c r="R60" s="77"/>
-      <c r="S60" s="77"/>
-      <c r="T60" s="77"/>
-      <c r="U60" s="77"/>
-      <c r="V60" s="77"/>
-      <c r="W60" s="77"/>
-      <c r="X60" s="77"/>
-      <c r="Y60" s="77"/>
-      <c r="Z60" s="77"/>
-      <c r="AA60" s="77"/>
-      <c r="AB60" s="77"/>
-      <c r="AC60" s="77"/>
-      <c r="AD60" s="78"/>
+      <c r="O60" s="55"/>
+      <c r="P60" s="53"/>
+      <c r="Q60" s="53"/>
+      <c r="R60" s="53"/>
+      <c r="S60" s="53"/>
+      <c r="T60" s="53"/>
+      <c r="U60" s="53"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="53"/>
+      <c r="Z60" s="53"/>
+      <c r="AA60" s="53"/>
+      <c r="AB60" s="53"/>
+      <c r="AC60" s="53"/>
+      <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="9" customHeight="1">
-      <c r="A61" s="12">
+      <c r="A61" s="28">
         <v>2017</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="18">
         <v>3</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-      <c r="L61" s="20"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="23"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
-      <c r="O61" s="76"/>
-      <c r="P61" s="77"/>
-      <c r="Q61" s="77"/>
-      <c r="R61" s="77"/>
-      <c r="S61" s="77"/>
-      <c r="T61" s="77"/>
-      <c r="U61" s="77"/>
-      <c r="V61" s="77"/>
-      <c r="W61" s="77"/>
-      <c r="X61" s="77"/>
-      <c r="Y61" s="77"/>
-      <c r="Z61" s="77"/>
-      <c r="AA61" s="77"/>
-      <c r="AB61" s="77"/>
-      <c r="AC61" s="77"/>
-      <c r="AD61" s="78"/>
+      <c r="O61" s="55"/>
+      <c r="P61" s="53"/>
+      <c r="Q61" s="53"/>
+      <c r="R61" s="53"/>
+      <c r="S61" s="53"/>
+      <c r="T61" s="53"/>
+      <c r="U61" s="53"/>
+      <c r="V61" s="53"/>
+      <c r="W61" s="53"/>
+      <c r="X61" s="53"/>
+      <c r="Y61" s="53"/>
+      <c r="Z61" s="53"/>
+      <c r="AA61" s="53"/>
+      <c r="AB61" s="53"/>
+      <c r="AC61" s="53"/>
+      <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="9" customHeight="1">
-      <c r="A62" s="13"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="23"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="14"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
-      <c r="O62" s="76"/>
-      <c r="P62" s="77"/>
-      <c r="Q62" s="77"/>
-      <c r="R62" s="77"/>
-      <c r="S62" s="77"/>
-      <c r="T62" s="77"/>
-      <c r="U62" s="77"/>
-      <c r="V62" s="77"/>
-      <c r="W62" s="77"/>
-      <c r="X62" s="77"/>
-      <c r="Y62" s="77"/>
-      <c r="Z62" s="77"/>
-      <c r="AA62" s="77"/>
-      <c r="AB62" s="77"/>
-      <c r="AC62" s="77"/>
-      <c r="AD62" s="78"/>
+      <c r="O62" s="55"/>
+      <c r="P62" s="53"/>
+      <c r="Q62" s="53"/>
+      <c r="R62" s="53"/>
+      <c r="S62" s="53"/>
+      <c r="T62" s="53"/>
+      <c r="U62" s="53"/>
+      <c r="V62" s="53"/>
+      <c r="W62" s="53"/>
+      <c r="X62" s="53"/>
+      <c r="Y62" s="53"/>
+      <c r="Z62" s="53"/>
+      <c r="AA62" s="53"/>
+      <c r="AB62" s="53"/>
+      <c r="AC62" s="53"/>
+      <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="9" customHeight="1">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="25"/>
-      <c r="K63" s="25"/>
-      <c r="L63" s="26"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="27"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-      <c r="O63" s="76"/>
-      <c r="P63" s="77"/>
-      <c r="Q63" s="77"/>
-      <c r="R63" s="77"/>
-      <c r="S63" s="77"/>
-      <c r="T63" s="77"/>
-      <c r="U63" s="77"/>
-      <c r="V63" s="77"/>
-      <c r="W63" s="77"/>
-      <c r="X63" s="77"/>
-      <c r="Y63" s="77"/>
-      <c r="Z63" s="77"/>
-      <c r="AA63" s="77"/>
-      <c r="AB63" s="77"/>
-      <c r="AC63" s="77"/>
-      <c r="AD63" s="78"/>
+      <c r="O63" s="55"/>
+      <c r="P63" s="53"/>
+      <c r="Q63" s="53"/>
+      <c r="R63" s="53"/>
+      <c r="S63" s="53"/>
+      <c r="T63" s="53"/>
+      <c r="U63" s="53"/>
+      <c r="V63" s="53"/>
+      <c r="W63" s="53"/>
+      <c r="X63" s="53"/>
+      <c r="Y63" s="53"/>
+      <c r="Z63" s="53"/>
+      <c r="AA63" s="53"/>
+      <c r="AB63" s="53"/>
+      <c r="AC63" s="53"/>
+      <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="9" customHeight="1">
-      <c r="A64" s="12">
+      <c r="A64" s="28">
         <v>2017</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="18">
         <v>6</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="20"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="23"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-      <c r="O64" s="76"/>
-      <c r="P64" s="77"/>
-      <c r="Q64" s="77"/>
-      <c r="R64" s="77"/>
-      <c r="S64" s="77"/>
-      <c r="T64" s="77"/>
-      <c r="U64" s="77"/>
-      <c r="V64" s="77"/>
-      <c r="W64" s="77"/>
-      <c r="X64" s="77"/>
-      <c r="Y64" s="77"/>
-      <c r="Z64" s="77"/>
-      <c r="AA64" s="77"/>
-      <c r="AB64" s="77"/>
-      <c r="AC64" s="77"/>
-      <c r="AD64" s="78"/>
+      <c r="O64" s="55"/>
+      <c r="P64" s="53"/>
+      <c r="Q64" s="53"/>
+      <c r="R64" s="53"/>
+      <c r="S64" s="53"/>
+      <c r="T64" s="53"/>
+      <c r="U64" s="53"/>
+      <c r="V64" s="53"/>
+      <c r="W64" s="53"/>
+      <c r="X64" s="53"/>
+      <c r="Y64" s="53"/>
+      <c r="Z64" s="53"/>
+      <c r="AA64" s="53"/>
+      <c r="AB64" s="53"/>
+      <c r="AC64" s="53"/>
+      <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="9" customHeight="1">
-      <c r="A65" s="13"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="23"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="14"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
-      <c r="O65" s="79"/>
-      <c r="P65" s="80"/>
-      <c r="Q65" s="80"/>
-      <c r="R65" s="80"/>
-      <c r="S65" s="80"/>
-      <c r="T65" s="80"/>
-      <c r="U65" s="80"/>
-      <c r="V65" s="80"/>
-      <c r="W65" s="80"/>
-      <c r="X65" s="80"/>
-      <c r="Y65" s="80"/>
-      <c r="Z65" s="80"/>
-      <c r="AA65" s="80"/>
-      <c r="AB65" s="80"/>
-      <c r="AC65" s="80"/>
-      <c r="AD65" s="81"/>
+      <c r="O65" s="56"/>
+      <c r="P65" s="57"/>
+      <c r="Q65" s="57"/>
+      <c r="R65" s="57"/>
+      <c r="S65" s="57"/>
+      <c r="T65" s="57"/>
+      <c r="U65" s="57"/>
+      <c r="V65" s="57"/>
+      <c r="W65" s="57"/>
+      <c r="X65" s="57"/>
+      <c r="Y65" s="57"/>
+      <c r="Z65" s="57"/>
+      <c r="AA65" s="57"/>
+      <c r="AB65" s="57"/>
+      <c r="AC65" s="57"/>
+      <c r="AD65" s="58"/>
     </row>
     <row r="66" spans="1:30" ht="9" customHeight="1">
-      <c r="A66" s="14"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="25"/>
-      <c r="L66" s="26"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="27"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
@@ -3858,24 +3858,24 @@
       <c r="AD66" s="3"/>
     </row>
     <row r="67" spans="1:30" ht="9" customHeight="1">
-      <c r="A67" s="12">
+      <c r="A67" s="28">
         <v>2019</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="18">
         <v>4</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="C67" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="19"/>
-      <c r="L67" s="20"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="23"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
@@ -3896,21 +3896,21 @@
       <c r="AD67" s="3"/>
     </row>
     <row r="68" spans="1:30" ht="9" customHeight="1">
-      <c r="A68" s="13"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="23"/>
+      <c r="A68" s="29"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="14"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="42" t="s">
+      <c r="O68" s="32" t="s">
         <v>10</v>
       </c>
       <c r="P68" s="33"/>
@@ -3930,552 +3930,552 @@
       <c r="AD68" s="34"/>
     </row>
     <row r="69" spans="1:30" ht="9" customHeight="1">
-      <c r="A69" s="14"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="25"/>
-      <c r="L69" s="26"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="27"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
-      <c r="O69" s="40"/>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="22"/>
-      <c r="R69" s="22"/>
-      <c r="S69" s="22"/>
-      <c r="T69" s="22"/>
-      <c r="U69" s="22"/>
-      <c r="V69" s="22"/>
-      <c r="W69" s="22"/>
-      <c r="X69" s="22"/>
-      <c r="Y69" s="22"/>
-      <c r="Z69" s="22"/>
-      <c r="AA69" s="22"/>
-      <c r="AB69" s="22"/>
-      <c r="AC69" s="22"/>
-      <c r="AD69" s="23"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="13"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="13"/>
+      <c r="U69" s="13"/>
+      <c r="V69" s="13"/>
+      <c r="W69" s="13"/>
+      <c r="X69" s="13"/>
+      <c r="Y69" s="13"/>
+      <c r="Z69" s="13"/>
+      <c r="AA69" s="13"/>
+      <c r="AB69" s="13"/>
+      <c r="AC69" s="13"/>
+      <c r="AD69" s="14"/>
     </row>
     <row r="70" spans="1:30" ht="9" customHeight="1" thickBot="1">
-      <c r="A70" s="12">
+      <c r="A70" s="28">
         <v>2019</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="18">
         <v>10</v>
       </c>
-      <c r="C70" s="27" t="s">
+      <c r="C70" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="20"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="23"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
-      <c r="O70" s="40"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="22"/>
-      <c r="S70" s="22"/>
-      <c r="T70" s="22"/>
-      <c r="U70" s="22"/>
-      <c r="V70" s="22"/>
-      <c r="W70" s="22"/>
-      <c r="X70" s="22"/>
-      <c r="Y70" s="22"/>
-      <c r="Z70" s="22"/>
-      <c r="AA70" s="22"/>
-      <c r="AB70" s="22"/>
-      <c r="AC70" s="22"/>
-      <c r="AD70" s="23"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="13"/>
+      <c r="Q70" s="13"/>
+      <c r="R70" s="13"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="13"/>
+      <c r="U70" s="13"/>
+      <c r="V70" s="13"/>
+      <c r="W70" s="13"/>
+      <c r="X70" s="13"/>
+      <c r="Y70" s="13"/>
+      <c r="Z70" s="13"/>
+      <c r="AA70" s="13"/>
+      <c r="AB70" s="13"/>
+      <c r="AC70" s="13"/>
+      <c r="AD70" s="14"/>
     </row>
     <row r="71" spans="1:30" ht="9" customHeight="1" thickTop="1">
-      <c r="A71" s="13"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="23"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="14"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="71" t="s">
+      <c r="O71" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="P71" s="72"/>
-      <c r="Q71" s="72"/>
-      <c r="R71" s="72"/>
-      <c r="S71" s="72"/>
-      <c r="T71" s="72"/>
-      <c r="U71" s="72"/>
-      <c r="V71" s="72"/>
-      <c r="W71" s="72"/>
-      <c r="X71" s="72"/>
-      <c r="Y71" s="72"/>
-      <c r="Z71" s="72"/>
-      <c r="AA71" s="72"/>
-      <c r="AB71" s="72"/>
-      <c r="AC71" s="72"/>
-      <c r="AD71" s="73"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="10"/>
+      <c r="Y71" s="10"/>
+      <c r="Z71" s="10"/>
+      <c r="AA71" s="10"/>
+      <c r="AB71" s="10"/>
+      <c r="AC71" s="10"/>
+      <c r="AD71" s="11"/>
     </row>
     <row r="72" spans="1:30" ht="9" customHeight="1">
-      <c r="A72" s="14"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="25"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="25"/>
-      <c r="L72" s="26"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="27"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
-      <c r="O72" s="40"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
-      <c r="Z72" s="22"/>
-      <c r="AA72" s="22"/>
-      <c r="AB72" s="22"/>
-      <c r="AC72" s="22"/>
-      <c r="AD72" s="23"/>
+      <c r="O72" s="12"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
+      <c r="R72" s="13"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="13"/>
+      <c r="U72" s="13"/>
+      <c r="V72" s="13"/>
+      <c r="W72" s="13"/>
+      <c r="X72" s="13"/>
+      <c r="Y72" s="13"/>
+      <c r="Z72" s="13"/>
+      <c r="AA72" s="13"/>
+      <c r="AB72" s="13"/>
+      <c r="AC72" s="13"/>
+      <c r="AD72" s="14"/>
     </row>
     <row r="73" spans="1:30" ht="9" customHeight="1">
-      <c r="A73" s="12">
+      <c r="A73" s="28">
         <v>2020</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="18">
         <v>3</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="C73" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="20"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="23"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="40"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
-      <c r="Z73" s="22"/>
-      <c r="AA73" s="22"/>
-      <c r="AB73" s="22"/>
-      <c r="AC73" s="22"/>
-      <c r="AD73" s="23"/>
+      <c r="O73" s="12"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="13"/>
+      <c r="U73" s="13"/>
+      <c r="V73" s="13"/>
+      <c r="W73" s="13"/>
+      <c r="X73" s="13"/>
+      <c r="Y73" s="13"/>
+      <c r="Z73" s="13"/>
+      <c r="AA73" s="13"/>
+      <c r="AB73" s="13"/>
+      <c r="AC73" s="13"/>
+      <c r="AD73" s="14"/>
     </row>
     <row r="74" spans="1:30" ht="9" customHeight="1">
-      <c r="A74" s="13"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="23"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="14"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
-      <c r="O74" s="40"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="22"/>
-      <c r="V74" s="22"/>
-      <c r="W74" s="22"/>
-      <c r="X74" s="22"/>
-      <c r="Y74" s="22"/>
-      <c r="Z74" s="22"/>
-      <c r="AA74" s="22"/>
-      <c r="AB74" s="22"/>
-      <c r="AC74" s="22"/>
-      <c r="AD74" s="23"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="13"/>
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+      <c r="X74" s="13"/>
+      <c r="Y74" s="13"/>
+      <c r="Z74" s="13"/>
+      <c r="AA74" s="13"/>
+      <c r="AB74" s="13"/>
+      <c r="AC74" s="13"/>
+      <c r="AD74" s="14"/>
     </row>
     <row r="75" spans="1:30" ht="9" customHeight="1">
-      <c r="A75" s="14"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="25"/>
-      <c r="L75" s="26"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="27"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-      <c r="O75" s="40"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
-      <c r="Z75" s="22"/>
-      <c r="AA75" s="22"/>
-      <c r="AB75" s="22"/>
-      <c r="AC75" s="22"/>
-      <c r="AD75" s="23"/>
+      <c r="O75" s="12"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+      <c r="R75" s="13"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="13"/>
+      <c r="U75" s="13"/>
+      <c r="V75" s="13"/>
+      <c r="W75" s="13"/>
+      <c r="X75" s="13"/>
+      <c r="Y75" s="13"/>
+      <c r="Z75" s="13"/>
+      <c r="AA75" s="13"/>
+      <c r="AB75" s="13"/>
+      <c r="AC75" s="13"/>
+      <c r="AD75" s="14"/>
     </row>
     <row r="76" spans="1:30" ht="9" customHeight="1">
-      <c r="A76" s="12">
+      <c r="A76" s="28">
         <v>2021</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="18">
         <v>3</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C76" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="20"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="23"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
-      <c r="O76" s="40"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="22"/>
-      <c r="R76" s="22"/>
-      <c r="S76" s="22"/>
-      <c r="T76" s="22"/>
-      <c r="U76" s="22"/>
-      <c r="V76" s="22"/>
-      <c r="W76" s="22"/>
-      <c r="X76" s="22"/>
-      <c r="Y76" s="22"/>
-      <c r="Z76" s="22"/>
-      <c r="AA76" s="22"/>
-      <c r="AB76" s="22"/>
-      <c r="AC76" s="22"/>
-      <c r="AD76" s="23"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="13"/>
+      <c r="Q76" s="13"/>
+      <c r="R76" s="13"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="13"/>
+      <c r="U76" s="13"/>
+      <c r="V76" s="13"/>
+      <c r="W76" s="13"/>
+      <c r="X76" s="13"/>
+      <c r="Y76" s="13"/>
+      <c r="Z76" s="13"/>
+      <c r="AA76" s="13"/>
+      <c r="AB76" s="13"/>
+      <c r="AC76" s="13"/>
+      <c r="AD76" s="14"/>
     </row>
     <row r="77" spans="1:30" ht="9" customHeight="1">
-      <c r="A77" s="50"/>
-      <c r="B77" s="52"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
-      <c r="L77" s="23"/>
+      <c r="A77" s="69"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="14"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
-      <c r="O77" s="40"/>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
-      <c r="R77" s="22"/>
-      <c r="S77" s="22"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="22"/>
-      <c r="X77" s="22"/>
-      <c r="Y77" s="22"/>
-      <c r="Z77" s="22"/>
-      <c r="AA77" s="22"/>
-      <c r="AB77" s="22"/>
-      <c r="AC77" s="22"/>
-      <c r="AD77" s="23"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="13"/>
+      <c r="Q77" s="13"/>
+      <c r="R77" s="13"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="13"/>
+      <c r="U77" s="13"/>
+      <c r="V77" s="13"/>
+      <c r="W77" s="13"/>
+      <c r="X77" s="13"/>
+      <c r="Y77" s="13"/>
+      <c r="Z77" s="13"/>
+      <c r="AA77" s="13"/>
+      <c r="AB77" s="13"/>
+      <c r="AC77" s="13"/>
+      <c r="AD77" s="14"/>
     </row>
     <row r="78" spans="1:30" ht="9" customHeight="1">
-      <c r="A78" s="51"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="25"/>
-      <c r="L78" s="26"/>
+      <c r="A78" s="71"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="27"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="40"/>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="T78" s="22"/>
-      <c r="U78" s="22"/>
-      <c r="V78" s="22"/>
-      <c r="W78" s="22"/>
-      <c r="X78" s="22"/>
-      <c r="Y78" s="22"/>
-      <c r="Z78" s="22"/>
-      <c r="AA78" s="22"/>
-      <c r="AB78" s="22"/>
-      <c r="AC78" s="22"/>
-      <c r="AD78" s="23"/>
+      <c r="O78" s="12"/>
+      <c r="P78" s="13"/>
+      <c r="Q78" s="13"/>
+      <c r="R78" s="13"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="13"/>
+      <c r="U78" s="13"/>
+      <c r="V78" s="13"/>
+      <c r="W78" s="13"/>
+      <c r="X78" s="13"/>
+      <c r="Y78" s="13"/>
+      <c r="Z78" s="13"/>
+      <c r="AA78" s="13"/>
+      <c r="AB78" s="13"/>
+      <c r="AC78" s="13"/>
+      <c r="AD78" s="14"/>
     </row>
     <row r="79" spans="1:30" ht="9" customHeight="1">
-      <c r="A79" s="12">
+      <c r="A79" s="28">
         <v>2021</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="18">
         <v>4</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
-      <c r="L79" s="20"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="23"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
-      <c r="O79" s="40"/>
-      <c r="P79" s="22"/>
-      <c r="Q79" s="22"/>
-      <c r="R79" s="22"/>
-      <c r="S79" s="22"/>
-      <c r="T79" s="22"/>
-      <c r="U79" s="22"/>
-      <c r="V79" s="22"/>
-      <c r="W79" s="22"/>
-      <c r="X79" s="22"/>
-      <c r="Y79" s="22"/>
-      <c r="Z79" s="22"/>
-      <c r="AA79" s="22"/>
-      <c r="AB79" s="22"/>
-      <c r="AC79" s="22"/>
-      <c r="AD79" s="23"/>
+      <c r="O79" s="12"/>
+      <c r="P79" s="13"/>
+      <c r="Q79" s="13"/>
+      <c r="R79" s="13"/>
+      <c r="S79" s="13"/>
+      <c r="T79" s="13"/>
+      <c r="U79" s="13"/>
+      <c r="V79" s="13"/>
+      <c r="W79" s="13"/>
+      <c r="X79" s="13"/>
+      <c r="Y79" s="13"/>
+      <c r="Z79" s="13"/>
+      <c r="AA79" s="13"/>
+      <c r="AB79" s="13"/>
+      <c r="AC79" s="13"/>
+      <c r="AD79" s="14"/>
     </row>
     <row r="80" spans="1:30" ht="9" customHeight="1">
-      <c r="A80" s="13"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="23"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
+      <c r="L80" s="14"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
-      <c r="O80" s="40"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
-      <c r="R80" s="22"/>
-      <c r="S80" s="22"/>
-      <c r="T80" s="22"/>
-      <c r="U80" s="22"/>
-      <c r="V80" s="22"/>
-      <c r="W80" s="22"/>
-      <c r="X80" s="22"/>
-      <c r="Y80" s="22"/>
-      <c r="Z80" s="22"/>
-      <c r="AA80" s="22"/>
-      <c r="AB80" s="22"/>
-      <c r="AC80" s="22"/>
-      <c r="AD80" s="23"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="13"/>
+      <c r="Q80" s="13"/>
+      <c r="R80" s="13"/>
+      <c r="S80" s="13"/>
+      <c r="T80" s="13"/>
+      <c r="U80" s="13"/>
+      <c r="V80" s="13"/>
+      <c r="W80" s="13"/>
+      <c r="X80" s="13"/>
+      <c r="Y80" s="13"/>
+      <c r="Z80" s="13"/>
+      <c r="AA80" s="13"/>
+      <c r="AB80" s="13"/>
+      <c r="AC80" s="13"/>
+      <c r="AD80" s="14"/>
     </row>
     <row r="81" spans="1:30" ht="9" customHeight="1">
-      <c r="A81" s="14"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="25"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
-      <c r="I81" s="25"/>
-      <c r="J81" s="25"/>
-      <c r="K81" s="25"/>
-      <c r="L81" s="26"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="27"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
-      <c r="O81" s="40"/>
-      <c r="P81" s="22"/>
-      <c r="Q81" s="22"/>
-      <c r="R81" s="22"/>
-      <c r="S81" s="22"/>
-      <c r="T81" s="22"/>
-      <c r="U81" s="22"/>
-      <c r="V81" s="22"/>
-      <c r="W81" s="22"/>
-      <c r="X81" s="22"/>
-      <c r="Y81" s="22"/>
-      <c r="Z81" s="22"/>
-      <c r="AA81" s="22"/>
-      <c r="AB81" s="22"/>
-      <c r="AC81" s="22"/>
-      <c r="AD81" s="23"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="13"/>
+      <c r="Q81" s="13"/>
+      <c r="R81" s="13"/>
+      <c r="S81" s="13"/>
+      <c r="T81" s="13"/>
+      <c r="U81" s="13"/>
+      <c r="V81" s="13"/>
+      <c r="W81" s="13"/>
+      <c r="X81" s="13"/>
+      <c r="Y81" s="13"/>
+      <c r="Z81" s="13"/>
+      <c r="AA81" s="13"/>
+      <c r="AB81" s="13"/>
+      <c r="AC81" s="13"/>
+      <c r="AD81" s="14"/>
     </row>
     <row r="82" spans="1:30" ht="14">
-      <c r="A82" s="12">
+      <c r="A82" s="28">
         <v>2025</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="18">
         <v>9</v>
       </c>
-      <c r="C82" s="27" t="s">
+      <c r="C82" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
-      <c r="K82" s="19"/>
-      <c r="L82" s="20"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="22"/>
+      <c r="L82" s="23"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="40"/>
-      <c r="P82" s="22"/>
-      <c r="Q82" s="22"/>
-      <c r="R82" s="22"/>
-      <c r="S82" s="22"/>
-      <c r="T82" s="22"/>
-      <c r="U82" s="22"/>
-      <c r="V82" s="22"/>
-      <c r="W82" s="22"/>
-      <c r="X82" s="22"/>
-      <c r="Y82" s="22"/>
-      <c r="Z82" s="22"/>
-      <c r="AA82" s="22"/>
-      <c r="AB82" s="22"/>
-      <c r="AC82" s="22"/>
-      <c r="AD82" s="23"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="13"/>
+      <c r="Q82" s="13"/>
+      <c r="R82" s="13"/>
+      <c r="S82" s="13"/>
+      <c r="T82" s="13"/>
+      <c r="U82" s="13"/>
+      <c r="V82" s="13"/>
+      <c r="W82" s="13"/>
+      <c r="X82" s="13"/>
+      <c r="Y82" s="13"/>
+      <c r="Z82" s="13"/>
+      <c r="AA82" s="13"/>
+      <c r="AB82" s="13"/>
+      <c r="AC82" s="13"/>
+      <c r="AD82" s="14"/>
     </row>
     <row r="83" spans="1:30" ht="14">
-      <c r="A83" s="13"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="22"/>
-      <c r="J83" s="22"/>
-      <c r="K83" s="22"/>
-      <c r="L83" s="23"/>
+      <c r="A83" s="29"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="14"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="40"/>
-      <c r="P83" s="22"/>
-      <c r="Q83" s="22"/>
-      <c r="R83" s="22"/>
-      <c r="S83" s="22"/>
-      <c r="T83" s="22"/>
-      <c r="U83" s="22"/>
-      <c r="V83" s="22"/>
-      <c r="W83" s="22"/>
-      <c r="X83" s="22"/>
-      <c r="Y83" s="22"/>
-      <c r="Z83" s="22"/>
-      <c r="AA83" s="22"/>
-      <c r="AB83" s="22"/>
-      <c r="AC83" s="22"/>
-      <c r="AD83" s="23"/>
+      <c r="O83" s="12"/>
+      <c r="P83" s="13"/>
+      <c r="Q83" s="13"/>
+      <c r="R83" s="13"/>
+      <c r="S83" s="13"/>
+      <c r="T83" s="13"/>
+      <c r="U83" s="13"/>
+      <c r="V83" s="13"/>
+      <c r="W83" s="13"/>
+      <c r="X83" s="13"/>
+      <c r="Y83" s="13"/>
+      <c r="Z83" s="13"/>
+      <c r="AA83" s="13"/>
+      <c r="AB83" s="13"/>
+      <c r="AC83" s="13"/>
+      <c r="AD83" s="14"/>
     </row>
     <row r="84" spans="1:30" ht="14">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="25"/>
-      <c r="J84" s="25"/>
-      <c r="K84" s="25"/>
-      <c r="L84" s="26"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="27"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-      <c r="O84" s="40"/>
-      <c r="P84" s="22"/>
-      <c r="Q84" s="22"/>
-      <c r="R84" s="22"/>
-      <c r="S84" s="22"/>
-      <c r="T84" s="22"/>
-      <c r="U84" s="22"/>
-      <c r="V84" s="22"/>
-      <c r="W84" s="22"/>
-      <c r="X84" s="22"/>
-      <c r="Y84" s="22"/>
-      <c r="Z84" s="22"/>
-      <c r="AA84" s="22"/>
-      <c r="AB84" s="22"/>
-      <c r="AC84" s="22"/>
-      <c r="AD84" s="23"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="13"/>
+      <c r="Q84" s="13"/>
+      <c r="R84" s="13"/>
+      <c r="S84" s="13"/>
+      <c r="T84" s="13"/>
+      <c r="U84" s="13"/>
+      <c r="V84" s="13"/>
+      <c r="W84" s="13"/>
+      <c r="X84" s="13"/>
+      <c r="Y84" s="13"/>
+      <c r="Z84" s="13"/>
+      <c r="AA84" s="13"/>
+      <c r="AB84" s="13"/>
+      <c r="AC84" s="13"/>
+      <c r="AD84" s="14"/>
     </row>
     <row r="85" spans="1:30" ht="9" customHeight="1">
-      <c r="A85" s="74"/>
-      <c r="B85" s="75"/>
+      <c r="A85" s="35"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="33"/>
       <c r="D85" s="33"/>
       <c r="E85" s="33"/>
@@ -4488,36 +4488,36 @@
       <c r="L85" s="33"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="41"/>
-      <c r="P85" s="37"/>
-      <c r="Q85" s="37"/>
-      <c r="R85" s="37"/>
-      <c r="S85" s="37"/>
-      <c r="T85" s="37"/>
-      <c r="U85" s="37"/>
-      <c r="V85" s="37"/>
-      <c r="W85" s="37"/>
-      <c r="X85" s="37"/>
-      <c r="Y85" s="37"/>
-      <c r="Z85" s="37"/>
-      <c r="AA85" s="37"/>
-      <c r="AB85" s="37"/>
-      <c r="AC85" s="37"/>
-      <c r="AD85" s="38"/>
+      <c r="O85" s="15"/>
+      <c r="P85" s="16"/>
+      <c r="Q85" s="16"/>
+      <c r="R85" s="16"/>
+      <c r="S85" s="16"/>
+      <c r="T85" s="16"/>
+      <c r="U85" s="16"/>
+      <c r="V85" s="16"/>
+      <c r="W85" s="16"/>
+      <c r="X85" s="16"/>
+      <c r="Y85" s="16"/>
+      <c r="Z85" s="16"/>
+      <c r="AA85" s="16"/>
+      <c r="AB85" s="16"/>
+      <c r="AC85" s="16"/>
+      <c r="AD85" s="17"/>
     </row>
     <row r="86" spans="1:30" ht="9" customHeight="1">
-      <c r="A86" s="22"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
-      <c r="G86" s="22"/>
-      <c r="H86" s="22"/>
-      <c r="I86" s="22"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="22"/>
-      <c r="L86" s="22"/>
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
@@ -33395,6 +33395,89 @@
     </row>
   </sheetData>
   <mergeCells count="107">
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:L60"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:L33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B19:J20"/>
+    <mergeCell ref="B21:J22"/>
+    <mergeCell ref="B10:I15"/>
+    <mergeCell ref="A16:G18"/>
+    <mergeCell ref="H16:I18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="B23:J26"/>
+    <mergeCell ref="K25:L26"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:L75"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:L54"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:L42"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="C76:L78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:L63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:L66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="C67:L69"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="Q1:AD3"/>
+    <mergeCell ref="F2:I3"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="F5:I6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:I9"/>
+    <mergeCell ref="Q4:AD6"/>
+    <mergeCell ref="Q7:AD9"/>
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="P4:P6"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="K4:L17"/>
+    <mergeCell ref="Q10:AD12"/>
+    <mergeCell ref="Q13:AD15"/>
+    <mergeCell ref="Q16:AD18"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="Q19:AD21"/>
+    <mergeCell ref="Q22:AD24"/>
+    <mergeCell ref="O26:AD28"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:L39"/>
+    <mergeCell ref="C28:L30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:L36"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="O29:AD65"/>
+    <mergeCell ref="P22:P24"/>
     <mergeCell ref="O71:AD85"/>
     <mergeCell ref="B82:B84"/>
     <mergeCell ref="C82:L84"/>
@@ -33419,89 +33502,6 @@
     <mergeCell ref="A79:A81"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="C79:L81"/>
-    <mergeCell ref="Q19:AD21"/>
-    <mergeCell ref="Q22:AD24"/>
-    <mergeCell ref="O26:AD28"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:L39"/>
-    <mergeCell ref="C28:L30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:L36"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="O22:O24"/>
-    <mergeCell ref="O29:AD65"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="O1:O3"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="Q1:AD3"/>
-    <mergeCell ref="F2:I3"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="F5:I6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:I9"/>
-    <mergeCell ref="Q4:AD6"/>
-    <mergeCell ref="Q7:AD9"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="P4:P6"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="K4:L17"/>
-    <mergeCell ref="Q10:AD12"/>
-    <mergeCell ref="Q13:AD15"/>
-    <mergeCell ref="Q16:AD18"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:L75"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:L54"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:L42"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="C76:L78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C61:L63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:L66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:L69"/>
-    <mergeCell ref="P22:P24"/>
-    <mergeCell ref="O13:O15"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:L60"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:L33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B19:J20"/>
-    <mergeCell ref="B21:J22"/>
-    <mergeCell ref="B10:I15"/>
-    <mergeCell ref="A16:G18"/>
-    <mergeCell ref="H16:I18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="B23:J26"/>
-    <mergeCell ref="K25:L26"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
